--- a/storage/processed/recipe/recipe_final.xlsx
+++ b/storage/processed/recipe/recipe_final.xlsx
@@ -2,100 +2,52 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rb78d969eb52b45e7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="recipe_final" sheetId="1" r:id="Re85771a73e974c09"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="recipe_detail" sheetId="2" r:id="Rd576f15c9ae04377"/>
   </x:sheets>
 </x:workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:si>
-    <x:t xml:space="preserve">레시피ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">레시피명</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">메뉴 대분류</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">세부 카테고리</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">주재료</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">상황 태그</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">재료명</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">재료 분량</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">재료 수</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">총 소요 시간(분)</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">난이도</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">필요 도구</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">설거지 수준</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">조리 단계 수</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">조리 단계</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">단계별 시간</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">보관 방법</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">대체 재료</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">생략 가능 재료</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">초보 팁</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">실패 방지 팁</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">초보 적합도(5점)</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">1인 가구 적합도(5점)</x:t>
-  </x:si>
-</x:sst>
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="1">
+  <x:fonts count="3">
     <x:font>
       <x:sz val="11"/>
-      <x:color theme="1"/>
-      <x:name val="Calibri"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FF4A2626"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FF3F3028"/>
+      <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
-  <x:fills count="2">
+  <x:fills count="4">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
     <x:fill>
       <x:patternFill patternType="gray125"/>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFBEAEC"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF7F3EE"/>
+      </x:patternFill>
     </x:fill>
   </x:fills>
   <x:borders count="1">
@@ -104,9 +56,21 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="2">
+  <x:cellXfs count="8">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -114,10 +78,61 @@
 </x:styleSheet>
 </file>
 
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="RecipeFinalTable" displayName="RecipeFinalTable" ref="A1:L172" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:tableColumns count="12">
+    <x:tableColumn id="1" name="RCP_SNO"/>
+    <x:tableColumn id="2" name="CKG_NM"/>
+    <x:tableColumn id="3" name="INQ_CNT"/>
+    <x:tableColumn id="4" name="SRAP_CNT"/>
+    <x:tableColumn id="5" name="CKG_MTH_ACTO_NM"/>
+    <x:tableColumn id="6" name="CKG_STA_ACTO_NM"/>
+    <x:tableColumn id="7" name="CKG_MTRL_ACTO_NM"/>
+    <x:tableColumn id="8" name="CKG_KND_ACTO_NM"/>
+    <x:tableColumn id="9" name="CKG_MTRL_CN"/>
+    <x:tableColumn id="10" name="CKG_INBUN_NM"/>
+    <x:tableColumn id="11" name="CKG_DODF_NM"/>
+    <x:tableColumn id="12" name="CKG_TIME_NM"/>
+  </x:tableColumns>
+  <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</x:table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="RecipeDetailTable" displayName="RecipeDetailTable" ref="A1:W172" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:tableColumns count="23">
+    <x:tableColumn id="1" name="레시피ID"/>
+    <x:tableColumn id="2" name="레시피명"/>
+    <x:tableColumn id="3" name="메뉴 대분류"/>
+    <x:tableColumn id="4" name="세부 카테고리"/>
+    <x:tableColumn id="5" name="주재료"/>
+    <x:tableColumn id="6" name="상황 태그"/>
+    <x:tableColumn id="7" name="재료명"/>
+    <x:tableColumn id="8" name="재료 분량"/>
+    <x:tableColumn id="9" name="재료 수"/>
+    <x:tableColumn id="10" name="총 소요 시간(분)"/>
+    <x:tableColumn id="11" name="난이도"/>
+    <x:tableColumn id="12" name="필요 도구"/>
+    <x:tableColumn id="13" name="설거지 수준"/>
+    <x:tableColumn id="14" name="조리 단계 수"/>
+    <x:tableColumn id="15" name="조리 단계"/>
+    <x:tableColumn id="16" name="단계별 시간"/>
+    <x:tableColumn id="17" name="보관 방법"/>
+    <x:tableColumn id="18" name="대체 재료"/>
+    <x:tableColumn id="19" name="생략 가능 재료"/>
+    <x:tableColumn id="20" name="초보 팁"/>
+    <x:tableColumn id="21" name="실패 방지 팁"/>
+    <x:tableColumn id="22" name="초보 적합도(5점)"/>
+    <x:tableColumn id="23" name="1인 가구 적합도(5점)"/>
+  </x:tableColumns>
+  <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</x:table>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="ChatGPT">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="ChatGPT">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -125,34 +140,34 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1F497D"/>
+        <a:srgbClr val="0E2841"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="EEECE1"/>
+        <a:srgbClr val="E8E8E8"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4F81BD"/>
+        <a:srgbClr val="156082"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="C0504D"/>
+        <a:srgbClr val="E97132"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9BBB59"/>
+        <a:srgbClr val="196B24"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064A2"/>
+        <a:srgbClr val="0F9ED5"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4BACC6"/>
+        <a:srgbClr val="A02B93"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="F79646"/>
+        <a:srgbClr val="4EA72E"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000FF"/>
+        <a:srgbClr val="467886"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="800080"/>
+        <a:srgbClr val="96607D"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
@@ -167,61 +182,74 @@
         <a:cs typeface="Calibri"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="ChatGPT">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:satMod val="300000"/>
+                <a:tint val="67000"/>
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="35000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:tint val="37000"/>
-                <a:satMod val="300000"/>
+                <a:tint val="73000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
-                <a:satMod val="350000"/>
+                <a:tint val="81000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="100000"/>
+                <a:tint val="94000"/>
+                <a:lumMod val="102000"/>
+                <a:satMod val="103000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
                 <a:shade val="100000"/>
-                <a:satMod val="130000"/>
+                <a:lumMod val="100000"/>
+                <a:satMod val="110000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:shade val="100000"/>
-                <a:satMod val="350000"/>
+                <a:shade val="78000"/>
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="0"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525">
+        <a:ln w="12700">
           <a:solidFill>
-            <a:schemeClr val="phClr">
-              <a:shade val="95000"/>
-              <a:satMod val="105000"/>
-            </a:schemeClr>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="19050">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -231,37 +259,19 @@
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="38100">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000">
               <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
+                <a:alpha val="63000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
@@ -271,50 +281,38 @@
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="40000"/>
-                <a:satMod val="350000"/>
+                <a:tint val="93000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
+                <a:satMod val="150000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="40000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:tint val="45000"/>
-                <a:shade val="99000"/>
-                <a:satMod val="350000"/>
+                <a:tint val="98000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="20000"/>
-                <a:satMod val="255000"/>
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
-          </a:path>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="80000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="30000"/>
-                <a:satMod val="200000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
-          </a:path>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
@@ -326,81 +324,6640 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="46" width="24.85714340209961" customWidth="1"/>
+    <x:col min="1" max="1" width="12" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="24" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="10" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="10" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="20" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="34" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="22" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="22" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="72" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="14" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="14" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="14" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1">
-      <x:c r="A1" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="B1" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C1" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D1" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E1" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="F1" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="G1" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="H1" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="I1" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="J1" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="K1" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="L1" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="M1" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="N1" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="O1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="P1" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="Q1" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="R1" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="S1" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="T1" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="U1" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="V1" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="W1" t="s">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2">
+    <x:row r="1" ht="26" customHeight="1">
+      <x:c r="A1" s="2" t="str">
+        <x:v>RCP_SNO</x:v>
+      </x:c>
+      <x:c r="B1" s="2" t="str">
+        <x:v>CKG_NM</x:v>
+      </x:c>
+      <x:c r="C1" s="2" t="str">
+        <x:v>INQ_CNT</x:v>
+      </x:c>
+      <x:c r="D1" s="2" t="str">
+        <x:v>SRAP_CNT</x:v>
+      </x:c>
+      <x:c r="E1" s="2" t="str">
+        <x:v>CKG_MTH_ACTO_NM</x:v>
+      </x:c>
+      <x:c r="F1" s="2" t="str">
+        <x:v>CKG_STA_ACTO_NM</x:v>
+      </x:c>
+      <x:c r="G1" s="2" t="str">
+        <x:v>CKG_MTRL_ACTO_NM</x:v>
+      </x:c>
+      <x:c r="H1" s="2" t="str">
+        <x:v>CKG_KND_ACTO_NM</x:v>
+      </x:c>
+      <x:c r="I1" s="2" t="str">
+        <x:v>CKG_MTRL_CN</x:v>
+      </x:c>
+      <x:c r="J1" s="2" t="str">
+        <x:v>CKG_INBUN_NM</x:v>
+      </x:c>
+      <x:c r="K1" s="2" t="str">
+        <x:v>CKG_DODF_NM</x:v>
+      </x:c>
+      <x:c r="L1" s="2" t="str">
+        <x:v>CKG_TIME_NM</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" ht="22" customHeight="1">
+      <x:c r="A2" s="4" t="n">
+        <x:v>1001</x:v>
+      </x:c>
+      <x:c r="B2" s="4" t="str">
+        <x:v>가지구이</x:v>
+      </x:c>
+      <x:c r="C2" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D2" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E2" s="5" t="str">
+        <x:v>구이</x:v>
+      </x:c>
+      <x:c r="F2" s="5" t="str">
+        <x:v>15분 이하|원팬 요리|도시락 가능|밥반찬</x:v>
+      </x:c>
+      <x:c r="G2" s="5" t="str">
+        <x:v>가지</x:v>
+      </x:c>
+      <x:c r="H2" s="5" t="str">
+        <x:v>반찬</x:v>
+      </x:c>
+      <x:c r="I2" s="5" t="str">
+        <x:v>[['가지', '1', '개(180g)'], ['식용유', '10', 'ml(2작은술)'], ['진간장', '5', 'ml(1작은술)'], ['식초', '5', 'ml(1작은술)'], ['설탕', '2', 'g(1/2작은술)'], ['다진 대파', '10', 'g'], ['통깨', '2', 'g(1/2작은술)']]</x:v>
+      </x:c>
+      <x:c r="J2" s="5" t="str">
+        <x:v>1인분</x:v>
+      </x:c>
+      <x:c r="K2" s="5" t="str">
+        <x:v>초급</x:v>
+      </x:c>
+      <x:c r="L2" s="5" t="str">
+        <x:v>15분이내</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="22" customHeight="1">
+      <x:c r="A3" s="4" t="n">
+        <x:v>1002</x:v>
+      </x:c>
+      <x:c r="B3" s="4" t="str">
+        <x:v>가지무침</x:v>
+      </x:c>
+      <x:c r="C3" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D3" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E3" s="5" t="str">
+        <x:v>무침</x:v>
+      </x:c>
+      <x:c r="F3" s="5" t="str">
+        <x:v>15분 이하|전자레인지|불 없이 가능|도시락 가능|밥반찬</x:v>
+      </x:c>
+      <x:c r="G3" s="5" t="str">
+        <x:v>가지</x:v>
+      </x:c>
+      <x:c r="H3" s="5" t="str">
+        <x:v>반찬</x:v>
+      </x:c>
+      <x:c r="I3" s="5" t="str">
+        <x:v>[['가지', '1', '개(180g)'], ['진간장', '7.5', 'ml(1/2큰술)'], ['다진 마늘', '2', 'g(1/2작은술)'], ['참기름', '5', 'ml(1작은술)'], ['고춧가루', '1', 'g(1/2작은술)'], ['다진 대파', '8', 'g'], ['통깨', '2', 'g(1/2작은술)']]</x:v>
+      </x:c>
+      <x:c r="J3" s="5" t="str">
+        <x:v>1인분</x:v>
+      </x:c>
+      <x:c r="K3" s="5" t="str">
+        <x:v>초급</x:v>
+      </x:c>
+      <x:c r="L3" s="5" t="str">
+        <x:v>12분이내</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="22" customHeight="1">
+      <x:c r="A4" s="4" t="n">
+        <x:v>1003</x:v>
+      </x:c>
+      <x:c r="B4" s="4" t="str">
+        <x:v>가지볶음</x:v>
+      </x:c>
+      <x:c r="C4" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D4" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E4" s="5" t="str">
+        <x:v>볶음</x:v>
+      </x:c>
+      <x:c r="F4" s="5" t="str">
+        <x:v>15분 이하|원팬 요리|설거지 적음|도시락 가능|밥반찬</x:v>
+      </x:c>
+      <x:c r="G4" s="5" t="str">
+        <x:v>가지|양파</x:v>
+      </x:c>
+      <x:c r="H4" s="5" t="str">
+        <x:v>반찬</x:v>
+      </x:c>
+      <x:c r="I4" s="5" t="str">
+        <x:v>[['가지', '1', '개(180g)'], ['양파', '1/4', '개(50g)'], ['식용유', '10', 'ml(2작은술)'], ['진간장', '10', 'ml(2작은술)'], ['굴소스', '5', 'ml(1작은술)'], ['다진 마늘', '2', 'g(1/2작은술)'], ['물', '30', 'ml(2큰술)'], ['참기름', '2.5', 'ml(1/2작은술)'], ['통깨', '1', 'g']]</x:v>
+      </x:c>
+      <x:c r="J4" s="5" t="str">
+        <x:v>1인분</x:v>
+      </x:c>
+      <x:c r="K4" s="5" t="str">
+        <x:v>초급</x:v>
+      </x:c>
+      <x:c r="L4" s="5" t="str">
+        <x:v>15분이내</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="22" customHeight="1">
+      <x:c r="A5" s="4" t="n">
+        <x:v>1004</x:v>
+      </x:c>
+      <x:c r="B5" s="4" t="str">
+        <x:v>감자전</x:v>
+      </x:c>
+      <x:c r="C5" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D5" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E5" s="5" t="str">
+        <x:v>전·부침</x:v>
+      </x:c>
+      <x:c r="F5" s="5" t="str">
+        <x:v>재료 5개 이하|원팬 요리|칼 없이 가능|설거지 적음|도시락 가능|밥반찬|남은 재료 활용</x:v>
+      </x:c>
+      <x:c r="G5" s="5" t="str">
+        <x:v>감자</x:v>
+      </x:c>
+      <x:c r="H5" s="5" t="str">
+        <x:v>반찬</x:v>
+      </x:c>
+      <x:c r="I5" s="5" t="str">
+        <x:v>[['감자', '1', '개(220g)'], ['부침가루', '15', 'g(1큰술)'], ['소금', '1', 'g'], ['식용유', '15', 'ml(1큰술)'], ['물', '15', 'ml(1큰술, 필요 시)']]</x:v>
+      </x:c>
+      <x:c r="J5" s="5" t="str">
+        <x:v>1인분</x:v>
+      </x:c>
+      <x:c r="K5" s="5" t="str">
+        <x:v>초급</x:v>
+      </x:c>
+      <x:c r="L5" s="5" t="str">
+        <x:v>20분이내</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="22" customHeight="1">
+      <x:c r="A6" s="4" t="n">
+        <x:v>1005</x:v>
+      </x:c>
+      <x:c r="B6" s="4" t="str">
+        <x:v>감자조림</x:v>
+      </x:c>
+      <x:c r="C6" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D6" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E6" s="5" t="str">
+        <x:v>조림</x:v>
+      </x:c>
+      <x:c r="F6" s="5" t="str">
+        <x:v>설거지 적음|도시락 가능|밥반찬</x:v>
+      </x:c>
+      <x:c r="G6" s="5" t="str">
+        <x:v>감자|양파</x:v>
+      </x:c>
+      <x:c r="H6" s="5" t="str">
+        <x:v>반찬</x:v>
+      </x:c>
+      <x:c r="I6" s="5" t="str">
+        <x:v>[['감자', '1', '개(200g)'], ['양파', '1/4', '개(50g)'], ['물', '150', 'ml'], ['진간장', '15', 'ml(1큰술)'], ['설탕', '5', 'g(1작은술)'], ['올리고당', '10', 'g(2작은술)'], ['식용유', '5', 'ml(1작은술)'], ['다진 마늘', '2', 'g(1/2작은술)'], ['통깨', '1', 'g']]</x:v>
+      </x:c>
+      <x:c r="J6" s="5" t="str">
+        <x:v>1인분</x:v>
+      </x:c>
+      <x:c r="K6" s="5" t="str">
+        <x:v>초급</x:v>
+      </x:c>
+      <x:c r="L6" s="5" t="str">
+        <x:v>25분이내</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="22" customHeight="1">
+      <x:c r="A7" s="4" t="n">
+        <x:v>1006</x:v>
+      </x:c>
+      <x:c r="B7" s="4" t="str">
+        <x:v>감자채볶음</x:v>
+      </x:c>
+      <x:c r="C7" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D7" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E7" s="5" t="str">
+        <x:v>볶음</x:v>
+      </x:c>
+      <x:c r="F7" s="5" t="str">
+        <x:v>원팬 요리|도시락 가능|밥반찬|남은 재료 활용</x:v>
+      </x:c>
+      <x:c r="G7" s="5" t="str">
+        <x:v>감자|양파|당근</x:v>
+      </x:c>
+      <x:c r="H7" s="5" t="str">
+        <x:v>반찬</x:v>
+      </x:c>
+      <x:c r="I7" s="5" t="str">
+        <x:v>[['감자', '1', '개(200g)'], ['양파', '1/4', '개(50g)'], ['당근', '20', 'g'], ['식용유', '10', 'ml(2작은술)'], ['소금', '1.5', 'g'], ['후추', '0.1', 'g'], ['통깨', '1', 'g']]</x:v>
+      </x:c>
+      <x:c r="J7" s="5" t="str">
+        <x:v>1인분</x:v>
+      </x:c>
+      <x:c r="K7" s="5" t="str">
+        <x:v>초급</x:v>
+      </x:c>
+      <x:c r="L7" s="5" t="str">
+        <x:v>18분이내</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="22" customHeight="1">
+      <x:c r="A8" s="4" t="n">
+        <x:v>1007</x:v>
+      </x:c>
+      <x:c r="B8" s="4" t="str">
+        <x:v>계란말이</x:v>
+      </x:c>
+      <x:c r="C8" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D8" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E8" s="5" t="str">
+        <x:v>계란 요리</x:v>
+      </x:c>
+      <x:c r="F8" s="5" t="str">
+        <x:v>15분 이하|원팬 요리|도시락 가능|밥반찬</x:v>
+      </x:c>
+      <x:c r="G8" s="5" t="str">
+        <x:v>계란|당근</x:v>
+      </x:c>
+      <x:c r="H8" s="5" t="str">
+        <x:v>반찬</x:v>
+      </x:c>
+      <x:c r="I8" s="5" t="str">
+        <x:v>[['계란', '3', '개(150g)'], ['대파', '10', 'g'], ['당근', '15', 'g'], ['소금', '1', 'g'], ['설탕', '2', 'g(1/2작은술)'], ['물', '15', 'ml(1큰술)'], ['식용유', '10', 'ml(2작은술)']]</x:v>
+      </x:c>
+      <x:c r="J8" s="5" t="str">
+        <x:v>1인분</x:v>
+      </x:c>
+      <x:c r="K8" s="5" t="str">
+        <x:v>중급</x:v>
+      </x:c>
+      <x:c r="L8" s="5" t="str">
+        <x:v>15분이내</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="22" customHeight="1">
+      <x:c r="A9" s="4" t="n">
+        <x:v>1008</x:v>
+      </x:c>
+      <x:c r="B9" s="4" t="str">
+        <x:v>계란장</x:v>
+      </x:c>
+      <x:c r="C9" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D9" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E9" s="5" t="str">
+        <x:v>절임</x:v>
+      </x:c>
+      <x:c r="F9" s="5" t="str">
+        <x:v>냄비 하나|도시락 가능|밥반찬</x:v>
+      </x:c>
+      <x:c r="G9" s="5" t="str">
+        <x:v>계란|양파</x:v>
+      </x:c>
+      <x:c r="H9" s="5" t="str">
+        <x:v>반찬</x:v>
+      </x:c>
+      <x:c r="I9" s="5" t="str">
+        <x:v>[['계란', '2', '개(100g)'], ['물', '100', 'ml'], ['진간장', '60', 'ml(4큰술)'], ['설탕', '10', 'g(2작은술)'], ['식초', '5', 'ml(1작은술)'], ['대파', '15', 'g'], ['양파', '30', 'g'], ['통깨', '2', 'g(1/2작은술)']]</x:v>
+      </x:c>
+      <x:c r="J9" s="5" t="str">
+        <x:v>1인분</x:v>
+      </x:c>
+      <x:c r="K9" s="5" t="str">
+        <x:v>초급</x:v>
+      </x:c>
+      <x:c r="L9" s="5" t="str">
+        <x:v>20분이내</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="22" customHeight="1">
+      <x:c r="A10" s="4" t="n">
+        <x:v>1009</x:v>
+      </x:c>
+      <x:c r="B10" s="4" t="str">
+        <x:v>계란찜</x:v>
+      </x:c>
+      <x:c r="C10" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D10" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E10" s="5" t="str">
+        <x:v>계란찜</x:v>
+      </x:c>
+      <x:c r="F10" s="5" t="str">
+        <x:v>10분 이하|전자레인지|칼 없이 가능|불 없이 가능|설거지 적음|도시락 가능|아침 식사|밥반찬</x:v>
+      </x:c>
+      <x:c r="G10" s="5" t="str">
+        <x:v>계란</x:v>
+      </x:c>
+      <x:c r="H10" s="5" t="str">
+        <x:v>반찬</x:v>
+      </x:c>
+      <x:c r="I10" s="5" t="str">
+        <x:v>[['계란', '2', '개(100g)'], ['물', '120', 'ml'], ['국간장', '5', 'ml(1작은술)'], ['소금', '0.5', 'g'], ['대파', '8', 'g'], ['참기름', '2.5', 'ml(1/2작은술)']]</x:v>
+      </x:c>
+      <x:c r="J10" s="5" t="str">
+        <x:v>1인분</x:v>
+      </x:c>
+      <x:c r="K10" s="5" t="str">
+        <x:v>초급</x:v>
+      </x:c>
+      <x:c r="L10" s="5" t="str">
+        <x:v>10분이내</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="22" customHeight="1">
+      <x:c r="A11" s="4" t="n">
+        <x:v>1010</x:v>
+      </x:c>
+      <x:c r="B11" s="4" t="str">
+        <x:v>계란프라이</x:v>
+      </x:c>
+      <x:c r="C11" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D11" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E11" s="5" t="str">
+        <x:v>계란 요리</x:v>
+      </x:c>
+      <x:c r="F11" s="5" t="str">
+        <x:v>10분 이하|재료 5개 이하|원팬 요리|칼 없이 가능|설거지 적음|아침 식사|밥반찬</x:v>
+      </x:c>
+      <x:c r="G11" s="5" t="str">
+        <x:v>계란</x:v>
+      </x:c>
+      <x:c r="H11" s="5" t="str">
+        <x:v>반찬</x:v>
+      </x:c>
+      <x:c r="I11" s="5" t="str">
+        <x:v>[['계란', '1', '개(50g)'], ['식용유', '5', 'ml(1작은술)'], ['소금', '0.3', 'g'], ['후추', '0.05', 'g']]</x:v>
+      </x:c>
+      <x:c r="J11" s="5" t="str">
+        <x:v>1인분</x:v>
+      </x:c>
+      <x:c r="K11" s="5" t="str">
+        <x:v>초급</x:v>
+      </x:c>
+      <x:c r="L11" s="5" t="str">
+        <x:v>5분이내</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="22" customHeight="1">
+      <x:c r="A12" s="4" t="n">
+        <x:v>1011</x:v>
+      </x:c>
+      <x:c r="B12" s="4" t="str">
+        <x:v>김치볶음</x:v>
+      </x:c>
+      <x:c r="C12" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D12" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E12" s="5" t="str">
+        <x:v>볶음</x:v>
+      </x:c>
+      <x:c r="F12" s="5" t="str">
+        <x:v>15분 이하|원팬 요리|설거지 적음|도시락 가능|냉동 가능|밥반찬|남은 재료 활용</x:v>
+      </x:c>
+      <x:c r="G12" s="5" t="str">
+        <x:v>김치|양파</x:v>
+      </x:c>
+      <x:c r="H12" s="5" t="str">
+        <x:v>반찬</x:v>
+      </x:c>
+      <x:c r="I12" s="5" t="str">
+        <x:v>[['배추김치', '180', 'g'], ['양파', '1/4', '개(50g)'], ['대파', '15', 'g'], ['식용유', '10', 'ml(2작은술)'], ['설탕', '5', 'g(1작은술)'], ['진간장', '5', 'ml(1작은술)'], ['참기름', '5', 'ml(1작은술)'], ['통깨', '1', 'g']]</x:v>
+      </x:c>
+      <x:c r="J12" s="5" t="str">
+        <x:v>1인분</x:v>
+      </x:c>
+      <x:c r="K12" s="5" t="str">
+        <x:v>초급</x:v>
+      </x:c>
+      <x:c r="L12" s="5" t="str">
+        <x:v>12분이내</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="22" customHeight="1">
+      <x:c r="A13" s="4" t="n">
+        <x:v>1012</x:v>
+      </x:c>
+      <x:c r="B13" s="4" t="str">
+        <x:v>김치전</x:v>
+      </x:c>
+      <x:c r="C13" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D13" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E13" s="5" t="str">
+        <x:v>전·부침</x:v>
+      </x:c>
+      <x:c r="F13" s="5" t="str">
+        <x:v>원팬 요리|도시락 가능|밥반찬|남은 재료 활용</x:v>
+      </x:c>
+      <x:c r="G13" s="5" t="str">
+        <x:v>김치</x:v>
+      </x:c>
+      <x:c r="H13" s="5" t="str">
+        <x:v>반찬</x:v>
+      </x:c>
+      <x:c r="I13" s="5" t="str">
+        <x:v>[['배추김치', '150', 'g'], ['부침가루', '80', 'g'], ['물', '80', 'ml'], ['김치국물', '20', 'ml'], ['대파', '15', 'g'], ['설탕', '2', 'g(1/2작은술)'], ['식용유', '20', 'ml(1큰술+1작은술)']]</x:v>
+      </x:c>
+      <x:c r="J13" s="5" t="str">
+        <x:v>1인분</x:v>
+      </x:c>
+      <x:c r="K13" s="5" t="str">
+        <x:v>초급</x:v>
+      </x:c>
+      <x:c r="L13" s="5" t="str">
+        <x:v>18분이내</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="22" customHeight="1">
+      <x:c r="A14" s="4" t="n">
+        <x:v>1013</x:v>
+      </x:c>
+      <x:c r="B14" s="4" t="str">
+        <x:v>단무지무침</x:v>
+      </x:c>
+      <x:c r="C14" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D14" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E14" s="5" t="str">
+        <x:v>무침</x:v>
+      </x:c>
+      <x:c r="F14" s="5" t="str">
+        <x:v>10분 이하|불 없이 가능|설거지 적음|도시락 가능|밥반찬</x:v>
+      </x:c>
+      <x:c r="G14" s="5" t="str">
+        <x:v>단무지</x:v>
+      </x:c>
+      <x:c r="H14" s="5" t="str">
+        <x:v>반찬</x:v>
+      </x:c>
+      <x:c r="I14" s="5" t="str">
+        <x:v>[['단무지', '100', 'g'], ['대파', '8', 'g'], ['고춧가루', '2', 'g(1작은술)'], ['식초', '5', 'ml(1작은술)'], ['설탕', '2', 'g(1/2작은술)'], ['참기름', '5', 'ml(1작은술)'], ['통깨', '2', 'g(1/2작은술)']]</x:v>
+      </x:c>
+      <x:c r="J14" s="5" t="str">
+        <x:v>1인분</x:v>
+      </x:c>
+      <x:c r="K14" s="5" t="str">
+        <x:v>초급</x:v>
+      </x:c>
+      <x:c r="L14" s="5" t="str">
+        <x:v>7분이내</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="22" customHeight="1">
+      <x:c r="A15" s="4" t="n">
+        <x:v>1014</x:v>
+      </x:c>
+      <x:c r="B15" s="4" t="str">
+        <x:v>돼지고기 장조림</x:v>
+      </x:c>
+      <x:c r="C15" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D15" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E15" s="5" t="str">
+        <x:v>장조림</x:v>
+      </x:c>
+      <x:c r="F15" s="5" t="str">
+        <x:v>냄비 하나|도시락 가능|냉동 가능|밥반찬</x:v>
+      </x:c>
+      <x:c r="G15" s="5" t="str">
+        <x:v>돼지고기</x:v>
+      </x:c>
+      <x:c r="H15" s="5" t="str">
+        <x:v>반찬</x:v>
+      </x:c>
+      <x:c r="I15" s="5" t="str">
+        <x:v>[['돼지고기 안심 또는 앞다리살', '180', 'g'], ['물', '500', 'ml'], ['진간장', '45', 'ml(3큰술)'], ['설탕', '10', 'g(2작은술)'], ['맛술', '15', 'ml(1큰술)'], ['다진 마늘', '3', 'g'], ['대파 흰 부분', '20', 'g'], ['통후추', '5', '알(0.2g)'], ['꽈리고추', '40', 'g(선택)']]</x:v>
+      </x:c>
+      <x:c r="J15" s="5" t="str">
+        <x:v>1인분</x:v>
+      </x:c>
+      <x:c r="K15" s="5" t="str">
+        <x:v>중급</x:v>
+      </x:c>
+      <x:c r="L15" s="5" t="str">
+        <x:v>40분이내</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="22" customHeight="1">
+      <x:c r="A16" s="4" t="n">
+        <x:v>1015</x:v>
+      </x:c>
+      <x:c r="B16" s="4" t="str">
+        <x:v>두부 계란볶음</x:v>
+      </x:c>
+      <x:c r="C16" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D16" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E16" s="5" t="str">
+        <x:v>볶음</x:v>
+      </x:c>
+      <x:c r="F16" s="5" t="str">
+        <x:v>15분 이하|원팬 요리|칼 없이 가능|설거지 적음|도시락 가능|밥반찬|남은 재료 활용</x:v>
+      </x:c>
+      <x:c r="G16" s="5" t="str">
+        <x:v>두부|계란</x:v>
+      </x:c>
+      <x:c r="H16" s="5" t="str">
+        <x:v>반찬</x:v>
+      </x:c>
+      <x:c r="I16" s="5" t="str">
+        <x:v>[['부침용 두부', '200', 'g'], ['계란', '2', '개(100g)'], ['대파', '15', 'g'], ['식용유', '10', 'ml(2작은술)'], ['진간장', '10', 'ml(2작은술)'], ['굴소스', '5', 'ml(1작은술)'], ['소금', '0.3', 'g'], ['후추', '0.1', 'g'], ['참기름', '2.5', 'ml(1/2작은술)']]</x:v>
+      </x:c>
+      <x:c r="J16" s="5" t="str">
+        <x:v>1인분</x:v>
+      </x:c>
+      <x:c r="K16" s="5" t="str">
+        <x:v>초급</x:v>
+      </x:c>
+      <x:c r="L16" s="5" t="str">
+        <x:v>15분이내</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="22" customHeight="1">
+      <x:c r="A17" s="4" t="n">
+        <x:v>1016</x:v>
+      </x:c>
+      <x:c r="B17" s="4" t="str">
+        <x:v>두부부침</x:v>
+      </x:c>
+      <x:c r="C17" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D17" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E17" s="5" t="str">
+        <x:v>전·부침</x:v>
+      </x:c>
+      <x:c r="F17" s="5" t="str">
+        <x:v>15분 이하|원팬 요리|도시락 가능|밥반찬</x:v>
+      </x:c>
+      <x:c r="G17" s="5" t="str">
+        <x:v>두부</x:v>
+      </x:c>
+      <x:c r="H17" s="5" t="str">
+        <x:v>반찬</x:v>
+      </x:c>
+      <x:c r="I17" s="5" t="str">
+        <x:v>[['부침용 두부', '250', 'g'], ['소금', '0.8', 'g'], ['식용유', '10', 'ml(2작은술)'], ['진간장', '7.5', 'ml(1/2큰술)'], ['식초', '5', 'ml(1작은술)'], ['고춧가루', '1', 'g(1/2작은술)'], ['다진 대파', '8', 'g'], ['통깨', '1', 'g']]</x:v>
+      </x:c>
+      <x:c r="J17" s="5" t="str">
+        <x:v>1인분</x:v>
+      </x:c>
+      <x:c r="K17" s="5" t="str">
+        <x:v>초급</x:v>
+      </x:c>
+      <x:c r="L17" s="5" t="str">
+        <x:v>15분이내</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="22" customHeight="1">
+      <x:c r="A18" s="4" t="n">
+        <x:v>1017</x:v>
+      </x:c>
+      <x:c r="B18" s="4" t="str">
+        <x:v>두부조림</x:v>
+      </x:c>
+      <x:c r="C18" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D18" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E18" s="5" t="str">
+        <x:v>조림</x:v>
+      </x:c>
+      <x:c r="F18" s="5" t="str">
+        <x:v>도시락 가능|밥반찬</x:v>
+      </x:c>
+      <x:c r="G18" s="5" t="str">
+        <x:v>두부|양파</x:v>
+      </x:c>
+      <x:c r="H18" s="5" t="str">
+        <x:v>반찬</x:v>
+      </x:c>
+      <x:c r="I18" s="5" t="str">
+        <x:v>[['부침용 두부', '250', 'g'], ['양파', '1/4', '개(50g)'], ['대파', '15', 'g'], ['식용유', '10', 'ml(2작은술)'], ['물', '120', 'ml'], ['진간장', '20', 'ml(1큰술+1작은술)'], ['고춧가루', '3', 'g(1/2큰술)'], ['설탕', '5', 'g(1작은술)'], ['다진 마늘', '3', 'g'], ['참기름', '2.5', 'ml(1/2작은술)'], ['통깨', '1', 'g']]</x:v>
+      </x:c>
+      <x:c r="J18" s="5" t="str">
+        <x:v>1인분</x:v>
+      </x:c>
+      <x:c r="K18" s="5" t="str">
+        <x:v>초급</x:v>
+      </x:c>
+      <x:c r="L18" s="5" t="str">
+        <x:v>22분이내</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="22" customHeight="1">
+      <x:c r="A19" s="4" t="n">
+        <x:v>1018</x:v>
+      </x:c>
+      <x:c r="B19" s="4" t="str">
+        <x:v>메추리알 장조림</x:v>
+      </x:c>
+      <x:c r="C19" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D19" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E19" s="5" t="str">
+        <x:v>장조림</x:v>
+      </x:c>
+      <x:c r="F19" s="5" t="str">
+        <x:v>냄비 하나|칼 없이 가능|설거지 적음|도시락 가능|밥반찬</x:v>
+      </x:c>
+      <x:c r="G19" s="5" t="str">
+        <x:v>메추리알|꽈리고추</x:v>
+      </x:c>
+      <x:c r="H19" s="5" t="str">
+        <x:v>반찬</x:v>
+      </x:c>
+      <x:c r="I19" s="5" t="str">
+        <x:v>[['삶은 깐 메추리알', '200', 'g(약 20개)'], ['물', '200', 'ml'], ['진간장', '50', 'ml(3큰술+1작은술)'], ['설탕', '10', 'g(2작은술)'], ['맛술', '15', 'ml(1큰술)'], ['다진 마늘', '2', 'g'], ['꽈리고추', '40', 'g(선택)'], ['통깨', '1', 'g']]</x:v>
+      </x:c>
+      <x:c r="J19" s="5" t="str">
+        <x:v>1인분</x:v>
+      </x:c>
+      <x:c r="K19" s="5" t="str">
+        <x:v>초급</x:v>
+      </x:c>
+      <x:c r="L19" s="5" t="str">
+        <x:v>20분이내</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="22" customHeight="1">
+      <x:c r="A20" s="4" t="n">
+        <x:v>1019</x:v>
+      </x:c>
+      <x:c r="B20" s="4" t="str">
+        <x:v>멸치볶음</x:v>
+      </x:c>
+      <x:c r="C20" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D20" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E20" s="5" t="str">
+        <x:v>볶음</x:v>
+      </x:c>
+      <x:c r="F20" s="5" t="str">
+        <x:v>15분 이하|원팬 요리|칼 없이 가능|설거지 적음|도시락 가능|밥반찬</x:v>
+      </x:c>
+      <x:c r="G20" s="5" t="str">
+        <x:v>잔멸치|견과류</x:v>
+      </x:c>
+      <x:c r="H20" s="5" t="str">
+        <x:v>반찬</x:v>
+      </x:c>
+      <x:c r="I20" s="5" t="str">
+        <x:v>[['볶음용 잔멸치', '50', 'g'], ['식용유', '5', 'ml(1작은술)'], ['진간장', '5', 'ml(1작은술)'], ['설탕', '3', 'g(3/4작은술)'], ['올리고당', '10', 'g(2작은술)'], ['맛술', '5', 'ml(1작은술)'], ['참기름', '2.5', 'ml(1/2작은술)'], ['통깨', '2', 'g(1/2작은술)'], ['견과류', '15', 'g(선택)']]</x:v>
+      </x:c>
+      <x:c r="J20" s="5" t="str">
+        <x:v>1인분</x:v>
+      </x:c>
+      <x:c r="K20" s="5" t="str">
+        <x:v>초급</x:v>
+      </x:c>
+      <x:c r="L20" s="5" t="str">
+        <x:v>12분이내</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" ht="22" customHeight="1">
+      <x:c r="A21" s="4" t="n">
+        <x:v>1020</x:v>
+      </x:c>
+      <x:c r="B21" s="4" t="str">
+        <x:v>무생채</x:v>
+      </x:c>
+      <x:c r="C21" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D21" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E21" s="5" t="str">
+        <x:v>무침</x:v>
+      </x:c>
+      <x:c r="F21" s="5" t="str">
+        <x:v>15분 이하|불 없이 가능|도시락 가능|밥반찬</x:v>
+      </x:c>
+      <x:c r="G21" s="5" t="str">
+        <x:v>무</x:v>
+      </x:c>
+      <x:c r="H21" s="5" t="str">
+        <x:v>반찬</x:v>
+      </x:c>
+      <x:c r="I21" s="5" t="str">
+        <x:v>[['무', '200', 'g'], ['대파', '10', 'g'], ['고춧가루', '5', 'g(2작은술)'], ['식초', '10', 'ml(2작은술)'], ['설탕', '8', 'g(2작은술)'], ['액젓', '7.5', 'ml(1/2큰술)'], ['다진 마늘', '3', 'g'], ['소금', '1', 'g'], ['통깨', '1', 'g']]</x:v>
+      </x:c>
+      <x:c r="J21" s="5" t="str">
+        <x:v>1인분</x:v>
+      </x:c>
+      <x:c r="K21" s="5" t="str">
+        <x:v>초급</x:v>
+      </x:c>
+      <x:c r="L21" s="5" t="str">
+        <x:v>12분이내</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" ht="22" customHeight="1">
+      <x:c r="A22" s="4" t="n">
+        <x:v>1021</x:v>
+      </x:c>
+      <x:c r="B22" s="4" t="str">
+        <x:v>버섯볶음</x:v>
+      </x:c>
+      <x:c r="C22" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D22" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E22" s="5" t="str">
+        <x:v>볶음</x:v>
+      </x:c>
+      <x:c r="F22" s="5" t="str">
+        <x:v>15분 이하|원팬 요리|설거지 적음|도시락 가능|밥반찬</x:v>
+      </x:c>
+      <x:c r="G22" s="5" t="str">
+        <x:v>느타리버섯|새송이버섯|양파</x:v>
+      </x:c>
+      <x:c r="H22" s="5" t="str">
+        <x:v>반찬</x:v>
+      </x:c>
+      <x:c r="I22" s="5" t="str">
+        <x:v>[['느타리버섯', '150', 'g'], ['새송이버섯', '100', 'g'], ['양파', '1/4', '개(50g)'], ['대파', '10', 'g'], ['식용유', '10', 'ml(2작은술)'], ['진간장', '10', 'ml(2작은술)'], ['굴소스', '5', 'ml(1작은술)'], ['다진 마늘', '2', 'g'], ['후추', '0.1', 'g'], ['참기름', '2.5', 'ml(1/2작은술)']]</x:v>
+      </x:c>
+      <x:c r="J22" s="5" t="str">
+        <x:v>1인분</x:v>
+      </x:c>
+      <x:c r="K22" s="5" t="str">
+        <x:v>초급</x:v>
+      </x:c>
+      <x:c r="L22" s="5" t="str">
+        <x:v>15분이내</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" ht="22" customHeight="1">
+      <x:c r="A23" s="4" t="n">
+        <x:v>1022</x:v>
+      </x:c>
+      <x:c r="B23" s="4" t="str">
+        <x:v>버터감자</x:v>
+      </x:c>
+      <x:c r="C23" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D23" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E23" s="5" t="str">
+        <x:v>감자 요리</x:v>
+      </x:c>
+      <x:c r="F23" s="5" t="str">
+        <x:v>원팬 요리|전자레인지|도시락 가능|밥반찬</x:v>
+      </x:c>
+      <x:c r="G23" s="5" t="str">
+        <x:v>감자</x:v>
+      </x:c>
+      <x:c r="H23" s="5" t="str">
+        <x:v>반찬</x:v>
+      </x:c>
+      <x:c r="I23" s="5" t="str">
+        <x:v>[['감자', '1', '개(220g)'], ['버터', '15', 'g'], ['소금', '1', 'g'], ['설탕', '3', 'g(3/4작은술, 선택)'], ['파슬리가루', '0.2', 'g(선택)'], ['물', '30', 'ml']]</x:v>
+      </x:c>
+      <x:c r="J23" s="5" t="str">
+        <x:v>1인분</x:v>
+      </x:c>
+      <x:c r="K23" s="5" t="str">
+        <x:v>초급</x:v>
+      </x:c>
+      <x:c r="L23" s="5" t="str">
+        <x:v>18분이내</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" ht="22" customHeight="1">
+      <x:c r="A24" s="4" t="n">
+        <x:v>1023</x:v>
+      </x:c>
+      <x:c r="B24" s="4" t="str">
+        <x:v>부추무침</x:v>
+      </x:c>
+      <x:c r="C24" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D24" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E24" s="5" t="str">
+        <x:v>무침</x:v>
+      </x:c>
+      <x:c r="F24" s="5" t="str">
+        <x:v>10분 이하|불 없이 가능|설거지 적음|도시락 가능|밥반찬</x:v>
+      </x:c>
+      <x:c r="G24" s="5" t="str">
+        <x:v>부추|양파</x:v>
+      </x:c>
+      <x:c r="H24" s="5" t="str">
+        <x:v>반찬</x:v>
+      </x:c>
+      <x:c r="I24" s="5" t="str">
+        <x:v>[['부추', '100', 'g'], ['양파', '30', 'g'], ['고춧가루', '3', 'g(1/2큰술)'], ['진간장', '10', 'ml(2작은술)'], ['식초', '10', 'ml(2작은술)'], ['설탕', '5', 'g(1작은술)'], ['참기름', '5', 'ml(1작은술)'], ['통깨', '1', 'g']]</x:v>
+      </x:c>
+      <x:c r="J24" s="5" t="str">
+        <x:v>1인분</x:v>
+      </x:c>
+      <x:c r="K24" s="5" t="str">
+        <x:v>초급</x:v>
+      </x:c>
+      <x:c r="L24" s="5" t="str">
+        <x:v>8분이내</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" ht="22" customHeight="1">
+      <x:c r="A25" s="4" t="n">
+        <x:v>1024</x:v>
+      </x:c>
+      <x:c r="B25" s="4" t="str">
+        <x:v>부추전</x:v>
+      </x:c>
+      <x:c r="C25" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D25" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E25" s="5" t="str">
+        <x:v>전·부침</x:v>
+      </x:c>
+      <x:c r="F25" s="5" t="str">
+        <x:v>원팬 요리|도시락 가능|밥반찬|남은 재료 활용</x:v>
+      </x:c>
+      <x:c r="G25" s="5" t="str">
+        <x:v>부추|양파|계란</x:v>
+      </x:c>
+      <x:c r="H25" s="5" t="str">
+        <x:v>반찬</x:v>
+      </x:c>
+      <x:c r="I25" s="5" t="str">
+        <x:v>[['부추', '100', 'g'], ['양파', '30', 'g'], ['부침가루', '80', 'g'], ['물', '100', 'ml'], ['계란', '1', '개(50g, 선택)'], ['소금', '0.5', 'g'], ['식용유', '20', 'ml(1큰술+1작은술)']]</x:v>
+      </x:c>
+      <x:c r="J25" s="5" t="str">
+        <x:v>1인분</x:v>
+      </x:c>
+      <x:c r="K25" s="5" t="str">
+        <x:v>초급</x:v>
+      </x:c>
+      <x:c r="L25" s="5" t="str">
+        <x:v>18분이내</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" ht="22" customHeight="1">
+      <x:c r="A26" s="4" t="n">
+        <x:v>1025</x:v>
+      </x:c>
+      <x:c r="B26" s="4" t="str">
+        <x:v>브로콜리찜</x:v>
+      </x:c>
+      <x:c r="C26" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D26" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E26" s="5" t="str">
+        <x:v>찜</x:v>
+      </x:c>
+      <x:c r="F26" s="5" t="str">
+        <x:v>10분 이하|재료 5개 이하|전자레인지|불 없이 가능|도시락 가능|냉동 가능|밥반찬</x:v>
+      </x:c>
+      <x:c r="G26" s="5" t="str">
+        <x:v>브로콜리</x:v>
+      </x:c>
+      <x:c r="H26" s="5" t="str">
+        <x:v>반찬</x:v>
+      </x:c>
+      <x:c r="I26" s="5" t="str">
+        <x:v>[['브로콜리', '200', 'g'], ['물', '30', 'ml(2큰술)'], ['소금', '0.5', 'g'], ['초고추장', '20', 'g(선택) 또는 진간장 10ml+식초 5ml']]</x:v>
+      </x:c>
+      <x:c r="J26" s="5" t="str">
+        <x:v>1인분</x:v>
+      </x:c>
+      <x:c r="K26" s="5" t="str">
+        <x:v>초급</x:v>
+      </x:c>
+      <x:c r="L26" s="5" t="str">
+        <x:v>8분이내</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" ht="22" customHeight="1">
+      <x:c r="A27" s="4" t="n">
+        <x:v>1026</x:v>
+      </x:c>
+      <x:c r="B27" s="4" t="str">
+        <x:v>상추겉절이</x:v>
+      </x:c>
+      <x:c r="C27" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D27" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E27" s="5" t="str">
+        <x:v>무침</x:v>
+      </x:c>
+      <x:c r="F27" s="5" t="str">
+        <x:v>10분 이하|불 없이 가능|설거지 적음|도시락 가능|밥반찬</x:v>
+      </x:c>
+      <x:c r="G27" s="5" t="str">
+        <x:v>상추|양파</x:v>
+      </x:c>
+      <x:c r="H27" s="5" t="str">
+        <x:v>반찬</x:v>
+      </x:c>
+      <x:c r="I27" s="5" t="str">
+        <x:v>[['상추', '100', 'g'], ['양파', '30', 'g'], ['대파', '8', 'g'], ['고춧가루', '3', 'g(1/2큰술)'], ['진간장', '10', 'ml(2작은술)'], ['식초', '10', 'ml(2작은술)'], ['설탕', '5', 'g(1작은술)'], ['참기름', '5', 'ml(1작은술)'], ['통깨', '1', 'g']]</x:v>
+      </x:c>
+      <x:c r="J27" s="5" t="str">
+        <x:v>1인분</x:v>
+      </x:c>
+      <x:c r="K27" s="5" t="str">
+        <x:v>초급</x:v>
+      </x:c>
+      <x:c r="L27" s="5" t="str">
+        <x:v>7분이내</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" ht="22" customHeight="1">
+      <x:c r="A28" s="4" t="n">
+        <x:v>1027</x:v>
+      </x:c>
+      <x:c r="B28" s="4" t="str">
+        <x:v>소고기 장조림</x:v>
+      </x:c>
+      <x:c r="C28" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D28" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E28" s="5" t="str">
+        <x:v>장조림</x:v>
+      </x:c>
+      <x:c r="F28" s="5" t="str">
+        <x:v>냄비 하나|도시락 가능|냉동 가능|밥반찬</x:v>
+      </x:c>
+      <x:c r="G28" s="5" t="str">
+        <x:v>소고기</x:v>
+      </x:c>
+      <x:c r="H28" s="5" t="str">
+        <x:v>반찬</x:v>
+      </x:c>
+      <x:c r="I28" s="5" t="str">
+        <x:v>[['소고기 홍두깨살 또는 우둔살', '180', 'g'], ['물', '650', 'ml'], ['진간장', '50', 'ml(3큰술+1작은술)'], ['설탕', '10', 'g(2작은술)'], ['맛술', '15', 'ml(1큰술)'], ['대파 흰 부분', '20', 'g'], ['마늘', '3', '쪽(15g)'], ['통후추', '5', '알(0.2g)'], ['꽈리고추', '40', 'g(선택)']]</x:v>
+      </x:c>
+      <x:c r="J28" s="5" t="str">
+        <x:v>1인분</x:v>
+      </x:c>
+      <x:c r="K28" s="5" t="str">
+        <x:v>중급</x:v>
+      </x:c>
+      <x:c r="L28" s="5" t="str">
+        <x:v>55분이내</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" ht="22" customHeight="1">
+      <x:c r="A29" s="4" t="n">
+        <x:v>1028</x:v>
+      </x:c>
+      <x:c r="B29" s="4" t="str">
+        <x:v>숙주나물</x:v>
+      </x:c>
+      <x:c r="C29" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D29" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E29" s="5" t="str">
+        <x:v>무침</x:v>
+      </x:c>
+      <x:c r="F29" s="5" t="str">
+        <x:v>10분 이하|냄비 하나|도시락 가능|밥반찬</x:v>
+      </x:c>
+      <x:c r="G29" s="5" t="str">
+        <x:v>숙주</x:v>
+      </x:c>
+      <x:c r="H29" s="5" t="str">
+        <x:v>반찬</x:v>
+      </x:c>
+      <x:c r="I29" s="5" t="str">
+        <x:v>[['숙주', '200', 'g'], ['대파', '10', 'g'], ['국간장', '5', 'ml(1작은술)'], ['소금', '0.8', 'g'], ['다진 마늘', '2', 'g'], ['참기름', '5', 'ml(1작은술)'], ['통깨', '2', 'g(1/2작은술)']]</x:v>
+      </x:c>
+      <x:c r="J29" s="5" t="str">
+        <x:v>1인분</x:v>
+      </x:c>
+      <x:c r="K29" s="5" t="str">
+        <x:v>초급</x:v>
+      </x:c>
+      <x:c r="L29" s="5" t="str">
+        <x:v>10분이내</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" ht="22" customHeight="1">
+      <x:c r="A30" s="4" t="n">
+        <x:v>1029</x:v>
+      </x:c>
+      <x:c r="B30" s="4" t="str">
+        <x:v>시금치무침</x:v>
+      </x:c>
+      <x:c r="C30" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D30" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E30" s="5" t="str">
+        <x:v>무침</x:v>
+      </x:c>
+      <x:c r="F30" s="5" t="str">
+        <x:v>10분 이하|냄비 하나|도시락 가능|밥반찬</x:v>
+      </x:c>
+      <x:c r="G30" s="5" t="str">
+        <x:v>시금치</x:v>
+      </x:c>
+      <x:c r="H30" s="5" t="str">
+        <x:v>반찬</x:v>
+      </x:c>
+      <x:c r="I30" s="5" t="str">
+        <x:v>[['시금치', '200', 'g'], ['국간장', '5', 'ml(1작은술)'], ['소금', '0.8', 'g'], ['다진 마늘', '2', 'g'], ['참기름', '5', 'ml(1작은술)'], ['통깨', '2', 'g(1/2작은술)']]</x:v>
+      </x:c>
+      <x:c r="J30" s="5" t="str">
+        <x:v>1인분</x:v>
+      </x:c>
+      <x:c r="K30" s="5" t="str">
+        <x:v>초급</x:v>
+      </x:c>
+      <x:c r="L30" s="5" t="str">
+        <x:v>10분이내</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" ht="22" customHeight="1">
+      <x:c r="A31" s="4" t="n">
+        <x:v>1030</x:v>
+      </x:c>
+      <x:c r="B31" s="4" t="str">
+        <x:v>애호박볶음</x:v>
+      </x:c>
+      <x:c r="C31" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D31" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E31" s="5" t="str">
+        <x:v>볶음</x:v>
+      </x:c>
+      <x:c r="F31" s="5" t="str">
+        <x:v>15분 이하|원팬 요리|설거지 적음|도시락 가능|밥반찬</x:v>
+      </x:c>
+      <x:c r="G31" s="5" t="str">
+        <x:v>애호박|양파</x:v>
+      </x:c>
+      <x:c r="H31" s="5" t="str">
+        <x:v>반찬</x:v>
+      </x:c>
+      <x:c r="I31" s="5" t="str">
+        <x:v>[['애호박', '1/2', '개(180g)'], ['양파', '1/4', '개(50g)'], ['대파', '10', 'g'], ['식용유', '10', 'ml(2작은술)'], ['새우젓', '5', 'g(1작은술) 또는 소금 1g'], ['다진 마늘', '2', 'g'], ['물', '15', 'ml'], ['참기름', '2.5', 'ml'], ['통깨', '1', 'g']]</x:v>
+      </x:c>
+      <x:c r="J31" s="5" t="str">
+        <x:v>1인분</x:v>
+      </x:c>
+      <x:c r="K31" s="5" t="str">
+        <x:v>초급</x:v>
+      </x:c>
+      <x:c r="L31" s="5" t="str">
+        <x:v>12분이내</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" ht="22" customHeight="1">
+      <x:c r="A32" s="4" t="n">
+        <x:v>1031</x:v>
+      </x:c>
+      <x:c r="B32" s="4" t="str">
+        <x:v>애호박전</x:v>
+      </x:c>
+      <x:c r="C32" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D32" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E32" s="5" t="str">
+        <x:v>전·부침</x:v>
+      </x:c>
+      <x:c r="F32" s="5" t="str">
+        <x:v>15분 이하|재료 5개 이하|원팬 요리|도시락 가능|밥반찬|남은 재료 활용</x:v>
+      </x:c>
+      <x:c r="G32" s="5" t="str">
+        <x:v>애호박|계란</x:v>
+      </x:c>
+      <x:c r="H32" s="5" t="str">
+        <x:v>반찬</x:v>
+      </x:c>
+      <x:c r="I32" s="5" t="str">
+        <x:v>[['애호박', '1/2', '개(180g)'], ['부침가루', '25', 'g(2큰술)'], ['계란', '1', '개(50g)'], ['소금', '0.8', 'g'], ['식용유', '15', 'ml(1큰술)']]</x:v>
+      </x:c>
+      <x:c r="J32" s="5" t="str">
+        <x:v>1인분</x:v>
+      </x:c>
+      <x:c r="K32" s="5" t="str">
+        <x:v>초급</x:v>
+      </x:c>
+      <x:c r="L32" s="5" t="str">
+        <x:v>15분이내</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" ht="22" customHeight="1">
+      <x:c r="A33" s="4" t="n">
+        <x:v>1032</x:v>
+      </x:c>
+      <x:c r="B33" s="4" t="str">
+        <x:v>양배추 계란볶음</x:v>
+      </x:c>
+      <x:c r="C33" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D33" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E33" s="5" t="str">
+        <x:v>볶음</x:v>
+      </x:c>
+      <x:c r="F33" s="5" t="str">
+        <x:v>15분 이하|원팬 요리|도시락 가능|밥반찬|남은 재료 활용</x:v>
+      </x:c>
+      <x:c r="G33" s="5" t="str">
+        <x:v>양배추|계란</x:v>
+      </x:c>
+      <x:c r="H33" s="5" t="str">
+        <x:v>반찬</x:v>
+      </x:c>
+      <x:c r="I33" s="5" t="str">
+        <x:v>[['양배추', '180', 'g'], ['계란', '2', '개(100g)'], ['대파', '15', 'g'], ['식용유', '10', 'ml(2작은술)'], ['굴소스', '10', 'ml(2작은술)'], ['진간장', '5', 'ml(1작은술)'], ['후추', '0.1', 'g'], ['참기름', '2.5', 'ml(1/2작은술)']]</x:v>
+      </x:c>
+      <x:c r="J33" s="5" t="str">
+        <x:v>1인분</x:v>
+      </x:c>
+      <x:c r="K33" s="5" t="str">
+        <x:v>초급</x:v>
+      </x:c>
+      <x:c r="L33" s="5" t="str">
+        <x:v>12분이내</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" ht="22" customHeight="1">
+      <x:c r="A34" s="4" t="n">
+        <x:v>1033</x:v>
+      </x:c>
+      <x:c r="B34" s="4" t="str">
+        <x:v>양배추볶음</x:v>
+      </x:c>
+      <x:c r="C34" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D34" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E34" s="5" t="str">
+        <x:v>볶음</x:v>
+      </x:c>
+      <x:c r="F34" s="5" t="str">
+        <x:v>15분 이하|원팬 요리|설거지 적음|도시락 가능|밥반찬|남은 재료 활용</x:v>
+      </x:c>
+      <x:c r="G34" s="5" t="str">
+        <x:v>양배추|양파</x:v>
+      </x:c>
+      <x:c r="H34" s="5" t="str">
+        <x:v>반찬</x:v>
+      </x:c>
+      <x:c r="I34" s="5" t="str">
+        <x:v>[['양배추', '250', 'g'], ['양파', '1/4', '개(50g)'], ['대파', '15', 'g'], ['식용유', '10', 'ml(2작은술)'], ['진간장', '10', 'ml(2작은술)'], ['굴소스', '5', 'ml(1작은술)'], ['다진 마늘', '2', 'g'], ['설탕', '1', 'g'], ['후추', '0.1', 'g'], ['참기름', '2.5', 'ml']]</x:v>
+      </x:c>
+      <x:c r="J34" s="5" t="str">
+        <x:v>1인분</x:v>
+      </x:c>
+      <x:c r="K34" s="5" t="str">
+        <x:v>초급</x:v>
+      </x:c>
+      <x:c r="L34" s="5" t="str">
+        <x:v>12분이내</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" ht="22" customHeight="1">
+      <x:c r="A35" s="4" t="n">
+        <x:v>1034</x:v>
+      </x:c>
+      <x:c r="B35" s="4" t="str">
+        <x:v>양배추전</x:v>
+      </x:c>
+      <x:c r="C35" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D35" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E35" s="5" t="str">
+        <x:v>전·부침</x:v>
+      </x:c>
+      <x:c r="F35" s="5" t="str">
+        <x:v>15분 이하|원팬 요리|도시락 가능|밥반찬|남은 재료 활용</x:v>
+      </x:c>
+      <x:c r="G35" s="5" t="str">
+        <x:v>양배추|계란</x:v>
+      </x:c>
+      <x:c r="H35" s="5" t="str">
+        <x:v>반찬</x:v>
+      </x:c>
+      <x:c r="I35" s="5" t="str">
+        <x:v>[['양배추', '180', 'g'], ['계란', '2', '개(100g)'], ['부침가루', '30', 'g(2큰술)'], ['물', '30', 'ml(2큰술)'], ['소금', '0.8', 'g'], ['식용유', '15', 'ml(1큰술)'], ['대파', '10', 'g(선택)']]</x:v>
+      </x:c>
+      <x:c r="J35" s="5" t="str">
+        <x:v>1인분</x:v>
+      </x:c>
+      <x:c r="K35" s="5" t="str">
+        <x:v>초급</x:v>
+      </x:c>
+      <x:c r="L35" s="5" t="str">
+        <x:v>15분이내</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" ht="22" customHeight="1">
+      <x:c r="A36" s="4" t="n">
+        <x:v>1035</x:v>
+      </x:c>
+      <x:c r="B36" s="4" t="str">
+        <x:v>어묵볶음</x:v>
+      </x:c>
+      <x:c r="C36" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D36" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E36" s="5" t="str">
+        <x:v>볶음</x:v>
+      </x:c>
+      <x:c r="F36" s="5" t="str">
+        <x:v>15분 이하|원팬 요리|설거지 적음|도시락 가능|밥반찬|남은 재료 활용</x:v>
+      </x:c>
+      <x:c r="G36" s="5" t="str">
+        <x:v>어묵|양파|당근</x:v>
+      </x:c>
+      <x:c r="H36" s="5" t="str">
+        <x:v>반찬</x:v>
+      </x:c>
+      <x:c r="I36" s="5" t="str">
+        <x:v>[['사각어묵', '3', '장(150g)'], ['양파', '1/4', '개(50g)'], ['당근', '20', 'g'], ['대파', '15', 'g'], ['식용유', '5', 'ml(1작은술)'], ['진간장', '15', 'ml(1큰술)'], ['설탕', '5', 'g(1작은술)'], ['올리고당', '10', 'g(2작은술)'], ['다진 마늘', '2', 'g'], ['물', '30', 'ml'], ['참기름', '2.5', 'ml'], ['통깨', '1', 'g']]</x:v>
+      </x:c>
+      <x:c r="J36" s="5" t="str">
+        <x:v>1인분</x:v>
+      </x:c>
+      <x:c r="K36" s="5" t="str">
+        <x:v>초급</x:v>
+      </x:c>
+      <x:c r="L36" s="5" t="str">
+        <x:v>12분이내</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" ht="22" customHeight="1">
+      <x:c r="A37" s="4" t="n">
+        <x:v>1036</x:v>
+      </x:c>
+      <x:c r="B37" s="4" t="str">
+        <x:v>오이무침</x:v>
+      </x:c>
+      <x:c r="C37" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D37" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E37" s="5" t="str">
+        <x:v>무침</x:v>
+      </x:c>
+      <x:c r="F37" s="5" t="str">
+        <x:v>10분 이하|불 없이 가능|설거지 적음|도시락 가능|밥반찬</x:v>
+      </x:c>
+      <x:c r="G37" s="5" t="str">
+        <x:v>오이|양파</x:v>
+      </x:c>
+      <x:c r="H37" s="5" t="str">
+        <x:v>반찬</x:v>
+      </x:c>
+      <x:c r="I37" s="5" t="str">
+        <x:v>[['오이', '1', '개(200g)'], ['양파', '30', 'g'], ['고춧가루', '4', 'g(2작은술)'], ['진간장', '7.5', 'ml(1/2큰술)'], ['식초', '10', 'ml(2작은술)'], ['설탕', '5', 'g(1작은술)'], ['다진 마늘', '2', 'g'], ['참기름', '2.5', 'ml'], ['소금', '1', 'g'], ['통깨', '1', 'g']]</x:v>
+      </x:c>
+      <x:c r="J37" s="5" t="str">
+        <x:v>1인분</x:v>
+      </x:c>
+      <x:c r="K37" s="5" t="str">
+        <x:v>초급</x:v>
+      </x:c>
+      <x:c r="L37" s="5" t="str">
+        <x:v>10분이내</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" ht="22" customHeight="1">
+      <x:c r="A38" s="4" t="n">
+        <x:v>1037</x:v>
+      </x:c>
+      <x:c r="B38" s="4" t="str">
+        <x:v>오이탕탕이</x:v>
+      </x:c>
+      <x:c r="C38" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D38" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E38" s="5" t="str">
+        <x:v>무침</x:v>
+      </x:c>
+      <x:c r="F38" s="5" t="str">
+        <x:v>10분 이하|불 없이 가능|설거지 적음|도시락 가능|밥반찬</x:v>
+      </x:c>
+      <x:c r="G38" s="5" t="str">
+        <x:v>오이</x:v>
+      </x:c>
+      <x:c r="H38" s="5" t="str">
+        <x:v>반찬</x:v>
+      </x:c>
+      <x:c r="I38" s="5" t="str">
+        <x:v>[['오이', '1', '개(200g)'], ['소금', '1', 'g'], ['진간장', '7.5', 'ml(1/2큰술)'], ['식초', '15', 'ml(1큰술)'], ['설탕', '5', 'g(1작은술)'], ['다진 마늘', '3', 'g'], ['참기름', '5', 'ml(1작은술)'], ['고춧가루', '1', 'g(선택)'], ['통깨', '2', 'g']]</x:v>
+      </x:c>
+      <x:c r="J38" s="5" t="str">
+        <x:v>1인분</x:v>
+      </x:c>
+      <x:c r="K38" s="5" t="str">
+        <x:v>초급</x:v>
+      </x:c>
+      <x:c r="L38" s="5" t="str">
+        <x:v>8분이내</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" ht="22" customHeight="1">
+      <x:c r="A39" s="4" t="n">
+        <x:v>1038</x:v>
+      </x:c>
+      <x:c r="B39" s="4" t="str">
+        <x:v>진미채볶음</x:v>
+      </x:c>
+      <x:c r="C39" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D39" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E39" s="5" t="str">
+        <x:v>볶음</x:v>
+      </x:c>
+      <x:c r="F39" s="5" t="str">
+        <x:v>15분 이하|원팬 요리|칼 없이 가능|설거지 적음|도시락 가능|밥반찬</x:v>
+      </x:c>
+      <x:c r="G39" s="5" t="str">
+        <x:v>진미채</x:v>
+      </x:c>
+      <x:c r="H39" s="5" t="str">
+        <x:v>반찬</x:v>
+      </x:c>
+      <x:c r="I39" s="5" t="str">
+        <x:v>[['진미채', '80', 'g'], ['마요네즈', '10', 'g(2작은술)'], ['고추장', '15', 'g(1큰술)'], ['고춧가루', '2', 'g(1작은술)'], ['진간장', '5', 'ml(1작은술)'], ['설탕', '5', 'g(1작은술)'], ['올리고당', '15', 'g(1큰술)'], ['물', '15', 'ml(1큰술)'], ['참기름', '2.5', 'ml'], ['통깨', '1', 'g']]</x:v>
+      </x:c>
+      <x:c r="J39" s="5" t="str">
+        <x:v>1인분</x:v>
+      </x:c>
+      <x:c r="K39" s="5" t="str">
+        <x:v>초급</x:v>
+      </x:c>
+      <x:c r="L39" s="5" t="str">
+        <x:v>12분이내</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" ht="22" customHeight="1">
+      <x:c r="A40" s="4" t="n">
+        <x:v>1039</x:v>
+      </x:c>
+      <x:c r="B40" s="4" t="str">
+        <x:v>콩나물무침</x:v>
+      </x:c>
+      <x:c r="C40" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D40" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E40" s="5" t="str">
+        <x:v>무침</x:v>
+      </x:c>
+      <x:c r="F40" s="5" t="str">
+        <x:v>10분 이하|냄비 하나|도시락 가능|밥반찬</x:v>
+      </x:c>
+      <x:c r="G40" s="5" t="str">
+        <x:v>콩나물</x:v>
+      </x:c>
+      <x:c r="H40" s="5" t="str">
+        <x:v>반찬</x:v>
+      </x:c>
+      <x:c r="I40" s="5" t="str">
+        <x:v>[['콩나물', '200', 'g'], ['대파', '10', 'g'], ['국간장', '5', 'ml(1작은술)'], ['소금', '0.8', 'g'], ['다진 마늘', '2', 'g'], ['참기름', '5', 'ml(1작은술)'], ['고춧가루', '1', 'g(선택)'], ['통깨', '2', 'g']]</x:v>
+      </x:c>
+      <x:c r="J40" s="5" t="str">
+        <x:v>1인분</x:v>
+      </x:c>
+      <x:c r="K40" s="5" t="str">
+        <x:v>초급</x:v>
+      </x:c>
+      <x:c r="L40" s="5" t="str">
+        <x:v>10분이내</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" ht="22" customHeight="1">
+      <x:c r="A41" s="4" t="n">
+        <x:v>1040</x:v>
+      </x:c>
+      <x:c r="B41" s="4" t="str">
+        <x:v>파전</x:v>
+      </x:c>
+      <x:c r="C41" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D41" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E41" s="5" t="str">
+        <x:v>전·부침</x:v>
+      </x:c>
+      <x:c r="F41" s="5" t="str">
+        <x:v>원팬 요리|도시락 가능|밥반찬|남은 재료 활용</x:v>
+      </x:c>
+      <x:c r="G41" s="5" t="str">
+        <x:v>쪽파|오징어·새우|계란</x:v>
+      </x:c>
+      <x:c r="H41" s="5" t="str">
+        <x:v>반찬</x:v>
+      </x:c>
+      <x:c r="I41" s="5" t="str">
+        <x:v>[['쪽파 또는 실파', '150', 'g'], ['부침가루', '90', 'g'], ['물', '120', 'ml'], ['계란', '1', '개(50g, 선택)'], ['오징어 또는 새우', '80', 'g(선택)'], ['소금', '0.5', 'g'], ['식용유', '20', 'ml(1큰술+1작은술)']]</x:v>
+      </x:c>
+      <x:c r="J41" s="5" t="str">
+        <x:v>1인분</x:v>
+      </x:c>
+      <x:c r="K41" s="5" t="str">
+        <x:v>초급</x:v>
+      </x:c>
+      <x:c r="L41" s="5" t="str">
+        <x:v>20분이내</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" ht="22" customHeight="1">
+      <x:c r="A42" s="4" t="n">
+        <x:v>1041</x:v>
+      </x:c>
+      <x:c r="B42" s="4" t="str">
+        <x:v>팽이버섯전</x:v>
+      </x:c>
+      <x:c r="C42" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D42" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E42" s="5" t="str">
+        <x:v>전·부침</x:v>
+      </x:c>
+      <x:c r="F42" s="5" t="str">
+        <x:v>15분 이하|원팬 요리|도시락 가능|밥반찬|남은 재료 활용</x:v>
+      </x:c>
+      <x:c r="G42" s="5" t="str">
+        <x:v>팽이버섯|계란</x:v>
+      </x:c>
+      <x:c r="H42" s="5" t="str">
+        <x:v>반찬</x:v>
+      </x:c>
+      <x:c r="I42" s="5" t="str">
+        <x:v>[['팽이버섯', '1', '봉(150g)'], ['계란', '2', '개(100g)'], ['부침가루', '20', 'g(1큰술+1작은술)'], ['대파', '10', 'g'], ['소금', '0.8', 'g'], ['식용유', '15', 'ml(1큰술)']]</x:v>
+      </x:c>
+      <x:c r="J42" s="5" t="str">
+        <x:v>1인분</x:v>
+      </x:c>
+      <x:c r="K42" s="5" t="str">
+        <x:v>초급</x:v>
+      </x:c>
+      <x:c r="L42" s="5" t="str">
+        <x:v>15분이내</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" ht="22" customHeight="1">
+      <x:c r="A43" s="4" t="n">
+        <x:v>2001</x:v>
+      </x:c>
+      <x:c r="B43" s="4" t="str">
+        <x:v>간장 계란밥</x:v>
+      </x:c>
+      <x:c r="C43" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D43" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E43" s="5" t="str">
+        <x:v>간편 비빔밥</x:v>
+      </x:c>
+      <x:c r="F43" s="5" t="str">
+        <x:v>10분 이하|원팬 요리|전자레인지|칼 없이 가능|설거지 적음|아침 식사|든든한 한 끼</x:v>
+      </x:c>
+      <x:c r="G43" s="5" t="str">
+        <x:v>밥|계란</x:v>
+      </x:c>
+      <x:c r="H43" s="5" t="str">
+        <x:v>밥</x:v>
+      </x:c>
+      <x:c r="I43" s="5" t="str">
+        <x:v>[['따뜻한 밥', '200', 'g'], ['계란', '1', '개(50g)'], ['식용유', '5', 'ml(1작은술)'], ['진간장', '7.5', 'ml(1/2큰술)'], ['참기름', '5', 'ml(1작은술)'], ['김가루', '3', 'g'], ['통깨', '1', 'g']]</x:v>
+      </x:c>
+      <x:c r="J43" s="5" t="str">
+        <x:v>1인분</x:v>
+      </x:c>
+      <x:c r="K43" s="5" t="str">
+        <x:v>초급</x:v>
+      </x:c>
+      <x:c r="L43" s="5" t="str">
+        <x:v>7분이내</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44" ht="22" customHeight="1">
+      <x:c r="A44" s="4" t="n">
+        <x:v>2002</x:v>
+      </x:c>
+      <x:c r="B44" s="4" t="str">
+        <x:v>김치주먹밥</x:v>
+      </x:c>
+      <x:c r="C44" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D44" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E44" s="5" t="str">
+        <x:v>주먹밥</x:v>
+      </x:c>
+      <x:c r="F44" s="5" t="str">
+        <x:v>15분 이하|원팬 요리|도시락 가능|든든한 한 끼|남은 재료 활용</x:v>
+      </x:c>
+      <x:c r="G44" s="5" t="str">
+        <x:v>밥|김치|참치</x:v>
+      </x:c>
+      <x:c r="H44" s="5" t="str">
+        <x:v>밥</x:v>
+      </x:c>
+      <x:c r="I44" s="5" t="str">
+        <x:v>[['밥', '200', 'g'], ['배추김치', '70', 'g'], ['참치 통조림', '50', 'g'], ['김가루', '5', 'g'], ['참기름', '5', 'ml(1작은술)'], ['설탕', '2', 'g(1/2작은술)'], ['식용유', '5', 'ml(1작은술)'], ['통깨', '1', 'g']]</x:v>
+      </x:c>
+      <x:c r="J44" s="5" t="str">
+        <x:v>1인분</x:v>
+      </x:c>
+      <x:c r="K44" s="5" t="str">
+        <x:v>초급</x:v>
+      </x:c>
+      <x:c r="L44" s="5" t="str">
+        <x:v>12분이내</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45" ht="22" customHeight="1">
+      <x:c r="A45" s="4" t="n">
+        <x:v>2003</x:v>
+      </x:c>
+      <x:c r="B45" s="4" t="str">
+        <x:v>비빔밥</x:v>
+      </x:c>
+      <x:c r="C45" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D45" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E45" s="5" t="str">
+        <x:v>비빔밥</x:v>
+      </x:c>
+      <x:c r="F45" s="5" t="str">
+        <x:v>도시락 가능|든든한 한 끼</x:v>
+      </x:c>
+      <x:c r="G45" s="5" t="str">
+        <x:v>밥|콩나물|시금치</x:v>
+      </x:c>
+      <x:c r="H45" s="5" t="str">
+        <x:v>밥</x:v>
+      </x:c>
+      <x:c r="I45" s="5" t="str">
+        <x:v>[['밥', '200', 'g'], ['콩나물', '70', 'g'], ['시금치', '60', 'g'], ['당근', '40', 'g'], ['애호박', '60', 'g'], ['계란', '1', '개(50g)'], ['식용유', '10', 'ml(2작은술)'], ['소금', '1.5', 'g'], ['참기름', '7.5', 'ml(1/2큰술)'], ['고추장', '20', 'g(1큰술+1작은술)'], ['설탕', '3', 'g'], ['통깨', '2', 'g']]</x:v>
+      </x:c>
+      <x:c r="J45" s="5" t="str">
+        <x:v>1인분</x:v>
+      </x:c>
+      <x:c r="K45" s="5" t="str">
+        <x:v>중급</x:v>
+      </x:c>
+      <x:c r="L45" s="5" t="str">
+        <x:v>30분이내</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46" ht="22" customHeight="1">
+      <x:c r="A46" s="4" t="n">
+        <x:v>2004</x:v>
+      </x:c>
+      <x:c r="B46" s="4" t="str">
+        <x:v>스팸 주먹밥</x:v>
+      </x:c>
+      <x:c r="C46" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D46" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E46" s="5" t="str">
+        <x:v>주먹밥</x:v>
+      </x:c>
+      <x:c r="F46" s="5" t="str">
+        <x:v>10분 이하|원팬 요리|도시락 가능|든든한 한 끼|남은 재료 활용</x:v>
+      </x:c>
+      <x:c r="G46" s="5" t="str">
+        <x:v>밥|스팸</x:v>
+      </x:c>
+      <x:c r="H46" s="5" t="str">
+        <x:v>밥</x:v>
+      </x:c>
+      <x:c r="I46" s="5" t="str">
+        <x:v>[['밥', '200', 'g'], ['스팸', '70', 'g'], ['김가루', '5', 'g'], ['참기름', '5', 'ml(1작은술)'], ['마요네즈', '10', 'g(2작은술, 선택)'], ['통깨', '1', 'g'], ['식용유', '2.5', 'ml(1/2작은술)']]</x:v>
+      </x:c>
+      <x:c r="J46" s="5" t="str">
+        <x:v>1인분</x:v>
+      </x:c>
+      <x:c r="K46" s="5" t="str">
+        <x:v>초급</x:v>
+      </x:c>
+      <x:c r="L46" s="5" t="str">
+        <x:v>10분이내</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47" ht="22" customHeight="1">
+      <x:c r="A47" s="4" t="n">
+        <x:v>2005</x:v>
+      </x:c>
+      <x:c r="B47" s="4" t="str">
+        <x:v>오므라이스</x:v>
+      </x:c>
+      <x:c r="C47" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D47" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E47" s="5" t="str">
+        <x:v>오므라이스</x:v>
+      </x:c>
+      <x:c r="F47" s="5" t="str">
+        <x:v>원팬 요리|도시락 가능|든든한 한 끼</x:v>
+      </x:c>
+      <x:c r="G47" s="5" t="str">
+        <x:v>밥|계란|햄·소시지</x:v>
+      </x:c>
+      <x:c r="H47" s="5" t="str">
+        <x:v>밥</x:v>
+      </x:c>
+      <x:c r="I47" s="5" t="str">
+        <x:v>[['밥', '200', 'g'], ['계란', '2', '개(100g)'], ['햄 또는 소시지', '60', 'g'], ['양파', '40', 'g'], ['당근', '25', 'g'], ['식용유', '15', 'ml(1큰술)'], ['케첩', '30', 'g(2큰술)'], ['진간장', '5', 'ml(1작은술)'], ['소금', '0.8', 'g'], ['후추', '0.1', 'g'], ['우유', '15', 'ml(1큰술, 선택)']]</x:v>
+      </x:c>
+      <x:c r="J47" s="5" t="str">
+        <x:v>1인분</x:v>
+      </x:c>
+      <x:c r="K47" s="5" t="str">
+        <x:v>중급</x:v>
+      </x:c>
+      <x:c r="L47" s="5" t="str">
+        <x:v>22분이내</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48" ht="22" customHeight="1">
+      <x:c r="A48" s="4" t="n">
+        <x:v>2006</x:v>
+      </x:c>
+      <x:c r="B48" s="4" t="str">
+        <x:v>유부초밥</x:v>
+      </x:c>
+      <x:c r="C48" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D48" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E48" s="5" t="str">
+        <x:v>유부초밥</x:v>
+      </x:c>
+      <x:c r="F48" s="5" t="str">
+        <x:v>15분 이하|불 없이 가능|도시락 가능|아침 식사|든든한 한 끼</x:v>
+      </x:c>
+      <x:c r="G48" s="5" t="str">
+        <x:v>밥|유부|당근</x:v>
+      </x:c>
+      <x:c r="H48" s="5" t="str">
+        <x:v>밥</x:v>
+      </x:c>
+      <x:c r="I48" s="5" t="str">
+        <x:v>[['밥', '200', 'g'], ['시판 조미유부', '8', '장(약 120g)'], ['동봉 초밥소스', '20', 'ml 또는 식초 15ml+설탕 8g+소금 0.8g'], ['당근', '20', 'g'], ['오이', '30', 'g'], ['통깨', '2', 'g']]</x:v>
+      </x:c>
+      <x:c r="J48" s="5" t="str">
+        <x:v>1인분</x:v>
+      </x:c>
+      <x:c r="K48" s="5" t="str">
+        <x:v>초급</x:v>
+      </x:c>
+      <x:c r="L48" s="5" t="str">
+        <x:v>15분이내</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49" ht="22" customHeight="1">
+      <x:c r="A49" s="4" t="n">
+        <x:v>2007</x:v>
+      </x:c>
+      <x:c r="B49" s="4" t="str">
+        <x:v>짜장밥</x:v>
+      </x:c>
+      <x:c r="C49" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D49" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E49" s="5" t="str">
+        <x:v>소스밥</x:v>
+      </x:c>
+      <x:c r="F49" s="5" t="str">
+        <x:v>도시락 가능|냉동 가능|든든한 한 끼</x:v>
+      </x:c>
+      <x:c r="G49" s="5" t="str">
+        <x:v>밥|돼지고기|양파</x:v>
+      </x:c>
+      <x:c r="H49" s="5" t="str">
+        <x:v>밥</x:v>
+      </x:c>
+      <x:c r="I49" s="5" t="str">
+        <x:v>[['밥', '200', 'g'], ['돼지고기 앞다리살', '100', 'g'], ['양파', '1/2', '개(100g)'], ['감자', '80', 'g'], ['당근', '30', 'g'], ['애호박', '60', 'g'], ['식용유', '10', 'ml'], ['춘장', '25', 'g 또는 짜장분말 25g'], ['설탕', '5', 'g(춘장 사용 시)'], ['물', '300', 'ml'], ['전분', '8', 'g(춘장 사용 시)'], ['전분물용 물', '20', 'ml']]</x:v>
+      </x:c>
+      <x:c r="J49" s="5" t="str">
+        <x:v>1인분</x:v>
+      </x:c>
+      <x:c r="K49" s="5" t="str">
+        <x:v>중급</x:v>
+      </x:c>
+      <x:c r="L49" s="5" t="str">
+        <x:v>30분이내</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50" ht="22" customHeight="1">
+      <x:c r="A50" s="4" t="n">
+        <x:v>2008</x:v>
+      </x:c>
+      <x:c r="B50" s="4" t="str">
+        <x:v>참치 비빔밥</x:v>
+      </x:c>
+      <x:c r="C50" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D50" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E50" s="5" t="str">
+        <x:v>비빔밥</x:v>
+      </x:c>
+      <x:c r="F50" s="5" t="str">
+        <x:v>15분 이하|불 없이 가능|도시락 가능|든든한 한 끼</x:v>
+      </x:c>
+      <x:c r="G50" s="5" t="str">
+        <x:v>밥|참치|상추</x:v>
+      </x:c>
+      <x:c r="H50" s="5" t="str">
+        <x:v>밥</x:v>
+      </x:c>
+      <x:c r="I50" s="5" t="str">
+        <x:v>[['밥', '200', 'g'], ['참치 통조림', '80', 'g'], ['상추', '50', 'g'], ['오이', '50', 'g'], ['당근', '30', 'g'], ['김가루', '3', 'g'], ['고추장', '20', 'g'], ['식초', '10', 'ml(2작은술)'], ['설탕', '5', 'g(1작은술)'], ['참기름', '5', 'ml(1작은술)'], ['통깨', '1', 'g'], ['계란', '1', '개(선택)']]</x:v>
+      </x:c>
+      <x:c r="J50" s="5" t="str">
+        <x:v>1인분</x:v>
+      </x:c>
+      <x:c r="K50" s="5" t="str">
+        <x:v>초급</x:v>
+      </x:c>
+      <x:c r="L50" s="5" t="str">
+        <x:v>12분이내</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51" ht="22" customHeight="1">
+      <x:c r="A51" s="4" t="n">
+        <x:v>2009</x:v>
+      </x:c>
+      <x:c r="B51" s="4" t="str">
+        <x:v>참치마요 주먹밥</x:v>
+      </x:c>
+      <x:c r="C51" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D51" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E51" s="5" t="str">
+        <x:v>주먹밥</x:v>
+      </x:c>
+      <x:c r="F51" s="5" t="str">
+        <x:v>10분 이하|불 없이 가능|도시락 가능|든든한 한 끼|남은 재료 활용</x:v>
+      </x:c>
+      <x:c r="G51" s="5" t="str">
+        <x:v>밥|참치|단무지</x:v>
+      </x:c>
+      <x:c r="H51" s="5" t="str">
+        <x:v>밥</x:v>
+      </x:c>
+      <x:c r="I51" s="5" t="str">
+        <x:v>[['밥', '200', 'g'], ['참치 통조림', '70', 'g'], ['마요네즈', '15', 'g(1큰술)'], ['김가루', '5', 'g'], ['단무지', '20', 'g'], ['참기름', '2.5', 'ml(1/2작은술)'], ['통깨', '1', 'g']]</x:v>
+      </x:c>
+      <x:c r="J51" s="5" t="str">
+        <x:v>1인분</x:v>
+      </x:c>
+      <x:c r="K51" s="5" t="str">
+        <x:v>초급</x:v>
+      </x:c>
+      <x:c r="L51" s="5" t="str">
+        <x:v>10분이내</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="52" ht="22" customHeight="1">
+      <x:c r="A52" s="4" t="n">
+        <x:v>2010</x:v>
+      </x:c>
+      <x:c r="B52" s="4" t="str">
+        <x:v>카레라이스</x:v>
+      </x:c>
+      <x:c r="C52" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D52" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E52" s="5" t="str">
+        <x:v>소스밥</x:v>
+      </x:c>
+      <x:c r="F52" s="5" t="str">
+        <x:v>냄비 하나|도시락 가능|냉동 가능|든든한 한 끼</x:v>
+      </x:c>
+      <x:c r="G52" s="5" t="str">
+        <x:v>밥|돼지고기·닭고기|감자</x:v>
+      </x:c>
+      <x:c r="H52" s="5" t="str">
+        <x:v>밥</x:v>
+      </x:c>
+      <x:c r="I52" s="5" t="str">
+        <x:v>[['밥', '200', 'g'], ['돼지고기 또는 닭고기', '100', 'g'], ['감자', '100', 'g'], ['양파', '100', 'g'], ['당근', '40', 'g'], ['식용유', '10', 'ml'], ['물', '400', 'ml'], ['고형카레', '2', '조각 또는 카레가루 40g(제품 1인분 표시량)']]</x:v>
+      </x:c>
+      <x:c r="J52" s="5" t="str">
+        <x:v>1인분</x:v>
+      </x:c>
+      <x:c r="K52" s="5" t="str">
+        <x:v>초급</x:v>
+      </x:c>
+      <x:c r="L52" s="5" t="str">
+        <x:v>30분이내</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53" ht="22" customHeight="1">
+      <x:c r="A53" s="4" t="n">
+        <x:v>2011</x:v>
+      </x:c>
+      <x:c r="B53" s="4" t="str">
+        <x:v>콩나물밥</x:v>
+      </x:c>
+      <x:c r="C53" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D53" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E53" s="5" t="str">
+        <x:v>나물밥</x:v>
+      </x:c>
+      <x:c r="F53" s="5" t="str">
+        <x:v>전기밥솥|칼 없이 가능|불 없이 가능|도시락 가능|든든한 한 끼</x:v>
+      </x:c>
+      <x:c r="G53" s="5" t="str">
+        <x:v>쌀|콩나물|돼지고기</x:v>
+      </x:c>
+      <x:c r="H53" s="5" t="str">
+        <x:v>밥</x:v>
+      </x:c>
+      <x:c r="I53" s="5" t="str">
+        <x:v>[['쌀', '90', 'g(종이컵 약 1/2컵) 또는 불린 쌀 110g'], ['콩나물', '150', 'g'], ['돼지고기 다짐육', '60', 'g(선택)'], ['물', '110', 'ml'], ['진간장', '15', 'ml(1큰술)'], ['대파', '15', 'g'], ['고춧가루', '1', 'g'], ['참기름', '5', 'ml'], ['식초', '5', 'ml'], ['설탕', '2', 'g'], ['통깨', '1', 'g']]</x:v>
+      </x:c>
+      <x:c r="J53" s="5" t="str">
+        <x:v>1인분</x:v>
+      </x:c>
+      <x:c r="K53" s="5" t="str">
+        <x:v>초급</x:v>
+      </x:c>
+      <x:c r="L53" s="5" t="str">
+        <x:v>35분이내</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="54" ht="22" customHeight="1">
+      <x:c r="A54" s="4" t="n">
+        <x:v>2012</x:v>
+      </x:c>
+      <x:c r="B54" s="4" t="str">
+        <x:v>하이라이스</x:v>
+      </x:c>
+      <x:c r="C54" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D54" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E54" s="5" t="str">
+        <x:v>소스밥</x:v>
+      </x:c>
+      <x:c r="F54" s="5" t="str">
+        <x:v>도시락 가능|냉동 가능|든든한 한 끼</x:v>
+      </x:c>
+      <x:c r="G54" s="5" t="str">
+        <x:v>밥|소고기|양파</x:v>
+      </x:c>
+      <x:c r="H54" s="5" t="str">
+        <x:v>밥</x:v>
+      </x:c>
+      <x:c r="I54" s="5" t="str">
+        <x:v>[['밥', '200', 'g'], ['소고기 불고기용', '100', 'g'], ['양파', '1/2', '개(100g)'], ['양송이 또는 새송이버섯', '80', 'g'], ['식용유', '10', 'ml'], ['물', '350', 'ml'], ['하이라이스 고형루', '2', '조각 또는 분말 40g(제품 1인분 표시량)'], ['케첩', '10', 'g(선택)']]</x:v>
+      </x:c>
+      <x:c r="J54" s="5" t="str">
+        <x:v>1인분</x:v>
+      </x:c>
+      <x:c r="K54" s="5" t="str">
+        <x:v>초급</x:v>
+      </x:c>
+      <x:c r="L54" s="5" t="str">
+        <x:v>25분이내</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55" ht="22" customHeight="1">
+      <x:c r="A55" s="4" t="n">
+        <x:v>3001</x:v>
+      </x:c>
+      <x:c r="B55" s="4" t="str">
+        <x:v>데리야키 치킨덮밥</x:v>
+      </x:c>
+      <x:c r="C55" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D55" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E55" s="5" t="str">
+        <x:v>덮밥</x:v>
+      </x:c>
+      <x:c r="F55" s="5" t="str">
+        <x:v>원팬 요리|도시락 가능|든든한 한 끼|남은 재료 활용</x:v>
+      </x:c>
+      <x:c r="G55" s="5" t="str">
+        <x:v>밥|닭다리살|양파</x:v>
+      </x:c>
+      <x:c r="H55" s="5" t="str">
+        <x:v>덮밥</x:v>
+      </x:c>
+      <x:c r="I55" s="5" t="str">
+        <x:v>[['밥', '200', 'g'], ['닭다리살', '180', 'g'], ['양파', '1/4', '개(50g)'], ['대파', '10', 'g'], ['식용유', '5', 'ml(1작은술)'], ['진간장', '20', 'ml(1큰술+1작은술)'], ['설탕', '8', 'g(2작은술)'], ['맛술', '15', 'ml(1큰술)'], ['물', '30', 'ml(2큰술)'], ['다진 마늘', '3', 'g'], ['후추', '0.1', 'g'], ['김가루', '2', 'g(선택)']]</x:v>
+      </x:c>
+      <x:c r="J55" s="5" t="str">
+        <x:v>1인분</x:v>
+      </x:c>
+      <x:c r="K55" s="5" t="str">
+        <x:v>초급</x:v>
+      </x:c>
+      <x:c r="L55" s="5" t="str">
+        <x:v>22분이내</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="56" ht="22" customHeight="1">
+      <x:c r="A56" s="4" t="n">
+        <x:v>3002</x:v>
+      </x:c>
+      <x:c r="B56" s="4" t="str">
+        <x:v>돈까스덮밥</x:v>
+      </x:c>
+      <x:c r="C56" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D56" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E56" s="5" t="str">
+        <x:v>덮밥</x:v>
+      </x:c>
+      <x:c r="F56" s="5" t="str">
+        <x:v>에어프라이어|도시락 가능|든든한 한 끼|남은 재료 활용</x:v>
+      </x:c>
+      <x:c r="G56" s="5" t="str">
+        <x:v>밥|돈까스|계란</x:v>
+      </x:c>
+      <x:c r="H56" s="5" t="str">
+        <x:v>덮밥</x:v>
+      </x:c>
+      <x:c r="I56" s="5" t="str">
+        <x:v>[['밥', '200', 'g'], ['냉동 또는 조리된 돈까스', '1', '장(120g)'], ['양파', '1/4', '개(50g)'], ['계란', '1', '개(50g)'], ['물', '120', 'ml'], ['진간장', '15', 'ml(1큰술)'], ['설탕', '5', 'g(1작은술)'], ['맛술', '10', 'ml(2작은술)'], ['대파', '8', 'g']]</x:v>
+      </x:c>
+      <x:c r="J56" s="5" t="str">
+        <x:v>1인분</x:v>
+      </x:c>
+      <x:c r="K56" s="5" t="str">
+        <x:v>초급</x:v>
+      </x:c>
+      <x:c r="L56" s="5" t="str">
+        <x:v>20분이내</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="57" ht="22" customHeight="1">
+      <x:c r="A57" s="4" t="n">
+        <x:v>3003</x:v>
+      </x:c>
+      <x:c r="B57" s="4" t="str">
+        <x:v>두부덮밥</x:v>
+      </x:c>
+      <x:c r="C57" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D57" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E57" s="5" t="str">
+        <x:v>덮밥</x:v>
+      </x:c>
+      <x:c r="F57" s="5" t="str">
+        <x:v>원팬 요리|도시락 가능|든든한 한 끼|남은 재료 활용</x:v>
+      </x:c>
+      <x:c r="G57" s="5" t="str">
+        <x:v>밥|두부|양파</x:v>
+      </x:c>
+      <x:c r="H57" s="5" t="str">
+        <x:v>덮밥</x:v>
+      </x:c>
+      <x:c r="I57" s="5" t="str">
+        <x:v>[['밥', '200', 'g'], ['부침용 두부', '200', 'g'], ['양파', '1/4', '개(50g)'], ['대파', '15', 'g'], ['식용유', '10', 'ml(2작은술)'], ['진간장', '15', 'ml(1큰술)'], ['굴소스', '5', 'ml(1작은술)'], ['설탕', '3', 'g(3/4작은술)'], ['물', '80', 'ml'], ['다진 마늘', '2', 'g'], ['참기름', '2.5', 'ml(1/2작은술)'], ['통깨', '1', 'g']]</x:v>
+      </x:c>
+      <x:c r="J57" s="5" t="str">
+        <x:v>1인분</x:v>
+      </x:c>
+      <x:c r="K57" s="5" t="str">
+        <x:v>초급</x:v>
+      </x:c>
+      <x:c r="L57" s="5" t="str">
+        <x:v>18분이내</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="58" ht="22" customHeight="1">
+      <x:c r="A58" s="4" t="n">
+        <x:v>3004</x:v>
+      </x:c>
+      <x:c r="B58" s="4" t="str">
+        <x:v>마파두부 덮밥</x:v>
+      </x:c>
+      <x:c r="C58" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D58" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E58" s="5" t="str">
+        <x:v>덮밥</x:v>
+      </x:c>
+      <x:c r="F58" s="5" t="str">
+        <x:v>원팬 요리|도시락 가능|든든한 한 끼|남은 재료 활용</x:v>
+      </x:c>
+      <x:c r="G58" s="5" t="str">
+        <x:v>밥|두부|돼지고기</x:v>
+      </x:c>
+      <x:c r="H58" s="5" t="str">
+        <x:v>덮밥</x:v>
+      </x:c>
+      <x:c r="I58" s="5" t="str">
+        <x:v>[['밥', '200', 'g'], ['부침용 두부', '200', 'g'], ['다진 돼지고기', '80', 'g'], ['대파', '20', 'g'], ['식용유', '10', 'ml(2작은술)'], ['고추장', '10', 'g(2작은술)'], ['된장', '5', 'g(1작은술)'], ['진간장', '10', 'ml(2작은술)'], ['고춧가루', '2', 'g(1작은술)'], ['설탕', '3', 'g'], ['다진 마늘', '3', 'g'], ['물', '180', 'ml'], ['전분', '8', 'g(2작은술)'], ['전분물용 물', '20', 'ml'], ['참기름', '2.5', 'ml']]</x:v>
+      </x:c>
+      <x:c r="J58" s="5" t="str">
+        <x:v>1인분</x:v>
+      </x:c>
+      <x:c r="K58" s="5" t="str">
+        <x:v>중급</x:v>
+      </x:c>
+      <x:c r="L58" s="5" t="str">
+        <x:v>22분이내</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="59" ht="22" customHeight="1">
+      <x:c r="A59" s="4" t="n">
+        <x:v>3005</x:v>
+      </x:c>
+      <x:c r="B59" s="4" t="str">
+        <x:v>불고기덮밥</x:v>
+      </x:c>
+      <x:c r="C59" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D59" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E59" s="5" t="str">
+        <x:v>덮밥</x:v>
+      </x:c>
+      <x:c r="F59" s="5" t="str">
+        <x:v>원팬 요리|도시락 가능|든든한 한 끼|남은 재료 활용</x:v>
+      </x:c>
+      <x:c r="G59" s="5" t="str">
+        <x:v>밥|소고기|양파</x:v>
+      </x:c>
+      <x:c r="H59" s="5" t="str">
+        <x:v>덮밥</x:v>
+      </x:c>
+      <x:c r="I59" s="5" t="str">
+        <x:v>[['밥', '200', 'g'], ['소고기 불고기용', '150', 'g'], ['양파', '1/4', '개(50g)'], ['당근', '20', 'g'], ['대파', '15', 'g'], ['식용유', '5', 'ml(1작은술)'], ['진간장', '20', 'ml(1큰술+1작은술)'], ['설탕', '8', 'g(2작은술)'], ['맛술', '10', 'ml(2작은술)'], ['다진 마늘', '3', 'g'], ['참기름', '5', 'ml(1작은술)'], ['후추', '0.1', 'g'], ['물', '50', 'ml']]</x:v>
+      </x:c>
+      <x:c r="J59" s="5" t="str">
+        <x:v>1인분</x:v>
+      </x:c>
+      <x:c r="K59" s="5" t="str">
+        <x:v>초급</x:v>
+      </x:c>
+      <x:c r="L59" s="5" t="str">
+        <x:v>20분이내</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="60" ht="22" customHeight="1">
+      <x:c r="A60" s="4" t="n">
+        <x:v>3006</x:v>
+      </x:c>
+      <x:c r="B60" s="4" t="str">
+        <x:v>스팸마요 덮밥</x:v>
+      </x:c>
+      <x:c r="C60" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D60" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E60" s="5" t="str">
+        <x:v>덮밥</x:v>
+      </x:c>
+      <x:c r="F60" s="5" t="str">
+        <x:v>15분 이하|원팬 요리|도시락 가능|든든한 한 끼|남은 재료 활용</x:v>
+      </x:c>
+      <x:c r="G60" s="5" t="str">
+        <x:v>밥|스팸|계란</x:v>
+      </x:c>
+      <x:c r="H60" s="5" t="str">
+        <x:v>덮밥</x:v>
+      </x:c>
+      <x:c r="I60" s="5" t="str">
+        <x:v>[['밥', '200', 'g'], ['스팸', '80', 'g'], ['계란', '1', '개(50g)'], ['양파', '1/4', '개(50g)'], ['식용유', '5', 'ml(1작은술)'], ['진간장', '10', 'ml(2작은술)'], ['설탕', '5', 'g(1작은술)'], ['물', '30', 'ml'], ['마요네즈', '20', 'g(1큰술+1작은술)'], ['김가루', '3', 'g'], ['대파', '8', 'g']]</x:v>
+      </x:c>
+      <x:c r="J60" s="5" t="str">
+        <x:v>1인분</x:v>
+      </x:c>
+      <x:c r="K60" s="5" t="str">
+        <x:v>초급</x:v>
+      </x:c>
+      <x:c r="L60" s="5" t="str">
+        <x:v>15분이내</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="61" ht="22" customHeight="1">
+      <x:c r="A61" s="4" t="n">
+        <x:v>3007</x:v>
+      </x:c>
+      <x:c r="B61" s="4" t="str">
+        <x:v>양배추덮밥</x:v>
+      </x:c>
+      <x:c r="C61" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D61" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E61" s="5" t="str">
+        <x:v>덮밥</x:v>
+      </x:c>
+      <x:c r="F61" s="5" t="str">
+        <x:v>원팬 요리|도시락 가능|든든한 한 끼|남은 재료 활용</x:v>
+      </x:c>
+      <x:c r="G61" s="5" t="str">
+        <x:v>밥|양배추|돼지고기</x:v>
+      </x:c>
+      <x:c r="H61" s="5" t="str">
+        <x:v>덮밥</x:v>
+      </x:c>
+      <x:c r="I61" s="5" t="str">
+        <x:v>[['밥', '200', 'g'], ['양배추', '180', 'g'], ['돼지고기 다짐육 또는 얇은 고기', '80', 'g'], ['양파', '30', 'g'], ['대파', '15', 'g'], ['식용유', '10', 'ml'], ['굴소스', '10', 'ml'], ['진간장', '10', 'ml'], ['설탕', '3', 'g'], ['다진 마늘', '2', 'g'], ['물', '80', 'ml'], ['전분', '5', 'g'], ['전분물용 물', '15', 'ml'], ['후추', '0.1', 'g']]</x:v>
+      </x:c>
+      <x:c r="J61" s="5" t="str">
+        <x:v>1인분</x:v>
+      </x:c>
+      <x:c r="K61" s="5" t="str">
+        <x:v>초급</x:v>
+      </x:c>
+      <x:c r="L61" s="5" t="str">
+        <x:v>18분이내</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="62" ht="22" customHeight="1">
+      <x:c r="A62" s="4" t="n">
+        <x:v>3008</x:v>
+      </x:c>
+      <x:c r="B62" s="4" t="str">
+        <x:v>오징어 덮밥</x:v>
+      </x:c>
+      <x:c r="C62" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D62" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E62" s="5" t="str">
+        <x:v>덮밥</x:v>
+      </x:c>
+      <x:c r="F62" s="5" t="str">
+        <x:v>원팬 요리|도시락 가능|든든한 한 끼|남은 재료 활용</x:v>
+      </x:c>
+      <x:c r="G62" s="5" t="str">
+        <x:v>밥|오징어|양파</x:v>
+      </x:c>
+      <x:c r="H62" s="5" t="str">
+        <x:v>덮밥</x:v>
+      </x:c>
+      <x:c r="I62" s="5" t="str">
+        <x:v>[['밥', '200', 'g'], ['손질 오징어', '180', 'g'], ['양파', '1/4', '개(50g)'], ['양배추', '80', 'g'], ['당근', '25', 'g'], ['대파', '20', 'g'], ['식용유', '10', 'ml(2작은술)'], ['고추장', '20', 'g'], ['고춧가루', '4', 'g'], ['진간장', '10', 'ml'], ['설탕', '8', 'g'], ['맛술', '10', 'ml'], ['다진 마늘', '5', 'g'], ['물', '30', 'ml'], ['참기름', '2.5', 'ml']]</x:v>
+      </x:c>
+      <x:c r="J62" s="5" t="str">
+        <x:v>1인분</x:v>
+      </x:c>
+      <x:c r="K62" s="5" t="str">
+        <x:v>초급</x:v>
+      </x:c>
+      <x:c r="L62" s="5" t="str">
+        <x:v>20분이내</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="63" ht="22" customHeight="1">
+      <x:c r="A63" s="4" t="n">
+        <x:v>3009</x:v>
+      </x:c>
+      <x:c r="B63" s="4" t="str">
+        <x:v>제육덮밥</x:v>
+      </x:c>
+      <x:c r="C63" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D63" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E63" s="5" t="str">
+        <x:v>덮밥</x:v>
+      </x:c>
+      <x:c r="F63" s="5" t="str">
+        <x:v>원팬 요리|도시락 가능|든든한 한 끼|남은 재료 활용</x:v>
+      </x:c>
+      <x:c r="G63" s="5" t="str">
+        <x:v>밥|돼지고기|양파</x:v>
+      </x:c>
+      <x:c r="H63" s="5" t="str">
+        <x:v>덮밥</x:v>
+      </x:c>
+      <x:c r="I63" s="5" t="str">
+        <x:v>[['밥', '200', 'g'], ['돼지고기 앞다리살', '170', 'g'], ['양파', '1/4', '개(50g)'], ['양배추', '80', 'g'], ['대파', '20', 'g'], ['식용유', '10', 'ml'], ['고추장', '20', 'g'], ['고춧가루', '4', 'g'], ['진간장', '12.5', 'ml'], ['설탕', '8', 'g'], ['맛술', '15', 'ml'], ['다진 마늘', '5', 'g'], ['참기름', '2.5', 'ml']]</x:v>
+      </x:c>
+      <x:c r="J63" s="5" t="str">
+        <x:v>1인분</x:v>
+      </x:c>
+      <x:c r="K63" s="5" t="str">
+        <x:v>초급</x:v>
+      </x:c>
+      <x:c r="L63" s="5" t="str">
+        <x:v>20분이내</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="64" ht="22" customHeight="1">
+      <x:c r="A64" s="4" t="n">
+        <x:v>3010</x:v>
+      </x:c>
+      <x:c r="B64" s="4" t="str">
+        <x:v>참치마요 덮밥</x:v>
+      </x:c>
+      <x:c r="C64" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D64" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E64" s="5" t="str">
+        <x:v>덮밥</x:v>
+      </x:c>
+      <x:c r="F64" s="5" t="str">
+        <x:v>15분 이하|원팬 요리|도시락 가능|든든한 한 끼|남은 재료 활용</x:v>
+      </x:c>
+      <x:c r="G64" s="5" t="str">
+        <x:v>밥|참치|계란</x:v>
+      </x:c>
+      <x:c r="H64" s="5" t="str">
+        <x:v>덮밥</x:v>
+      </x:c>
+      <x:c r="I64" s="5" t="str">
+        <x:v>[['밥', '200', 'g'], ['참치 통조림', '80', 'g'], ['마요네즈', '20', 'g(1큰술+1작은술)'], ['계란', '1', '개(50g)'], ['양파', '20', 'g'], ['진간장', '7.5', 'ml(1/2큰술)'], ['설탕', '3', 'g'], ['물', '20', 'ml'], ['김가루', '3', 'g'], ['대파', '8', 'g'], ['식용유', '5', 'ml']]</x:v>
+      </x:c>
+      <x:c r="J64" s="5" t="str">
+        <x:v>1인분</x:v>
+      </x:c>
+      <x:c r="K64" s="5" t="str">
+        <x:v>초급</x:v>
+      </x:c>
+      <x:c r="L64" s="5" t="str">
+        <x:v>12분이내</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="65" ht="22" customHeight="1">
+      <x:c r="A65" s="4" t="n">
+        <x:v>3011</x:v>
+      </x:c>
+      <x:c r="B65" s="4" t="str">
+        <x:v>치킨마요 덮밥</x:v>
+      </x:c>
+      <x:c r="C65" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D65" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E65" s="5" t="str">
+        <x:v>덮밥</x:v>
+      </x:c>
+      <x:c r="F65" s="5" t="str">
+        <x:v>원팬 요리|에어프라이어|도시락 가능|든든한 한 끼|남은 재료 활용</x:v>
+      </x:c>
+      <x:c r="G65" s="5" t="str">
+        <x:v>밥|치킨|계란</x:v>
+      </x:c>
+      <x:c r="H65" s="5" t="str">
+        <x:v>덮밥</x:v>
+      </x:c>
+      <x:c r="I65" s="5" t="str">
+        <x:v>[['밥', '200', 'g'], ['순살 치킨 또는 치킨너겟', '120', 'g'], ['계란', '1', '개(50g)'], ['양파', '1/4', '개(50g)'], ['식용유', '5', 'ml'], ['진간장', '10', 'ml(2작은술)'], ['설탕', '5', 'g(1작은술)'], ['물', '30', 'ml'], ['마요네즈', '20', 'g'], ['김가루', '3', 'g'], ['대파', '8', 'g']]</x:v>
+      </x:c>
+      <x:c r="J65" s="5" t="str">
+        <x:v>1인분</x:v>
+      </x:c>
+      <x:c r="K65" s="5" t="str">
+        <x:v>초급</x:v>
+      </x:c>
+      <x:c r="L65" s="5" t="str">
+        <x:v>18분이내</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="66" ht="22" customHeight="1">
+      <x:c r="A66" s="4" t="n">
+        <x:v>4001</x:v>
+      </x:c>
+      <x:c r="B66" s="4" t="str">
+        <x:v>계란볶음밥</x:v>
+      </x:c>
+      <x:c r="C66" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D66" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E66" s="5" t="str">
+        <x:v>볶음밥</x:v>
+      </x:c>
+      <x:c r="F66" s="5" t="str">
+        <x:v>15분 이하|원팬 요리|전자레인지|도시락 가능|든든한 한 끼|남은 재료 활용</x:v>
+      </x:c>
+      <x:c r="G66" s="5" t="str">
+        <x:v>밥|계란</x:v>
+      </x:c>
+      <x:c r="H66" s="5" t="str">
+        <x:v>볶음밥</x:v>
+      </x:c>
+      <x:c r="I66" s="5" t="str">
+        <x:v>[['밥', '200', 'g'], ['계란', '2', '개(100g)'], ['대파', '20', 'g'], ['식용유', '10', 'ml(2작은술)'], ['진간장', '7.5', 'ml(1/2큰술)'], ['소금', '0.5', 'g'], ['후추', '0.1', 'g'], ['참기름', '2.5', 'ml(1/2작은술)']]</x:v>
+      </x:c>
+      <x:c r="J66" s="5" t="str">
+        <x:v>1인분</x:v>
+      </x:c>
+      <x:c r="K66" s="5" t="str">
+        <x:v>초급</x:v>
+      </x:c>
+      <x:c r="L66" s="5" t="str">
+        <x:v>12분이내</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="67" ht="22" customHeight="1">
+      <x:c r="A67" s="4" t="n">
+        <x:v>4002</x:v>
+      </x:c>
+      <x:c r="B67" s="4" t="str">
+        <x:v>김치볶음밥</x:v>
+      </x:c>
+      <x:c r="C67" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D67" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E67" s="5" t="str">
+        <x:v>볶음밥</x:v>
+      </x:c>
+      <x:c r="F67" s="5" t="str">
+        <x:v>15분 이하|원팬 요리|전자레인지|설거지 적음|도시락 가능|든든한 한 끼|남은 재료 활용</x:v>
+      </x:c>
+      <x:c r="G67" s="5" t="str">
+        <x:v>밥|김치|계란</x:v>
+      </x:c>
+      <x:c r="H67" s="5" t="str">
+        <x:v>볶음밥</x:v>
+      </x:c>
+      <x:c r="I67" s="5" t="str">
+        <x:v>[['밥', '200', 'g'], ['배추김치', '120', 'g'], ['대파', '20', 'g'], ['식용유', '10', 'ml(2작은술)'], ['고추장', '5', 'g(1작은술)'], ['진간장', '5', 'ml(1작은술)'], ['설탕', '3', 'g(3/4작은술)'], ['참기름', '2.5', 'ml(1/2작은술)'], ['계란', '1', '개(50g, 선택)'], ['김가루', '2', 'g']]</x:v>
+      </x:c>
+      <x:c r="J67" s="5" t="str">
+        <x:v>1인분</x:v>
+      </x:c>
+      <x:c r="K67" s="5" t="str">
+        <x:v>초급</x:v>
+      </x:c>
+      <x:c r="L67" s="5" t="str">
+        <x:v>15분이내</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="68" ht="22" customHeight="1">
+      <x:c r="A68" s="4" t="n">
+        <x:v>4003</x:v>
+      </x:c>
+      <x:c r="B68" s="4" t="str">
+        <x:v>새우볶음밥</x:v>
+      </x:c>
+      <x:c r="C68" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D68" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E68" s="5" t="str">
+        <x:v>볶음밥</x:v>
+      </x:c>
+      <x:c r="F68" s="5" t="str">
+        <x:v>15분 이하|원팬 요리|전자레인지|도시락 가능|든든한 한 끼|남은 재료 활용</x:v>
+      </x:c>
+      <x:c r="G68" s="5" t="str">
+        <x:v>밥|새우|계란</x:v>
+      </x:c>
+      <x:c r="H68" s="5" t="str">
+        <x:v>볶음밥</x:v>
+      </x:c>
+      <x:c r="I68" s="5" t="str">
+        <x:v>[['밥', '200', 'g'], ['손질 새우', '100', 'g'], ['계란', '1', '개(50g)'], ['대파', '20', 'g'], ['당근', '30', 'g'], ['양파', '30', 'g'], ['식용유', '10', 'ml(2작은술)'], ['진간장', '7.5', 'ml(1/2큰술)'], ['소금', '0.5', 'g'], ['후추', '0.1', 'g'], ['참기름', '2.5', 'ml(1/2작은술)']]</x:v>
+      </x:c>
+      <x:c r="J68" s="5" t="str">
+        <x:v>1인분</x:v>
+      </x:c>
+      <x:c r="K68" s="5" t="str">
+        <x:v>초급</x:v>
+      </x:c>
+      <x:c r="L68" s="5" t="str">
+        <x:v>15분이내</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="69" ht="22" customHeight="1">
+      <x:c r="A69" s="4" t="n">
+        <x:v>4004</x:v>
+      </x:c>
+      <x:c r="B69" s="4" t="str">
+        <x:v>소시지 볶음밥</x:v>
+      </x:c>
+      <x:c r="C69" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D69" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E69" s="5" t="str">
+        <x:v>볶음밥</x:v>
+      </x:c>
+      <x:c r="F69" s="5" t="str">
+        <x:v>15분 이하|원팬 요리|전자레인지|도시락 가능|든든한 한 끼|남은 재료 활용</x:v>
+      </x:c>
+      <x:c r="G69" s="5" t="str">
+        <x:v>밥|소시지|계란</x:v>
+      </x:c>
+      <x:c r="H69" s="5" t="str">
+        <x:v>볶음밥</x:v>
+      </x:c>
+      <x:c r="I69" s="5" t="str">
+        <x:v>[['밥', '200', 'g'], ['비엔나소시지', '80', 'g'], ['계란', '1', '개(50g)'], ['양파', '40', 'g'], ['당근', '30', 'g'], ['대파', '15', 'g'], ['식용유', '10', 'ml(2작은술)'], ['진간장', '7.5', 'ml(1/2큰술)'], ['케첩', '10', 'g(2작은술, 선택)'], ['소금', '0.3', 'g'], ['후추', '0.1', 'g']]</x:v>
+      </x:c>
+      <x:c r="J69" s="5" t="str">
+        <x:v>1인분</x:v>
+      </x:c>
+      <x:c r="K69" s="5" t="str">
+        <x:v>초급</x:v>
+      </x:c>
+      <x:c r="L69" s="5" t="str">
+        <x:v>15분이내</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="70" ht="22" customHeight="1">
+      <x:c r="A70" s="4" t="n">
+        <x:v>4005</x:v>
+      </x:c>
+      <x:c r="B70" s="4" t="str">
+        <x:v>스팸 김치볶음밥</x:v>
+      </x:c>
+      <x:c r="C70" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D70" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E70" s="5" t="str">
+        <x:v>볶음밥</x:v>
+      </x:c>
+      <x:c r="F70" s="5" t="str">
+        <x:v>15분 이하|원팬 요리|전자레인지|설거지 적음|도시락 가능|든든한 한 끼|남은 재료 활용</x:v>
+      </x:c>
+      <x:c r="G70" s="5" t="str">
+        <x:v>밥|스팸|김치</x:v>
+      </x:c>
+      <x:c r="H70" s="5" t="str">
+        <x:v>볶음밥</x:v>
+      </x:c>
+      <x:c r="I70" s="5" t="str">
+        <x:v>[['밥', '200', 'g'], ['스팸', '80', 'g'], ['배추김치', '100', 'g'], ['대파', '20', 'g'], ['식용유', '5', 'ml(1작은술)'], ['고추장', '5', 'g(1작은술)'], ['진간장', '2.5', 'ml(1/2작은술)'], ['설탕', '2', 'g'], ['참기름', '2.5', 'ml(1/2작은술)'], ['계란', '1', '개(선택)'], ['김가루', '2', 'g']]</x:v>
+      </x:c>
+      <x:c r="J70" s="5" t="str">
+        <x:v>1인분</x:v>
+      </x:c>
+      <x:c r="K70" s="5" t="str">
+        <x:v>초급</x:v>
+      </x:c>
+      <x:c r="L70" s="5" t="str">
+        <x:v>15분이내</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="71" ht="22" customHeight="1">
+      <x:c r="A71" s="4" t="n">
+        <x:v>4006</x:v>
+      </x:c>
+      <x:c r="B71" s="4" t="str">
+        <x:v>참치 김치볶음밥</x:v>
+      </x:c>
+      <x:c r="C71" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D71" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E71" s="5" t="str">
+        <x:v>볶음밥</x:v>
+      </x:c>
+      <x:c r="F71" s="5" t="str">
+        <x:v>15분 이하|원팬 요리|전자레인지|도시락 가능|든든한 한 끼|남은 재료 활용</x:v>
+      </x:c>
+      <x:c r="G71" s="5" t="str">
+        <x:v>밥|참치|김치</x:v>
+      </x:c>
+      <x:c r="H71" s="5" t="str">
+        <x:v>볶음밥</x:v>
+      </x:c>
+      <x:c r="I71" s="5" t="str">
+        <x:v>[['밥', '200', 'g'], ['참치 통조림', '80', 'g'], ['배추김치', '110', 'g'], ['대파', '20', 'g'], ['식용유', '5', 'ml'], ['고추장', '5', 'g'], ['진간장', '5', 'ml'], ['설탕', '2', 'g'], ['참기름', '2.5', 'ml'], ['김가루', '2', 'g'], ['계란', '1', '개(선택)']]</x:v>
+      </x:c>
+      <x:c r="J71" s="5" t="str">
+        <x:v>1인분</x:v>
+      </x:c>
+      <x:c r="K71" s="5" t="str">
+        <x:v>초급</x:v>
+      </x:c>
+      <x:c r="L71" s="5" t="str">
+        <x:v>15분이내</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="72" ht="22" customHeight="1">
+      <x:c r="A72" s="4" t="n">
+        <x:v>5001</x:v>
+      </x:c>
+      <x:c r="B72" s="4" t="str">
+        <x:v>감자 계란국</x:v>
+      </x:c>
+      <x:c r="C72" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D72" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E72" s="5" t="str">
+        <x:v>국</x:v>
+      </x:c>
+      <x:c r="F72" s="5" t="str">
+        <x:v>냄비 하나|아침 식사|남은 재료 활용</x:v>
+      </x:c>
+      <x:c r="G72" s="5" t="str">
+        <x:v>감자|계란</x:v>
+      </x:c>
+      <x:c r="H72" s="5" t="str">
+        <x:v>국·탕</x:v>
+      </x:c>
+      <x:c r="I72" s="5" t="str">
+        <x:v>[['감자', '1/2', '개(100g)'], ['계란', '1', '개(50g)'], ['대파', '10', 'g'], ['물', '450', 'ml'], ['국간장', '7.5', 'ml(1/2큰술)'], ['다진 마늘', '2', 'g(1/2작은술)'], ['소금', '1', 'g'], ['후추', '0.1', 'g']]</x:v>
+      </x:c>
+      <x:c r="J72" s="5" t="str">
+        <x:v>1인분</x:v>
+      </x:c>
+      <x:c r="K72" s="5" t="str">
+        <x:v>초급</x:v>
+      </x:c>
+      <x:c r="L72" s="5" t="str">
+        <x:v>18분이내</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="73" ht="22" customHeight="1">
+      <x:c r="A73" s="4" t="n">
+        <x:v>5002</x:v>
+      </x:c>
+      <x:c r="B73" s="4" t="str">
+        <x:v>계란국</x:v>
+      </x:c>
+      <x:c r="C73" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D73" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E73" s="5" t="str">
+        <x:v>국</x:v>
+      </x:c>
+      <x:c r="F73" s="5" t="str">
+        <x:v>10분 이하|냄비 하나|칼 없이 가능|설거지 적음|아침 식사|남은 재료 활용</x:v>
+      </x:c>
+      <x:c r="G73" s="5" t="str">
+        <x:v>계란</x:v>
+      </x:c>
+      <x:c r="H73" s="5" t="str">
+        <x:v>국·탕</x:v>
+      </x:c>
+      <x:c r="I73" s="5" t="str">
+        <x:v>[['계란', '1', '개(50g)'], ['물', '450', 'ml'], ['대파', '10', 'g'], ['국간장', '7.5', 'ml(1/2큰술)'], ['다진 마늘', '2', 'g(1/2작은술)'], ['소금', '0.8', 'g'], ['후추', '0.1', 'g'], ['참기름', '2.5', 'ml(1/2작은술)']]</x:v>
+      </x:c>
+      <x:c r="J73" s="5" t="str">
+        <x:v>1인분</x:v>
+      </x:c>
+      <x:c r="K73" s="5" t="str">
+        <x:v>초급</x:v>
+      </x:c>
+      <x:c r="L73" s="5" t="str">
+        <x:v>10분이내</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="74" ht="22" customHeight="1">
+      <x:c r="A74" s="4" t="n">
+        <x:v>5003</x:v>
+      </x:c>
+      <x:c r="B74" s="4" t="str">
+        <x:v>김치 콩나물국</x:v>
+      </x:c>
+      <x:c r="C74" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D74" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E74" s="5" t="str">
+        <x:v>국</x:v>
+      </x:c>
+      <x:c r="F74" s="5" t="str">
+        <x:v>15분 이하|냄비 하나|설거지 적음|남은 재료 활용</x:v>
+      </x:c>
+      <x:c r="G74" s="5" t="str">
+        <x:v>김치|콩나물</x:v>
+      </x:c>
+      <x:c r="H74" s="5" t="str">
+        <x:v>국·탕</x:v>
+      </x:c>
+      <x:c r="I74" s="5" t="str">
+        <x:v>[['배추김치', '100', 'g'], ['콩나물', '100', 'g'], ['대파', '15', 'g'], ['물', '500', 'ml'], ['김치국물', '30', 'ml(2큰술)'], ['국간장', '7.5', 'ml(1/2큰술)'], ['다진 마늘', '3', 'g(2/3작은술)'], ['고춧가루', '1', 'g(1/2작은술, 선택)']]</x:v>
+      </x:c>
+      <x:c r="J74" s="5" t="str">
+        <x:v>1인분</x:v>
+      </x:c>
+      <x:c r="K74" s="5" t="str">
+        <x:v>초급</x:v>
+      </x:c>
+      <x:c r="L74" s="5" t="str">
+        <x:v>15분이내</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="75" ht="22" customHeight="1">
+      <x:c r="A75" s="4" t="n">
+        <x:v>5004</x:v>
+      </x:c>
+      <x:c r="B75" s="4" t="str">
+        <x:v>떡국</x:v>
+      </x:c>
+      <x:c r="C75" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D75" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E75" s="5" t="str">
+        <x:v>떡국</x:v>
+      </x:c>
+      <x:c r="F75" s="5" t="str">
+        <x:v>냄비 하나|든든한 한 끼|남은 재료 활용</x:v>
+      </x:c>
+      <x:c r="G75" s="5" t="str">
+        <x:v>떡국떡|소고기|계란</x:v>
+      </x:c>
+      <x:c r="H75" s="5" t="str">
+        <x:v>국·탕</x:v>
+      </x:c>
+      <x:c r="I75" s="5" t="str">
+        <x:v>[['떡국떡', '180', 'g'], ['소고기 국거리', '60', 'g'], ['계란', '1', '개(50g)'], ['대파', '15', 'g'], ['물', '550', 'ml'], ['국간장', '10', 'ml(2작은술)'], ['다진 마늘', '3', 'g'], ['참기름', '5', 'ml(1작은술)'], ['소금', '0.5', 'g'], ['김가루', '2', 'g']]</x:v>
+      </x:c>
+      <x:c r="J75" s="5" t="str">
+        <x:v>1인분</x:v>
+      </x:c>
+      <x:c r="K75" s="5" t="str">
+        <x:v>초급</x:v>
+      </x:c>
+      <x:c r="L75" s="5" t="str">
+        <x:v>20분이내</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="76" ht="22" customHeight="1">
+      <x:c r="A76" s="4" t="n">
+        <x:v>5005</x:v>
+      </x:c>
+      <x:c r="B76" s="4" t="str">
+        <x:v>떡만두국</x:v>
+      </x:c>
+      <x:c r="C76" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D76" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E76" s="5" t="str">
+        <x:v>떡국</x:v>
+      </x:c>
+      <x:c r="F76" s="5" t="str">
+        <x:v>냄비 하나|칼 없이 가능|든든한 한 끼|남은 재료 활용</x:v>
+      </x:c>
+      <x:c r="G76" s="5" t="str">
+        <x:v>떡국떡|냉동만두|계란</x:v>
+      </x:c>
+      <x:c r="H76" s="5" t="str">
+        <x:v>국·탕</x:v>
+      </x:c>
+      <x:c r="I76" s="5" t="str">
+        <x:v>[['떡국떡', '120', 'g'], ['냉동만두', '4', '개(120g)'], ['계란', '1', '개(50g)'], ['대파', '15', 'g'], ['물', '600', 'ml'], ['국간장', '10', 'ml(2작은술)'], ['다진 마늘', '3', 'g'], ['소금', '0.5', 'g'], ['참기름', '2.5', 'ml(1/2작은술)'], ['김가루', '2', 'g']]</x:v>
+      </x:c>
+      <x:c r="J76" s="5" t="str">
+        <x:v>1인분</x:v>
+      </x:c>
+      <x:c r="K76" s="5" t="str">
+        <x:v>초급</x:v>
+      </x:c>
+      <x:c r="L76" s="5" t="str">
+        <x:v>18분이내</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="77" ht="22" customHeight="1">
+      <x:c r="A77" s="4" t="n">
+        <x:v>5006</x:v>
+      </x:c>
+      <x:c r="B77" s="4" t="str">
+        <x:v>미역국</x:v>
+      </x:c>
+      <x:c r="C77" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D77" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E77" s="5" t="str">
+        <x:v>국</x:v>
+      </x:c>
+      <x:c r="F77" s="5" t="str">
+        <x:v>냄비 하나|칼 없이 가능|냉동 가능|아침 식사</x:v>
+      </x:c>
+      <x:c r="G77" s="5" t="str">
+        <x:v>미역</x:v>
+      </x:c>
+      <x:c r="H77" s="5" t="str">
+        <x:v>국·탕</x:v>
+      </x:c>
+      <x:c r="I77" s="5" t="str">
+        <x:v>[['마른 미역', '8', 'g'], ['물', '550', 'ml'], ['국간장', '10', 'ml(2작은술)'], ['다진 마늘', '3', 'g'], ['참기름', '5', 'ml(1작은술)'], ['소금', '0.5', 'g']]</x:v>
+      </x:c>
+      <x:c r="J77" s="5" t="str">
+        <x:v>1인분</x:v>
+      </x:c>
+      <x:c r="K77" s="5" t="str">
+        <x:v>초급</x:v>
+      </x:c>
+      <x:c r="L77" s="5" t="str">
+        <x:v>20분이내</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="78" ht="22" customHeight="1">
+      <x:c r="A78" s="4" t="n">
+        <x:v>5007</x:v>
+      </x:c>
+      <x:c r="B78" s="4" t="str">
+        <x:v>배추된장국</x:v>
+      </x:c>
+      <x:c r="C78" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D78" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E78" s="5" t="str">
+        <x:v>국</x:v>
+      </x:c>
+      <x:c r="F78" s="5" t="str">
+        <x:v>냄비 하나|남은 재료 활용</x:v>
+      </x:c>
+      <x:c r="G78" s="5" t="str">
+        <x:v>배추|두부|국물용 멸치</x:v>
+      </x:c>
+      <x:c r="H78" s="5" t="str">
+        <x:v>국·탕</x:v>
+      </x:c>
+      <x:c r="I78" s="5" t="str">
+        <x:v>[['알배추', '150', 'g'], ['두부', '80', 'g'], ['대파', '15', 'g'], ['물', '500', 'ml'], ['된장', '20', 'g(1큰술)'], ['다진 마늘', '3', 'g'], ['국물용 멸치', '5', '마리(8g, 선택)'], ['고춧가루', '1', 'g(선택)']]</x:v>
+      </x:c>
+      <x:c r="J78" s="5" t="str">
+        <x:v>1인분</x:v>
+      </x:c>
+      <x:c r="K78" s="5" t="str">
+        <x:v>초급</x:v>
+      </x:c>
+      <x:c r="L78" s="5" t="str">
+        <x:v>18분이내</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="79" ht="22" customHeight="1">
+      <x:c r="A79" s="4" t="n">
+        <x:v>5008</x:v>
+      </x:c>
+      <x:c r="B79" s="4" t="str">
+        <x:v>북엇국</x:v>
+      </x:c>
+      <x:c r="C79" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D79" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E79" s="5" t="str">
+        <x:v>국</x:v>
+      </x:c>
+      <x:c r="F79" s="5" t="str">
+        <x:v>냄비 하나|남은 재료 활용</x:v>
+      </x:c>
+      <x:c r="G79" s="5" t="str">
+        <x:v>북어채|계란|무</x:v>
+      </x:c>
+      <x:c r="H79" s="5" t="str">
+        <x:v>국·탕</x:v>
+      </x:c>
+      <x:c r="I79" s="5" t="str">
+        <x:v>[['북어채', '30', 'g'], ['계란', '1', '개(50g)'], ['무', '80', 'g'], ['대파', '15', 'g'], ['물', '550', 'ml'], ['국간장', '10', 'ml(2작은술)'], ['다진 마늘', '3', 'g'], ['참기름', '5', 'ml(1작은술)'], ['소금', '0.5', 'g'], ['후추', '0.1', 'g']]</x:v>
+      </x:c>
+      <x:c r="J79" s="5" t="str">
+        <x:v>1인분</x:v>
+      </x:c>
+      <x:c r="K79" s="5" t="str">
+        <x:v>초급</x:v>
+      </x:c>
+      <x:c r="L79" s="5" t="str">
+        <x:v>18분이내</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="80" ht="22" customHeight="1">
+      <x:c r="A80" s="4" t="n">
+        <x:v>5009</x:v>
+      </x:c>
+      <x:c r="B80" s="4" t="str">
+        <x:v>소고기 무국</x:v>
+      </x:c>
+      <x:c r="C80" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D80" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E80" s="5" t="str">
+        <x:v>국</x:v>
+      </x:c>
+      <x:c r="F80" s="5" t="str">
+        <x:v>냄비 하나|설거지 적음|냉동 가능</x:v>
+      </x:c>
+      <x:c r="G80" s="5" t="str">
+        <x:v>소고기|무</x:v>
+      </x:c>
+      <x:c r="H80" s="5" t="str">
+        <x:v>국·탕</x:v>
+      </x:c>
+      <x:c r="I80" s="5" t="str">
+        <x:v>[['소고기 국거리', '100', 'g'], ['무', '150', 'g'], ['대파', '15', 'g'], ['물', '600', 'ml'], ['국간장', '10', 'ml(2작은술)'], ['다진 마늘', '3', 'g'], ['참기름', '5', 'ml(1작은술)'], ['소금', '0.8', 'g'], ['후추', '0.1', 'g']]</x:v>
+      </x:c>
+      <x:c r="J80" s="5" t="str">
+        <x:v>1인분</x:v>
+      </x:c>
+      <x:c r="K80" s="5" t="str">
+        <x:v>초급</x:v>
+      </x:c>
+      <x:c r="L80" s="5" t="str">
+        <x:v>25분이내</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="81" ht="22" customHeight="1">
+      <x:c r="A81" s="4" t="n">
+        <x:v>5010</x:v>
+      </x:c>
+      <x:c r="B81" s="4" t="str">
+        <x:v>소고기 미역국</x:v>
+      </x:c>
+      <x:c r="C81" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D81" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E81" s="5" t="str">
+        <x:v>국</x:v>
+      </x:c>
+      <x:c r="F81" s="5" t="str">
+        <x:v>냄비 하나|칼 없이 가능|냉동 가능|아침 식사</x:v>
+      </x:c>
+      <x:c r="G81" s="5" t="str">
+        <x:v>미역|소고기</x:v>
+      </x:c>
+      <x:c r="H81" s="5" t="str">
+        <x:v>국·탕</x:v>
+      </x:c>
+      <x:c r="I81" s="5" t="str">
+        <x:v>[['마른 미역', '8', 'g'], ['소고기 국거리', '80', 'g'], ['물', '600', 'ml'], ['국간장', '12.5', 'ml(2.5작은술)'], ['다진 마늘', '3', 'g'], ['참기름', '5', 'ml(1작은술)'], ['소금', '0.5', 'g']]</x:v>
+      </x:c>
+      <x:c r="J81" s="5" t="str">
+        <x:v>1인분</x:v>
+      </x:c>
+      <x:c r="K81" s="5" t="str">
+        <x:v>초급</x:v>
+      </x:c>
+      <x:c r="L81" s="5" t="str">
+        <x:v>25분이내</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="82" ht="22" customHeight="1">
+      <x:c r="A82" s="4" t="n">
+        <x:v>5011</x:v>
+      </x:c>
+      <x:c r="B82" s="4" t="str">
+        <x:v>순두부 계란국</x:v>
+      </x:c>
+      <x:c r="C82" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D82" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E82" s="5" t="str">
+        <x:v>국</x:v>
+      </x:c>
+      <x:c r="F82" s="5" t="str">
+        <x:v>15분 이하|냄비 하나|칼 없이 가능|설거지 적음|아침 식사|남은 재료 활용</x:v>
+      </x:c>
+      <x:c r="G82" s="5" t="str">
+        <x:v>순두부|계란</x:v>
+      </x:c>
+      <x:c r="H82" s="5" t="str">
+        <x:v>국·탕</x:v>
+      </x:c>
+      <x:c r="I82" s="5" t="str">
+        <x:v>[['순두부', '200', 'g'], ['계란', '1', '개(50g)'], ['대파', '15', 'g'], ['물', '450', 'ml'], ['국간장', '7.5', 'ml(1/2큰술)'], ['다진 마늘', '2', 'g'], ['소금', '0.5', 'g'], ['참기름', '2.5', 'ml(1/2작은술)'], ['후추', '0.1', 'g']]</x:v>
+      </x:c>
+      <x:c r="J82" s="5" t="str">
+        <x:v>1인분</x:v>
+      </x:c>
+      <x:c r="K82" s="5" t="str">
+        <x:v>초급</x:v>
+      </x:c>
+      <x:c r="L82" s="5" t="str">
+        <x:v>12분이내</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="83" ht="22" customHeight="1">
+      <x:c r="A83" s="4" t="n">
+        <x:v>5012</x:v>
+      </x:c>
+      <x:c r="B83" s="4" t="str">
+        <x:v>어묵국</x:v>
+      </x:c>
+      <x:c r="C83" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D83" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E83" s="5" t="str">
+        <x:v>국</x:v>
+      </x:c>
+      <x:c r="F83" s="5" t="str">
+        <x:v>냄비 하나|설거지 적음|남은 재료 활용</x:v>
+      </x:c>
+      <x:c r="G83" s="5" t="str">
+        <x:v>어묵|무|국물용 멸치</x:v>
+      </x:c>
+      <x:c r="H83" s="5" t="str">
+        <x:v>국·탕</x:v>
+      </x:c>
+      <x:c r="I83" s="5" t="str">
+        <x:v>[['사각어묵', '2', '장(100g)'], ['무', '100', 'g'], ['대파', '15', 'g'], ['물', '600', 'ml'], ['국간장', '10', 'ml(2작은술)'], ['다진 마늘', '2', 'g'], ['국물용 멸치', '5', '마리(8g, 선택)'], ['소금', '0.5', 'g'], ['후추', '0.1', 'g']]</x:v>
+      </x:c>
+      <x:c r="J83" s="5" t="str">
+        <x:v>1인분</x:v>
+      </x:c>
+      <x:c r="K83" s="5" t="str">
+        <x:v>초급</x:v>
+      </x:c>
+      <x:c r="L83" s="5" t="str">
+        <x:v>18분이내</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="84" ht="22" customHeight="1">
+      <x:c r="A84" s="4" t="n">
+        <x:v>5013</x:v>
+      </x:c>
+      <x:c r="B84" s="4" t="str">
+        <x:v>오이냉국</x:v>
+      </x:c>
+      <x:c r="C84" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D84" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E84" s="5" t="str">
+        <x:v>국</x:v>
+      </x:c>
+      <x:c r="F84" s="5" t="str">
+        <x:v>10분 이하|불 없이 가능</x:v>
+      </x:c>
+      <x:c r="G84" s="5" t="str">
+        <x:v>오이|미역</x:v>
+      </x:c>
+      <x:c r="H84" s="5" t="str">
+        <x:v>국·탕</x:v>
+      </x:c>
+      <x:c r="I84" s="5" t="str">
+        <x:v>[['오이', '1/2', '개(100g)'], ['마른 미역', '3', 'g'], ['찬물', '350', 'ml'], ['식초', '30', 'ml(2큰술)'], ['설탕', '15', 'g(1큰술)'], ['소금', '3', 'g(1/2작은술)'], ['국간장', '5', 'ml(1작은술)'], ['다진 마늘', '1', 'g(1/4작은술)'], ['통깨', '1', 'g'], ['얼음', '6', '개']]</x:v>
+      </x:c>
+      <x:c r="J84" s="5" t="str">
+        <x:v>1인분</x:v>
+      </x:c>
+      <x:c r="K84" s="5" t="str">
+        <x:v>초급</x:v>
+      </x:c>
+      <x:c r="L84" s="5" t="str">
+        <x:v>10분이내</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="85" ht="22" customHeight="1">
+      <x:c r="A85" s="4" t="n">
+        <x:v>5014</x:v>
+      </x:c>
+      <x:c r="B85" s="4" t="str">
+        <x:v>오징어 무국</x:v>
+      </x:c>
+      <x:c r="C85" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D85" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E85" s="5" t="str">
+        <x:v>국</x:v>
+      </x:c>
+      <x:c r="F85" s="5" t="str">
+        <x:v>냄비 하나|설거지 적음</x:v>
+      </x:c>
+      <x:c r="G85" s="5" t="str">
+        <x:v>오징어|무</x:v>
+      </x:c>
+      <x:c r="H85" s="5" t="str">
+        <x:v>국·탕</x:v>
+      </x:c>
+      <x:c r="I85" s="5" t="str">
+        <x:v>[['손질 오징어', '150', 'g'], ['무', '150', 'g'], ['대파', '15', 'g'], ['물', '600', 'ml'], ['국간장', '12.5', 'ml(2.5작은술)'], ['고춧가루', '2', 'g(1작은술, 선택)'], ['다진 마늘', '3', 'g'], ['소금', '0.5', 'g'], ['참기름', '5', 'ml(1작은술)']]</x:v>
+      </x:c>
+      <x:c r="J85" s="5" t="str">
+        <x:v>1인분</x:v>
+      </x:c>
+      <x:c r="K85" s="5" t="str">
+        <x:v>초급</x:v>
+      </x:c>
+      <x:c r="L85" s="5" t="str">
+        <x:v>22분이내</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="86" ht="22" customHeight="1">
+      <x:c r="A86" s="4" t="n">
+        <x:v>5015</x:v>
+      </x:c>
+      <x:c r="B86" s="4" t="str">
+        <x:v>콩나물국</x:v>
+      </x:c>
+      <x:c r="C86" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D86" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E86" s="5" t="str">
+        <x:v>국</x:v>
+      </x:c>
+      <x:c r="F86" s="5" t="str">
+        <x:v>15분 이하|냄비 하나|칼 없이 가능|설거지 적음|아침 식사|남은 재료 활용</x:v>
+      </x:c>
+      <x:c r="G86" s="5" t="str">
+        <x:v>콩나물</x:v>
+      </x:c>
+      <x:c r="H86" s="5" t="str">
+        <x:v>국·탕</x:v>
+      </x:c>
+      <x:c r="I86" s="5" t="str">
+        <x:v>[['콩나물', '150', 'g'], ['대파', '15', 'g'], ['물', '550', 'ml'], ['국간장', '7.5', 'ml(1/2큰술)'], ['다진 마늘', '2', 'g'], ['소금', '0.8', 'g'], ['고춧가루', '1', 'g(선택)']]</x:v>
+      </x:c>
+      <x:c r="J86" s="5" t="str">
+        <x:v>1인분</x:v>
+      </x:c>
+      <x:c r="K86" s="5" t="str">
+        <x:v>초급</x:v>
+      </x:c>
+      <x:c r="L86" s="5" t="str">
+        <x:v>12분이내</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="87" ht="22" customHeight="1">
+      <x:c r="A87" s="4" t="n">
+        <x:v>6001</x:v>
+      </x:c>
+      <x:c r="B87" s="4" t="str">
+        <x:v>고추장찌개</x:v>
+      </x:c>
+      <x:c r="C87" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D87" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E87" s="5" t="str">
+        <x:v>찌개</x:v>
+      </x:c>
+      <x:c r="F87" s="5" t="str">
+        <x:v>냄비 하나|설거지 적음|든든한 한 끼|남은 재료 활용</x:v>
+      </x:c>
+      <x:c r="G87" s="5" t="str">
+        <x:v>돼지고기|감자|애호박</x:v>
+      </x:c>
+      <x:c r="H87" s="5" t="str">
+        <x:v>찌개</x:v>
+      </x:c>
+      <x:c r="I87" s="5" t="str">
+        <x:v>[['돼지고기 앞다리살', '100', 'g'], ['감자', '1/2', '개(100g)'], ['애호박', '80', 'g'], ['양파', '1/4', '개(50g)'], ['두부', '100', 'g'], ['대파', '15', 'g'], ['물', '450', 'ml'], ['고추장', '20', 'g(1큰술)'], ['고춧가루', '3', 'g(1/2큰술)'], ['국간장', '5', 'ml(1작은술)'], ['다진 마늘', '5', 'g(1작은술)'], ['식용유', '5', 'ml(1작은술)']]</x:v>
+      </x:c>
+      <x:c r="J87" s="5" t="str">
+        <x:v>1인분</x:v>
+      </x:c>
+      <x:c r="K87" s="5" t="str">
+        <x:v>중급</x:v>
+      </x:c>
+      <x:c r="L87" s="5" t="str">
+        <x:v>25분이내</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="88" ht="22" customHeight="1">
+      <x:c r="A88" s="4" t="n">
+        <x:v>6002</x:v>
+      </x:c>
+      <x:c r="B88" s="4" t="str">
+        <x:v>김치찌개</x:v>
+      </x:c>
+      <x:c r="C88" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D88" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E88" s="5" t="str">
+        <x:v>찌개</x:v>
+      </x:c>
+      <x:c r="F88" s="5" t="str">
+        <x:v>냄비 하나|설거지 적음|냉동 가능|든든한 한 끼|남은 재료 활용</x:v>
+      </x:c>
+      <x:c r="G88" s="5" t="str">
+        <x:v>김치|돼지고기|두부</x:v>
+      </x:c>
+      <x:c r="H88" s="5" t="str">
+        <x:v>찌개</x:v>
+      </x:c>
+      <x:c r="I88" s="5" t="str">
+        <x:v>[['배추김치', '180', 'g'], ['돼지고기 앞다리살', '100', 'g'], ['두부', '120', 'g'], ['양파', '1/4', '개(50g)'], ['대파', '15', 'g'], ['물', '450', 'ml'], ['김치국물', '30', 'ml'], ['고춧가루', '3', 'g(1/2큰술)'], ['국간장', '5', 'ml(1작은술)'], ['다진 마늘', '5', 'g(1작은술)'], ['식용유', '5', 'ml(1작은술)'], ['설탕', '2', 'g(1/2작은술)']]</x:v>
+      </x:c>
+      <x:c r="J88" s="5" t="str">
+        <x:v>1인분</x:v>
+      </x:c>
+      <x:c r="K88" s="5" t="str">
+        <x:v>초급</x:v>
+      </x:c>
+      <x:c r="L88" s="5" t="str">
+        <x:v>25분이내</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="89" ht="22" customHeight="1">
+      <x:c r="A89" s="4" t="n">
+        <x:v>6003</x:v>
+      </x:c>
+      <x:c r="B89" s="4" t="str">
+        <x:v>돼지고기 김치찌개</x:v>
+      </x:c>
+      <x:c r="C89" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D89" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E89" s="5" t="str">
+        <x:v>찌개</x:v>
+      </x:c>
+      <x:c r="F89" s="5" t="str">
+        <x:v>냄비 하나|설거지 적음|냉동 가능|든든한 한 끼|남은 재료 활용</x:v>
+      </x:c>
+      <x:c r="G89" s="5" t="str">
+        <x:v>돼지고기|김치|두부</x:v>
+      </x:c>
+      <x:c r="H89" s="5" t="str">
+        <x:v>찌개</x:v>
+      </x:c>
+      <x:c r="I89" s="5" t="str">
+        <x:v>[['돼지고기 앞다리살', '130', 'g'], ['배추김치', '180', 'g'], ['두부', '120', 'g'], ['양파', '1/4', '개(50g)'], ['대파', '15', 'g'], ['물', '450', 'ml'], ['김치국물', '30', 'ml'], ['고춧가루', '3', 'g(1/2큰술)'], ['국간장', '5', 'ml(1작은술)'], ['다진 마늘', '5', 'g(1작은술)'], ['식용유', '5', 'ml(1작은술)'], ['설탕', '2', 'g']]</x:v>
+      </x:c>
+      <x:c r="J89" s="5" t="str">
+        <x:v>1인분</x:v>
+      </x:c>
+      <x:c r="K89" s="5" t="str">
+        <x:v>초급</x:v>
+      </x:c>
+      <x:c r="L89" s="5" t="str">
+        <x:v>25분이내</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="90" ht="22" customHeight="1">
+      <x:c r="A90" s="4" t="n">
+        <x:v>6004</x:v>
+      </x:c>
+      <x:c r="B90" s="4" t="str">
+        <x:v>된장찌개</x:v>
+      </x:c>
+      <x:c r="C90" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D90" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E90" s="5" t="str">
+        <x:v>찌개</x:v>
+      </x:c>
+      <x:c r="F90" s="5" t="str">
+        <x:v>냄비 하나|든든한 한 끼|남은 재료 활용</x:v>
+      </x:c>
+      <x:c r="G90" s="5" t="str">
+        <x:v>두부|애호박|감자</x:v>
+      </x:c>
+      <x:c r="H90" s="5" t="str">
+        <x:v>찌개</x:v>
+      </x:c>
+      <x:c r="I90" s="5" t="str">
+        <x:v>[['두부', '120', 'g'], ['애호박', '80', 'g'], ['감자', '80', 'g'], ['양파', '1/4', '개(50g)'], ['대파', '15', 'g'], ['물', '450', 'ml'], ['된장', '25', 'g(1큰술+1작은술)'], ['고추장', '5', 'g(1작은술, 선택)'], ['다진 마늘', '3', 'g'], ['국물용 멸치', '5', '마리(8g, 선택)']]</x:v>
+      </x:c>
+      <x:c r="J90" s="5" t="str">
+        <x:v>1인분</x:v>
+      </x:c>
+      <x:c r="K90" s="5" t="str">
+        <x:v>초급</x:v>
+      </x:c>
+      <x:c r="L90" s="5" t="str">
+        <x:v>22분이내</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="91" ht="22" customHeight="1">
+      <x:c r="A91" s="4" t="n">
+        <x:v>6005</x:v>
+      </x:c>
+      <x:c r="B91" s="4" t="str">
+        <x:v>부대찌개</x:v>
+      </x:c>
+      <x:c r="C91" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D91" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E91" s="5" t="str">
+        <x:v>찌개</x:v>
+      </x:c>
+      <x:c r="F91" s="5" t="str">
+        <x:v>냄비 하나|설거지 적음|든든한 한 끼|남은 재료 활용</x:v>
+      </x:c>
+      <x:c r="G91" s="5" t="str">
+        <x:v>스팸|소시지|김치</x:v>
+      </x:c>
+      <x:c r="H91" s="5" t="str">
+        <x:v>찌개</x:v>
+      </x:c>
+      <x:c r="I91" s="5" t="str">
+        <x:v>[['스팸', '80', 'g'], ['비엔나소시지', '80', 'g'], ['배추김치', '100', 'g'], ['두부', '100', 'g'], ['양파', '1/4', '개(50g)'], ['대파', '20', 'g'], ['라면사리', '1/2', '개(55g, 선택)'], ['물', '500', 'ml'], ['고추장', '15', 'g(1큰술)'], ['고춧가루', '4', 'g(2작은술)'], ['진간장', '10', 'ml(2작은술)'], ['다진 마늘', '5', 'g'], ['설탕', '3', 'g'], ['슬라이스 치즈', '1', '장(20g, 선택)']]</x:v>
+      </x:c>
+      <x:c r="J91" s="5" t="str">
+        <x:v>1인분</x:v>
+      </x:c>
+      <x:c r="K91" s="5" t="str">
+        <x:v>초급</x:v>
+      </x:c>
+      <x:c r="L91" s="5" t="str">
+        <x:v>25분이내</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="92" ht="22" customHeight="1">
+      <x:c r="A92" s="4" t="n">
+        <x:v>6006</x:v>
+      </x:c>
+      <x:c r="B92" s="4" t="str">
+        <x:v>순두부찌개</x:v>
+      </x:c>
+      <x:c r="C92" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D92" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E92" s="5" t="str">
+        <x:v>찌개</x:v>
+      </x:c>
+      <x:c r="F92" s="5" t="str">
+        <x:v>냄비 하나|설거지 적음|든든한 한 끼</x:v>
+      </x:c>
+      <x:c r="G92" s="5" t="str">
+        <x:v>순두부|돼지고기|양파</x:v>
+      </x:c>
+      <x:c r="H92" s="5" t="str">
+        <x:v>찌개</x:v>
+      </x:c>
+      <x:c r="I92" s="5" t="str">
+        <x:v>[['순두부', '300', 'g'], ['돼지고기 다짐육', '80', 'g'], ['양파', '1/4', '개(50g)'], ['애호박', '60', 'g'], ['대파', '15', 'g'], ['계란', '1', '개(50g, 선택)'], ['물', '350', 'ml'], ['고춧가루', '5', 'g(2작은술)'], ['국간장', '10', 'ml(2작은술)'], ['다진 마늘', '5', 'g'], ['식용유', '10', 'ml(2작은술)'], ['소금', '0.5', 'g']]</x:v>
+      </x:c>
+      <x:c r="J92" s="5" t="str">
+        <x:v>1인분</x:v>
+      </x:c>
+      <x:c r="K92" s="5" t="str">
+        <x:v>초급</x:v>
+      </x:c>
+      <x:c r="L92" s="5" t="str">
+        <x:v>20분이내</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="93" ht="22" customHeight="1">
+      <x:c r="A93" s="4" t="n">
+        <x:v>6007</x:v>
+      </x:c>
+      <x:c r="B93" s="4" t="str">
+        <x:v>스팸 감자짜글이</x:v>
+      </x:c>
+      <x:c r="C93" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D93" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E93" s="5" t="str">
+        <x:v>짜글이</x:v>
+      </x:c>
+      <x:c r="F93" s="5" t="str">
+        <x:v>냄비 하나|설거지 적음|든든한 한 끼</x:v>
+      </x:c>
+      <x:c r="G93" s="5" t="str">
+        <x:v>스팸|감자|양파</x:v>
+      </x:c>
+      <x:c r="H93" s="5" t="str">
+        <x:v>찌개</x:v>
+      </x:c>
+      <x:c r="I93" s="5" t="str">
+        <x:v>[['스팸', '100', 'g'], ['감자', '1', '개(200g)'], ['양파', '1/2', '개(100g)'], ['대파', '20', 'g'], ['물', '400', 'ml'], ['고추장', '15', 'g(1큰술)'], ['고춧가루', '4', 'g(2작은술)'], ['진간장', '10', 'ml(2작은술)'], ['설탕', '3', 'g'], ['다진 마늘', '3', 'g']]</x:v>
+      </x:c>
+      <x:c r="J93" s="5" t="str">
+        <x:v>1인분</x:v>
+      </x:c>
+      <x:c r="K93" s="5" t="str">
+        <x:v>초급</x:v>
+      </x:c>
+      <x:c r="L93" s="5" t="str">
+        <x:v>25분이내</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="94" ht="22" customHeight="1">
+      <x:c r="A94" s="4" t="n">
+        <x:v>6008</x:v>
+      </x:c>
+      <x:c r="B94" s="4" t="str">
+        <x:v>참치 김치찌개</x:v>
+      </x:c>
+      <x:c r="C94" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D94" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E94" s="5" t="str">
+        <x:v>찌개</x:v>
+      </x:c>
+      <x:c r="F94" s="5" t="str">
+        <x:v>냄비 하나|든든한 한 끼|남은 재료 활용</x:v>
+      </x:c>
+      <x:c r="G94" s="5" t="str">
+        <x:v>참치|김치|두부</x:v>
+      </x:c>
+      <x:c r="H94" s="5" t="str">
+        <x:v>찌개</x:v>
+      </x:c>
+      <x:c r="I94" s="5" t="str">
+        <x:v>[['참치 통조림', '100', 'g'], ['배추김치', '180', 'g'], ['두부', '120', 'g'], ['양파', '1/4', '개(50g)'], ['대파', '15', 'g'], ['물', '450', 'ml'], ['김치국물', '30', 'ml'], ['고춧가루', '3', 'g'], ['국간장', '5', 'ml'], ['다진 마늘', '3', 'g'], ['설탕', '2', 'g']]</x:v>
+      </x:c>
+      <x:c r="J94" s="5" t="str">
+        <x:v>1인분</x:v>
+      </x:c>
+      <x:c r="K94" s="5" t="str">
+        <x:v>초급</x:v>
+      </x:c>
+      <x:c r="L94" s="5" t="str">
+        <x:v>20분이내</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="95" ht="22" customHeight="1">
+      <x:c r="A95" s="4" t="n">
+        <x:v>6009</x:v>
+      </x:c>
+      <x:c r="B95" s="4" t="str">
+        <x:v>참치 순두부찌개</x:v>
+      </x:c>
+      <x:c r="C95" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D95" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E95" s="5" t="str">
+        <x:v>찌개</x:v>
+      </x:c>
+      <x:c r="F95" s="5" t="str">
+        <x:v>냄비 하나|든든한 한 끼|남은 재료 활용</x:v>
+      </x:c>
+      <x:c r="G95" s="5" t="str">
+        <x:v>순두부|참치|양파</x:v>
+      </x:c>
+      <x:c r="H95" s="5" t="str">
+        <x:v>찌개</x:v>
+      </x:c>
+      <x:c r="I95" s="5" t="str">
+        <x:v>[['순두부', '300', 'g'], ['참치 통조림', '80', 'g'], ['양파', '1/4', '개(50g)'], ['애호박', '60', 'g'], ['대파', '15', 'g'], ['계란', '1', '개(선택)'], ['물', '350', 'ml'], ['고춧가루', '5', 'g(2작은술)'], ['국간장', '10', 'ml(2작은술)'], ['다진 마늘', '3', 'g'], ['식용유 또는 참치기름', '5', 'ml'], ['소금', '0.5', 'g']]</x:v>
+      </x:c>
+      <x:c r="J95" s="5" t="str">
+        <x:v>1인분</x:v>
+      </x:c>
+      <x:c r="K95" s="5" t="str">
+        <x:v>초급</x:v>
+      </x:c>
+      <x:c r="L95" s="5" t="str">
+        <x:v>18분이내</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="96" ht="22" customHeight="1">
+      <x:c r="A96" s="4" t="n">
+        <x:v>7001</x:v>
+      </x:c>
+      <x:c r="B96" s="4" t="str">
+        <x:v>김치비빔국수</x:v>
+      </x:c>
+      <x:c r="C96" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D96" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E96" s="5" t="str">
+        <x:v>국수</x:v>
+      </x:c>
+      <x:c r="F96" s="5" t="str">
+        <x:v>15분 이하|냄비 하나|든든한 한 끼|야식|남은 재료 활용</x:v>
+      </x:c>
+      <x:c r="G96" s="5" t="str">
+        <x:v>소면|김치|오이</x:v>
+      </x:c>
+      <x:c r="H96" s="5" t="str">
+        <x:v>면</x:v>
+      </x:c>
+      <x:c r="I96" s="5" t="str">
+        <x:v>[['소면', '100', 'g'], ['배추김치', '100', 'g'], ['오이', '40', 'g'], ['고추장', '15', 'g(1큰술)'], ['고춧가루', '2', 'g(1작은술)'], ['식초', '15', 'ml(1큰술)'], ['설탕', '10', 'g(2작은술)'], ['진간장', '5', 'ml(1작은술)'], ['참기름', '5', 'ml(1작은술)'], ['통깨', '2', 'g(1/2작은술)']]</x:v>
+      </x:c>
+      <x:c r="J96" s="5" t="str">
+        <x:v>1인분</x:v>
+      </x:c>
+      <x:c r="K96" s="5" t="str">
+        <x:v>초급</x:v>
+      </x:c>
+      <x:c r="L96" s="5" t="str">
+        <x:v>15분이내</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="97" ht="22" customHeight="1">
+      <x:c r="A97" s="4" t="n">
+        <x:v>7002</x:v>
+      </x:c>
+      <x:c r="B97" s="4" t="str">
+        <x:v>김치우동</x:v>
+      </x:c>
+      <x:c r="C97" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D97" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E97" s="5" t="str">
+        <x:v>우동</x:v>
+      </x:c>
+      <x:c r="F97" s="5" t="str">
+        <x:v>15분 이하|냄비 하나|든든한 한 끼|야식</x:v>
+      </x:c>
+      <x:c r="G97" s="5" t="str">
+        <x:v>우동면|김치|어묵</x:v>
+      </x:c>
+      <x:c r="H97" s="5" t="str">
+        <x:v>면</x:v>
+      </x:c>
+      <x:c r="I97" s="5" t="str">
+        <x:v>[['냉동 우동면', '1', '개(200g)'], ['배추김치', '100', 'g'], ['어묵', '50', 'g'], ['대파', '15', 'g'], ['물', '500', 'ml'], ['김치국물', '30', 'ml(2큰술)'], ['국간장', '7.5', 'ml(1/2큰술)'], ['고춧가루', '1', 'g(1/2작은술)'], ['다진 마늘', '2', 'g(1/2작은술)']]</x:v>
+      </x:c>
+      <x:c r="J97" s="5" t="str">
+        <x:v>1인분</x:v>
+      </x:c>
+      <x:c r="K97" s="5" t="str">
+        <x:v>초급</x:v>
+      </x:c>
+      <x:c r="L97" s="5" t="str">
+        <x:v>15분이내</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="98" ht="22" customHeight="1">
+      <x:c r="A98" s="4" t="n">
+        <x:v>7003</x:v>
+      </x:c>
+      <x:c r="B98" s="4" t="str">
+        <x:v>로제파스타</x:v>
+      </x:c>
+      <x:c r="C98" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D98" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E98" s="5" t="str">
+        <x:v>파스타</x:v>
+      </x:c>
+      <x:c r="F98" s="5" t="str">
+        <x:v>든든한 한 끼|야식</x:v>
+      </x:c>
+      <x:c r="G98" s="5" t="str">
+        <x:v>스파게티면|토마토소스·우유|베이컨</x:v>
+      </x:c>
+      <x:c r="H98" s="5" t="str">
+        <x:v>면</x:v>
+      </x:c>
+      <x:c r="I98" s="5" t="str">
+        <x:v>[['스파게티면', '100', 'g'], ['토마토소스', '120', 'g'], ['우유', '120', 'ml'], ['베이컨', '50', 'g'], ['양파', '1/4', '개(50g)'], ['다진 마늘', '5', 'g'], ['올리브유', '10', 'ml(2작은술)'], ['소금', '8', 'g(면 삶는 물용)'], ['후추', '0.1', 'g'], ['파르메산 치즈', '10', 'g(선택)']]</x:v>
+      </x:c>
+      <x:c r="J98" s="5" t="str">
+        <x:v>1인분</x:v>
+      </x:c>
+      <x:c r="K98" s="5" t="str">
+        <x:v>초급</x:v>
+      </x:c>
+      <x:c r="L98" s="5" t="str">
+        <x:v>22분이내</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="99" ht="22" customHeight="1">
+      <x:c r="A99" s="4" t="n">
+        <x:v>7004</x:v>
+      </x:c>
+      <x:c r="B99" s="4" t="str">
+        <x:v>메밀소바</x:v>
+      </x:c>
+      <x:c r="C99" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D99" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E99" s="5" t="str">
+        <x:v>메밀면</x:v>
+      </x:c>
+      <x:c r="F99" s="5" t="str">
+        <x:v>15분 이하|냄비 하나|든든한 한 끼|야식</x:v>
+      </x:c>
+      <x:c r="G99" s="5" t="str">
+        <x:v>메밀면|무</x:v>
+      </x:c>
+      <x:c r="H99" s="5" t="str">
+        <x:v>면</x:v>
+      </x:c>
+      <x:c r="I99" s="5" t="str">
+        <x:v>[['건 메밀면', '100', 'g'], ['쯔유(3배 농축)', '50', 'ml'], ['찬물', '150', 'ml'], ['무', '50', 'g'], ['대파', '10', 'g'], ['김가루', '2', 'g'], ['와사비', '2', 'g(선택)'], ['얼음', '5', '개']]</x:v>
+      </x:c>
+      <x:c r="J99" s="5" t="str">
+        <x:v>1인분</x:v>
+      </x:c>
+      <x:c r="K99" s="5" t="str">
+        <x:v>초급</x:v>
+      </x:c>
+      <x:c r="L99" s="5" t="str">
+        <x:v>15분이내</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="100" ht="22" customHeight="1">
+      <x:c r="A100" s="4" t="n">
+        <x:v>7005</x:v>
+      </x:c>
+      <x:c r="B100" s="4" t="str">
+        <x:v>물냉면</x:v>
+      </x:c>
+      <x:c r="C100" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D100" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E100" s="5" t="str">
+        <x:v>냉면</x:v>
+      </x:c>
+      <x:c r="F100" s="5" t="str">
+        <x:v>15분 이하|냄비 하나|든든한 한 끼|야식</x:v>
+      </x:c>
+      <x:c r="G100" s="5" t="str">
+        <x:v>냉면|오이|계란</x:v>
+      </x:c>
+      <x:c r="H100" s="5" t="str">
+        <x:v>면</x:v>
+      </x:c>
+      <x:c r="I100" s="5" t="str">
+        <x:v>[['냉면사리', '1', '인분(180g)'], ['시판 냉면육수', '1', '봉(300ml)'], ['오이', '40', 'g'], ['삶은 계란', '1/2', '개(25g)'], ['무절임', '40', 'g'], ['식초', '10', 'ml(2작은술)'], ['겨자', '2', 'g(선택)'], ['얼음', '5', '개']]</x:v>
+      </x:c>
+      <x:c r="J100" s="5" t="str">
+        <x:v>1인분</x:v>
+      </x:c>
+      <x:c r="K100" s="5" t="str">
+        <x:v>초급</x:v>
+      </x:c>
+      <x:c r="L100" s="5" t="str">
+        <x:v>15분이내</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="101" ht="22" customHeight="1">
+      <x:c r="A101" s="4" t="n">
+        <x:v>7006</x:v>
+      </x:c>
+      <x:c r="B101" s="4" t="str">
+        <x:v>볶음우동</x:v>
+      </x:c>
+      <x:c r="C101" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D101" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E101" s="5" t="str">
+        <x:v>우동</x:v>
+      </x:c>
+      <x:c r="F101" s="5" t="str">
+        <x:v>원팬 요리|전자레인지|든든한 한 끼|야식|남은 재료 활용</x:v>
+      </x:c>
+      <x:c r="G101" s="5" t="str">
+        <x:v>우동면|돼지고기|양배추</x:v>
+      </x:c>
+      <x:c r="H101" s="5" t="str">
+        <x:v>면</x:v>
+      </x:c>
+      <x:c r="I101" s="5" t="str">
+        <x:v>[['냉동 우동면', '1', '개(200g)'], ['돼지고기 또는 소고기 얇은 것', '80', 'g'], ['양배추', '80', 'g'], ['양파', '1/4', '개(50g)'], ['당근', '20', 'g'], ['대파', '15', 'g'], ['식용유', '10', 'ml(2작은술)'], ['굴소스', '15', 'ml(1큰술)'], ['진간장', '5', 'ml(1작은술)'], ['설탕', '2', 'g'], ['물', '30', 'ml'], ['후추', '0.1', 'g']]</x:v>
+      </x:c>
+      <x:c r="J101" s="5" t="str">
+        <x:v>1인분</x:v>
+      </x:c>
+      <x:c r="K101" s="5" t="str">
+        <x:v>초급</x:v>
+      </x:c>
+      <x:c r="L101" s="5" t="str">
+        <x:v>18분이내</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="102" ht="22" customHeight="1">
+      <x:c r="A102" s="4" t="n">
+        <x:v>7007</x:v>
+      </x:c>
+      <x:c r="B102" s="4" t="str">
+        <x:v>비빔국수</x:v>
+      </x:c>
+      <x:c r="C102" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D102" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E102" s="5" t="str">
+        <x:v>국수</x:v>
+      </x:c>
+      <x:c r="F102" s="5" t="str">
+        <x:v>15분 이하|냄비 하나|든든한 한 끼|야식</x:v>
+      </x:c>
+      <x:c r="G102" s="5" t="str">
+        <x:v>소면|오이|상추</x:v>
+      </x:c>
+      <x:c r="H102" s="5" t="str">
+        <x:v>면</x:v>
+      </x:c>
+      <x:c r="I102" s="5" t="str">
+        <x:v>[['소면', '100', 'g'], ['오이', '50', 'g'], ['상추', '30', 'g'], ['삶은 계란', '1/2', '개(25g, 선택)'], ['고추장', '20', 'g(1큰술+1작은술)'], ['식초', '15', 'ml(1큰술)'], ['설탕', '10', 'g(2작은술)'], ['진간장', '5', 'ml(1작은술)'], ['고춧가루', '2', 'g(1작은술)'], ['참기름', '5', 'ml(1작은술)'], ['통깨', '2', 'g']]</x:v>
+      </x:c>
+      <x:c r="J102" s="5" t="str">
+        <x:v>1인분</x:v>
+      </x:c>
+      <x:c r="K102" s="5" t="str">
+        <x:v>초급</x:v>
+      </x:c>
+      <x:c r="L102" s="5" t="str">
+        <x:v>15분이내</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="103" ht="22" customHeight="1">
+      <x:c r="A103" s="4" t="n">
+        <x:v>7008</x:v>
+      </x:c>
+      <x:c r="B103" s="4" t="str">
+        <x:v>비빔냉면</x:v>
+      </x:c>
+      <x:c r="C103" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D103" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E103" s="5" t="str">
+        <x:v>냉면</x:v>
+      </x:c>
+      <x:c r="F103" s="5" t="str">
+        <x:v>15분 이하|냄비 하나|든든한 한 끼|야식</x:v>
+      </x:c>
+      <x:c r="G103" s="5" t="str">
+        <x:v>냉면|오이|무절임</x:v>
+      </x:c>
+      <x:c r="H103" s="5" t="str">
+        <x:v>면</x:v>
+      </x:c>
+      <x:c r="I103" s="5" t="str">
+        <x:v>[['냉면사리', '1', '인분(180g)'], ['오이', '40', 'g'], ['무절임', '40', 'g'], ['삶은 계란', '1/2', '개(25g)'], ['고추장', '20', 'g'], ['식초', '15', 'ml(1큰술)'], ['설탕', '12', 'g(1큰술)'], ['진간장', '7.5', 'ml(1/2큰술)'], ['고춧가루', '2', 'g'], ['참기름', '5', 'ml(1작은술)'], ['냉면육수', '50', 'ml'], ['통깨', '1', 'g']]</x:v>
+      </x:c>
+      <x:c r="J103" s="5" t="str">
+        <x:v>1인분</x:v>
+      </x:c>
+      <x:c r="K103" s="5" t="str">
+        <x:v>초급</x:v>
+      </x:c>
+      <x:c r="L103" s="5" t="str">
+        <x:v>15분이내</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="104" ht="22" customHeight="1">
+      <x:c r="A104" s="4" t="n">
+        <x:v>7009</x:v>
+      </x:c>
+      <x:c r="B104" s="4" t="str">
+        <x:v>알리오 올리오</x:v>
+      </x:c>
+      <x:c r="C104" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D104" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E104" s="5" t="str">
+        <x:v>파스타</x:v>
+      </x:c>
+      <x:c r="F104" s="5" t="str">
+        <x:v>든든한 한 끼|야식</x:v>
+      </x:c>
+      <x:c r="G104" s="5" t="str">
+        <x:v>스파게티면|마늘</x:v>
+      </x:c>
+      <x:c r="H104" s="5" t="str">
+        <x:v>면</x:v>
+      </x:c>
+      <x:c r="I104" s="5" t="str">
+        <x:v>[['스파게티면', '100', 'g'], ['마늘', '6', '쪽(30g)'], ['올리브유', '30', 'ml(2큰술)'], ['페페론치노', '2', '개(0.5g, 선택)'], ['소금', '8', 'g(면 삶는 물용)'], ['면수', '100', 'ml'], ['후추', '0.1', 'g'], ['파슬리가루', '0.2', 'g(선택)']]</x:v>
+      </x:c>
+      <x:c r="J104" s="5" t="str">
+        <x:v>1인분</x:v>
+      </x:c>
+      <x:c r="K104" s="5" t="str">
+        <x:v>초급</x:v>
+      </x:c>
+      <x:c r="L104" s="5" t="str">
+        <x:v>20분이내</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="105" ht="22" customHeight="1">
+      <x:c r="A105" s="4" t="n">
+        <x:v>7010</x:v>
+      </x:c>
+      <x:c r="B105" s="4" t="str">
+        <x:v>어묵 우동</x:v>
+      </x:c>
+      <x:c r="C105" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D105" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E105" s="5" t="str">
+        <x:v>우동</x:v>
+      </x:c>
+      <x:c r="F105" s="5" t="str">
+        <x:v>15분 이하|냄비 하나|든든한 한 끼|야식</x:v>
+      </x:c>
+      <x:c r="G105" s="5" t="str">
+        <x:v>우동면|어묵</x:v>
+      </x:c>
+      <x:c r="H105" s="5" t="str">
+        <x:v>면</x:v>
+      </x:c>
+      <x:c r="I105" s="5" t="str">
+        <x:v>[['냉동 우동면', '1', '개(200g)'], ['사각어묵', '2', '장(100g)'], ['대파', '15', 'g'], ['물', '550', 'ml'], ['국간장', '10', 'ml(2작은술)'], ['진간장', '5', 'ml(1작은술)'], ['설탕', '2', 'g'], ['다진 마늘', '2', 'g'], ['김가루', '2', 'g(선택)']]</x:v>
+      </x:c>
+      <x:c r="J105" s="5" t="str">
+        <x:v>1인분</x:v>
+      </x:c>
+      <x:c r="K105" s="5" t="str">
+        <x:v>초급</x:v>
+      </x:c>
+      <x:c r="L105" s="5" t="str">
+        <x:v>13분이내</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="106" ht="22" customHeight="1">
+      <x:c r="A106" s="4" t="n">
+        <x:v>7011</x:v>
+      </x:c>
+      <x:c r="B106" s="4" t="str">
+        <x:v>열무 비빔국수</x:v>
+      </x:c>
+      <x:c r="C106" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D106" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E106" s="5" t="str">
+        <x:v>국수</x:v>
+      </x:c>
+      <x:c r="F106" s="5" t="str">
+        <x:v>15분 이하|냄비 하나|든든한 한 끼|야식</x:v>
+      </x:c>
+      <x:c r="G106" s="5" t="str">
+        <x:v>소면|열무김치|열무김치국물</x:v>
+      </x:c>
+      <x:c r="H106" s="5" t="str">
+        <x:v>면</x:v>
+      </x:c>
+      <x:c r="I106" s="5" t="str">
+        <x:v>[['소면', '100', 'g'], ['열무김치', '120', 'g'], ['열무김치국물', '30', 'ml'], ['오이', '40', 'g'], ['고추장', '10', 'g(2작은술)'], ['식초', '10', 'ml(2작은술)'], ['설탕', '8', 'g(2작은술)'], ['참기름', '5', 'ml(1작은술)'], ['통깨', '2', 'g']]</x:v>
+      </x:c>
+      <x:c r="J106" s="5" t="str">
+        <x:v>1인분</x:v>
+      </x:c>
+      <x:c r="K106" s="5" t="str">
+        <x:v>초급</x:v>
+      </x:c>
+      <x:c r="L106" s="5" t="str">
+        <x:v>15분이내</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="107" ht="22" customHeight="1">
+      <x:c r="A107" s="4" t="n">
+        <x:v>7012</x:v>
+      </x:c>
+      <x:c r="B107" s="4" t="str">
+        <x:v>잔치국수</x:v>
+      </x:c>
+      <x:c r="C107" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D107" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E107" s="5" t="str">
+        <x:v>국수</x:v>
+      </x:c>
+      <x:c r="F107" s="5" t="str">
+        <x:v>든든한 한 끼|야식</x:v>
+      </x:c>
+      <x:c r="G107" s="5" t="str">
+        <x:v>소면|애호박|당근</x:v>
+      </x:c>
+      <x:c r="H107" s="5" t="str">
+        <x:v>면</x:v>
+      </x:c>
+      <x:c r="I107" s="5" t="str">
+        <x:v>[['소면', '100', 'g'], ['애호박', '50', 'g'], ['당근', '20', 'g'], ['계란', '1', '개(50g)'], ['대파', '10', 'g'], ['김가루', '2', 'g'], ['물', '650', 'ml'], ['국물용 멸치', '7', '마리(12g)'], ['국간장', '10', 'ml(2작은술)'], ['진간장', '5', 'ml(1작은술)'], ['소금', '0.5', 'g'], ['식용유', '2.5', 'ml']]</x:v>
+      </x:c>
+      <x:c r="J107" s="5" t="str">
+        <x:v>1인분</x:v>
+      </x:c>
+      <x:c r="K107" s="5" t="str">
+        <x:v>중급</x:v>
+      </x:c>
+      <x:c r="L107" s="5" t="str">
+        <x:v>25분이내</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="108" ht="22" customHeight="1">
+      <x:c r="A108" s="4" t="n">
+        <x:v>7013</x:v>
+      </x:c>
+      <x:c r="B108" s="4" t="str">
+        <x:v>쫄면</x:v>
+      </x:c>
+      <x:c r="C108" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D108" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E108" s="5" t="str">
+        <x:v>쫄면</x:v>
+      </x:c>
+      <x:c r="F108" s="5" t="str">
+        <x:v>냄비 하나|든든한 한 끼|야식</x:v>
+      </x:c>
+      <x:c r="G108" s="5" t="str">
+        <x:v>쫄면|양배추|오이</x:v>
+      </x:c>
+      <x:c r="H108" s="5" t="str">
+        <x:v>면</x:v>
+      </x:c>
+      <x:c r="I108" s="5" t="str">
+        <x:v>[['쫄면사리', '200', 'g'], ['양배추', '70', 'g'], ['오이', '50', 'g'], ['당근', '20', 'g'], ['콩나물', '70', 'g'], ['삶은 계란', '1/2', '개(25g)'], ['고추장', '20', 'g'], ['식초', '20', 'ml'], ['설탕', '12', 'g'], ['진간장', '5', 'ml'], ['고춧가루', '2', 'g'], ['참기름', '5', 'ml'], ['통깨', '2', 'g']]</x:v>
+      </x:c>
+      <x:c r="J108" s="5" t="str">
+        <x:v>1인분</x:v>
+      </x:c>
+      <x:c r="K108" s="5" t="str">
+        <x:v>초급</x:v>
+      </x:c>
+      <x:c r="L108" s="5" t="str">
+        <x:v>20분이내</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="109" ht="22" customHeight="1">
+      <x:c r="A109" s="4" t="n">
+        <x:v>7014</x:v>
+      </x:c>
+      <x:c r="B109" s="4" t="str">
+        <x:v>크림파스타</x:v>
+      </x:c>
+      <x:c r="C109" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D109" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E109" s="5" t="str">
+        <x:v>파스타</x:v>
+      </x:c>
+      <x:c r="F109" s="5" t="str">
+        <x:v>든든한 한 끼|야식</x:v>
+      </x:c>
+      <x:c r="G109" s="5" t="str">
+        <x:v>스파게티면|우유·생크림|베이컨</x:v>
+      </x:c>
+      <x:c r="H109" s="5" t="str">
+        <x:v>면</x:v>
+      </x:c>
+      <x:c r="I109" s="5" t="str">
+        <x:v>[['스파게티면', '100', 'g'], ['우유', '200', 'ml'], ['생크림', '80', 'ml(없으면 우유 80ml 추가)'], ['베이컨', '50', 'g'], ['양파', '1/4', '개(50g)'], ['다진 마늘', '5', 'g'], ['버터', '10', 'g'], ['소금', '8', 'g(면 삶는 물용)'], ['파르메산 치즈', '15', 'g'], ['후추', '0.1', 'g'], ['면수', '50', 'ml']]</x:v>
+      </x:c>
+      <x:c r="J109" s="5" t="str">
+        <x:v>1인분</x:v>
+      </x:c>
+      <x:c r="K109" s="5" t="str">
+        <x:v>초급</x:v>
+      </x:c>
+      <x:c r="L109" s="5" t="str">
+        <x:v>22분이내</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="110" ht="22" customHeight="1">
+      <x:c r="A110" s="4" t="n">
+        <x:v>7015</x:v>
+      </x:c>
+      <x:c r="B110" s="4" t="str">
+        <x:v>토마토파스타</x:v>
+      </x:c>
+      <x:c r="C110" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D110" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E110" s="5" t="str">
+        <x:v>파스타</x:v>
+      </x:c>
+      <x:c r="F110" s="5" t="str">
+        <x:v>든든한 한 끼|야식</x:v>
+      </x:c>
+      <x:c r="G110" s="5" t="str">
+        <x:v>스파게티면|토마토소스|베이컨·다진고기</x:v>
+      </x:c>
+      <x:c r="H110" s="5" t="str">
+        <x:v>면</x:v>
+      </x:c>
+      <x:c r="I110" s="5" t="str">
+        <x:v>[['스파게티면', '100', 'g'], ['시판 토마토소스', '150', 'g'], ['양파', '1/4', '개(50g)'], ['다진 마늘', '5', 'g'], ['베이컨 또는 다진 고기', '60', 'g(선택)'], ['올리브유', '10', 'ml'], ['소금', '8', 'g(면 삶는 물용)'], ['면수', '80', 'ml'], ['후추', '0.1', 'g'], ['파르메산 치즈', '10', 'g(선택)']]</x:v>
+      </x:c>
+      <x:c r="J110" s="5" t="str">
+        <x:v>1인분</x:v>
+      </x:c>
+      <x:c r="K110" s="5" t="str">
+        <x:v>초급</x:v>
+      </x:c>
+      <x:c r="L110" s="5" t="str">
+        <x:v>20분이내</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="111" ht="22" customHeight="1">
+      <x:c r="A111" s="4" t="n">
+        <x:v>7016</x:v>
+      </x:c>
+      <x:c r="B111" s="4" t="str">
+        <x:v>해장라면</x:v>
+      </x:c>
+      <x:c r="C111" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D111" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E111" s="5" t="str">
+        <x:v>라면</x:v>
+      </x:c>
+      <x:c r="F111" s="5" t="str">
+        <x:v>10분 이하|냄비 하나|설거지 적음|든든한 한 끼|야식</x:v>
+      </x:c>
+      <x:c r="G111" s="5" t="str">
+        <x:v>라면|콩나물|김치</x:v>
+      </x:c>
+      <x:c r="H111" s="5" t="str">
+        <x:v>면</x:v>
+      </x:c>
+      <x:c r="I111" s="5" t="str">
+        <x:v>[['봉지라면', '1', '개(면과 수프)'], ['물', '550', 'ml 또는 제품 표시량'], ['콩나물', '100', 'g'], ['대파', '15', 'g'], ['배추김치', '60', 'g'], ['계란', '1', '개(선택)'], ['고춧가루', '1', 'g(선택)']]</x:v>
+      </x:c>
+      <x:c r="J111" s="5" t="str">
+        <x:v>1인분</x:v>
+      </x:c>
+      <x:c r="K111" s="5" t="str">
+        <x:v>초급</x:v>
+      </x:c>
+      <x:c r="L111" s="5" t="str">
+        <x:v>10분이내</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="112" ht="22" customHeight="1">
+      <x:c r="A112" s="4" t="n">
+        <x:v>8001</x:v>
+      </x:c>
+      <x:c r="B112" s="4" t="str">
+        <x:v>간장 닭조림</x:v>
+      </x:c>
+      <x:c r="C112" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D112" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E112" s="5" t="str">
+        <x:v>조림</x:v>
+      </x:c>
+      <x:c r="F112" s="5" t="str">
+        <x:v>도시락 가능|든든한 한 끼|밥반찬</x:v>
+      </x:c>
+      <x:c r="G112" s="5" t="str">
+        <x:v>닭다리살|감자|양파</x:v>
+      </x:c>
+      <x:c r="H112" s="5" t="str">
+        <x:v>메인요리</x:v>
+      </x:c>
+      <x:c r="I112" s="5" t="str">
+        <x:v>[['닭다리살', '180', 'g'], ['감자', '1/2', '개(100g)'], ['양파', '1/4', '개(50g)'], ['물', '150', 'ml'], ['진간장', '20', 'ml(1큰술+1작은술)'], ['설탕', '6', 'g(1/2큰술)'], ['맛술', '10', 'ml(2작은술)'], ['다진 마늘', '5', 'g(1작은술)'], ['식용유', '5', 'ml(1작은술)'], ['후추', '0.1', 'g']]</x:v>
+      </x:c>
+      <x:c r="J112" s="5" t="str">
+        <x:v>1인분</x:v>
+      </x:c>
+      <x:c r="K112" s="5" t="str">
+        <x:v>중급</x:v>
+      </x:c>
+      <x:c r="L112" s="5" t="str">
+        <x:v>30분이내</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="113" ht="22" customHeight="1">
+      <x:c r="A113" s="4" t="n">
+        <x:v>8002</x:v>
+      </x:c>
+      <x:c r="B113" s="4" t="str">
+        <x:v>고등어 무조림</x:v>
+      </x:c>
+      <x:c r="C113" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D113" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E113" s="5" t="str">
+        <x:v>조림</x:v>
+      </x:c>
+      <x:c r="F113" s="5" t="str">
+        <x:v>냄비 하나|도시락 가능|냉동 가능|든든한 한 끼|밥반찬</x:v>
+      </x:c>
+      <x:c r="G113" s="5" t="str">
+        <x:v>고등어|무</x:v>
+      </x:c>
+      <x:c r="H113" s="5" t="str">
+        <x:v>메인요리</x:v>
+      </x:c>
+      <x:c r="I113" s="5" t="str">
+        <x:v>[['손질 고등어', '1', '토막(180g)'], ['무', '150', 'g'], ['대파', '15', 'g'], ['물', '250', 'ml'], ['고춧가루', '7', 'g(1큰술)'], ['진간장', '20', 'ml(1큰술+1작은술)'], ['고추장', '10', 'g(2작은술)'], ['설탕', '5', 'g(1작은술)'], ['맛술', '15', 'ml(1큰술)'], ['다진 마늘', '5', 'g(1작은술)'], ['생강가루', '0.2', 'g(선택)']]</x:v>
+      </x:c>
+      <x:c r="J113" s="5" t="str">
+        <x:v>1인분</x:v>
+      </x:c>
+      <x:c r="K113" s="5" t="str">
+        <x:v>중급</x:v>
+      </x:c>
+      <x:c r="L113" s="5" t="str">
+        <x:v>35분이내</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="114" ht="22" customHeight="1">
+      <x:c r="A114" s="4" t="n">
+        <x:v>8003</x:v>
+      </x:c>
+      <x:c r="B114" s="4" t="str">
+        <x:v>고등어구이</x:v>
+      </x:c>
+      <x:c r="C114" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D114" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E114" s="5" t="str">
+        <x:v>구이</x:v>
+      </x:c>
+      <x:c r="F114" s="5" t="str">
+        <x:v>재료 5개 이하|원팬 요리|칼 없이 가능|설거지 적음|도시락 가능|든든한 한 끼|밥반찬</x:v>
+      </x:c>
+      <x:c r="G114" s="5" t="str">
+        <x:v>고등어</x:v>
+      </x:c>
+      <x:c r="H114" s="5" t="str">
+        <x:v>메인요리</x:v>
+      </x:c>
+      <x:c r="I114" s="5" t="str">
+        <x:v>[['손질 고등어', '1', '토막(180g)'], ['소금', '0.8', 'g'], ['식용유', '5', 'ml(1작은술)'], ['레몬즙', '5', 'ml(1작은술, 선택)']]</x:v>
+      </x:c>
+      <x:c r="J114" s="5" t="str">
+        <x:v>1인분</x:v>
+      </x:c>
+      <x:c r="K114" s="5" t="str">
+        <x:v>초급</x:v>
+      </x:c>
+      <x:c r="L114" s="5" t="str">
+        <x:v>18분이내</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="115" ht="22" customHeight="1">
+      <x:c r="A115" s="4" t="n">
+        <x:v>8004</x:v>
+      </x:c>
+      <x:c r="B115" s="4" t="str">
+        <x:v>닭가슴살 채소볶음</x:v>
+      </x:c>
+      <x:c r="C115" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D115" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E115" s="5" t="str">
+        <x:v>볶음</x:v>
+      </x:c>
+      <x:c r="F115" s="5" t="str">
+        <x:v>원팬 요리|설거지 적음|도시락 가능|든든한 한 끼|밥반찬|남은 재료 활용</x:v>
+      </x:c>
+      <x:c r="G115" s="5" t="str">
+        <x:v>닭가슴살|양배추|양파</x:v>
+      </x:c>
+      <x:c r="H115" s="5" t="str">
+        <x:v>메인요리</x:v>
+      </x:c>
+      <x:c r="I115" s="5" t="str">
+        <x:v>[['닭가슴살', '150', 'g'], ['양배추', '80', 'g'], ['양파', '1/4', '개(50g)'], ['파프리카', '50', 'g'], ['식용유', '10', 'ml(2작은술)'], ['굴소스', '10', 'ml(2작은술)'], ['진간장', '5', 'ml(1작은술)'], ['다진 마늘', '3', 'g'], ['후추', '0.1', 'g'], ['물', '15', 'ml(1큰술)']]</x:v>
+      </x:c>
+      <x:c r="J115" s="5" t="str">
+        <x:v>1인분</x:v>
+      </x:c>
+      <x:c r="K115" s="5" t="str">
+        <x:v>초급</x:v>
+      </x:c>
+      <x:c r="L115" s="5" t="str">
+        <x:v>18분이내</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="116" ht="22" customHeight="1">
+      <x:c r="A116" s="4" t="n">
+        <x:v>8005</x:v>
+      </x:c>
+      <x:c r="B116" s="4" t="str">
+        <x:v>닭갈비</x:v>
+      </x:c>
+      <x:c r="C116" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D116" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E116" s="5" t="str">
+        <x:v>볶음</x:v>
+      </x:c>
+      <x:c r="F116" s="5" t="str">
+        <x:v>원팬 요리|도시락 가능|든든한 한 끼|밥반찬</x:v>
+      </x:c>
+      <x:c r="G116" s="5" t="str">
+        <x:v>닭다리살|양배추|양파</x:v>
+      </x:c>
+      <x:c r="H116" s="5" t="str">
+        <x:v>메인요리</x:v>
+      </x:c>
+      <x:c r="I116" s="5" t="str">
+        <x:v>[['닭다리살', '180', 'g'], ['양배추', '120', 'g'], ['양파', '1/4', '개(50g)'], ['고구마', '80', 'g'], ['대파', '20', 'g'], ['식용유', '5', 'ml(1작은술)'], ['고추장', '20', 'g(1큰술)'], ['고춧가루', '4', 'g(2작은술)'], ['진간장', '10', 'ml(2작은술)'], ['설탕', '8', 'g(2작은술)'], ['맛술', '10', 'ml(2작은술)'], ['다진 마늘', '5', 'g(1작은술)'], ['물', '30', 'ml']]</x:v>
+      </x:c>
+      <x:c r="J116" s="5" t="str">
+        <x:v>1인분</x:v>
+      </x:c>
+      <x:c r="K116" s="5" t="str">
+        <x:v>중급</x:v>
+      </x:c>
+      <x:c r="L116" s="5" t="str">
+        <x:v>25분이내</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="117" ht="22" customHeight="1">
+      <x:c r="A117" s="4" t="n">
+        <x:v>8006</x:v>
+      </x:c>
+      <x:c r="B117" s="4" t="str">
+        <x:v>닭다리살 구이</x:v>
+      </x:c>
+      <x:c r="C117" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D117" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E117" s="5" t="str">
+        <x:v>구이</x:v>
+      </x:c>
+      <x:c r="F117" s="5" t="str">
+        <x:v>원팬 요리|칼 없이 가능|설거지 적음|도시락 가능|든든한 한 끼|밥반찬</x:v>
+      </x:c>
+      <x:c r="G117" s="5" t="str">
+        <x:v>닭다리살</x:v>
+      </x:c>
+      <x:c r="H117" s="5" t="str">
+        <x:v>메인요리</x:v>
+      </x:c>
+      <x:c r="I117" s="5" t="str">
+        <x:v>[['닭다리살', '200', 'g'], ['소금', '1.5', 'g'], ['후추', '0.1', 'g'], ['식용유', '5', 'ml(1작은술)'], ['다진 마늘', '3', 'g'], ['레몬즙', '5', 'ml(1작은술, 선택)']]</x:v>
+      </x:c>
+      <x:c r="J117" s="5" t="str">
+        <x:v>1인분</x:v>
+      </x:c>
+      <x:c r="K117" s="5" t="str">
+        <x:v>초급</x:v>
+      </x:c>
+      <x:c r="L117" s="5" t="str">
+        <x:v>20분이내</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="118" ht="22" customHeight="1">
+      <x:c r="A118" s="4" t="n">
+        <x:v>8007</x:v>
+      </x:c>
+      <x:c r="B118" s="4" t="str">
+        <x:v>닭볶음탕</x:v>
+      </x:c>
+      <x:c r="C118" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D118" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E118" s="5" t="str">
+        <x:v>찜·조림</x:v>
+      </x:c>
+      <x:c r="F118" s="5" t="str">
+        <x:v>냄비 하나|도시락 가능|냉동 가능|든든한 한 끼|밥반찬|남은 재료 활용</x:v>
+      </x:c>
+      <x:c r="G118" s="5" t="str">
+        <x:v>닭고기|감자|당근</x:v>
+      </x:c>
+      <x:c r="H118" s="5" t="str">
+        <x:v>메인요리</x:v>
+      </x:c>
+      <x:c r="I118" s="5" t="str">
+        <x:v>[['볶음탕용 닭', '350', 'g'], ['감자', '1', '개(180g)'], ['당근', '50', 'g'], ['양파', '1/2', '개(100g)'], ['대파', '20', 'g'], ['물', '400', 'ml'], ['고추장', '25', 'g(1큰술+1작은술)'], ['고춧가루', '7', 'g(1큰술)'], ['진간장', '25', 'ml(1큰술+2작은술)'], ['설탕', '10', 'g(2작은술)'], ['맛술', '15', 'ml(1큰술)'], ['다진 마늘', '7', 'g(1/2큰술)'], ['후추', '0.1', 'g']]</x:v>
+      </x:c>
+      <x:c r="J118" s="5" t="str">
+        <x:v>1인분</x:v>
+      </x:c>
+      <x:c r="K118" s="5" t="str">
+        <x:v>중급</x:v>
+      </x:c>
+      <x:c r="L118" s="5" t="str">
+        <x:v>40분이내</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="119" ht="22" customHeight="1">
+      <x:c r="A119" s="4" t="n">
+        <x:v>8008</x:v>
+      </x:c>
+      <x:c r="B119" s="4" t="str">
+        <x:v>대패삼겹살 숙주볶음</x:v>
+      </x:c>
+      <x:c r="C119" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D119" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E119" s="5" t="str">
+        <x:v>볶음</x:v>
+      </x:c>
+      <x:c r="F119" s="5" t="str">
+        <x:v>15분 이하|원팬 요리|설거지 적음|도시락 가능|든든한 한 끼|밥반찬|남은 재료 활용</x:v>
+      </x:c>
+      <x:c r="G119" s="5" t="str">
+        <x:v>대패삼겹살|숙주|양파</x:v>
+      </x:c>
+      <x:c r="H119" s="5" t="str">
+        <x:v>메인요리</x:v>
+      </x:c>
+      <x:c r="I119" s="5" t="str">
+        <x:v>[['대패삼겹살', '150', 'g'], ['숙주', '180', 'g'], ['양파', '1/4', '개(50g)'], ['대파', '20', 'g'], ['진간장', '10', 'ml(2작은술)'], ['굴소스', '10', 'ml(2작은술)'], ['다진 마늘', '3', 'g'], ['설탕', '2', 'g(1/2작은술)'], ['후추', '0.1', 'g'], ['참기름', '2.5', 'ml(1/2작은술)']]</x:v>
+      </x:c>
+      <x:c r="J119" s="5" t="str">
+        <x:v>1인분</x:v>
+      </x:c>
+      <x:c r="K119" s="5" t="str">
+        <x:v>초급</x:v>
+      </x:c>
+      <x:c r="L119" s="5" t="str">
+        <x:v>15분이내</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="120" ht="22" customHeight="1">
+      <x:c r="A120" s="4" t="n">
+        <x:v>8009</x:v>
+      </x:c>
+      <x:c r="B120" s="4" t="str">
+        <x:v>돼지고기 김치볶음</x:v>
+      </x:c>
+      <x:c r="C120" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D120" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E120" s="5" t="str">
+        <x:v>볶음</x:v>
+      </x:c>
+      <x:c r="F120" s="5" t="str">
+        <x:v>원팬 요리|설거지 적음|도시락 가능|든든한 한 끼|밥반찬|남은 재료 활용</x:v>
+      </x:c>
+      <x:c r="G120" s="5" t="str">
+        <x:v>돼지고기|김치|양파</x:v>
+      </x:c>
+      <x:c r="H120" s="5" t="str">
+        <x:v>메인요리</x:v>
+      </x:c>
+      <x:c r="I120" s="5" t="str">
+        <x:v>[['돼지고기 앞다리살', '150', 'g'], ['배추김치', '150', 'g'], ['양파', '1/4', '개(50g)'], ['대파', '15', 'g'], ['식용유', '5', 'ml(1작은술)'], ['고춧가루', '2', 'g(1작은술)'], ['진간장', '5', 'ml(1작은술)'], ['설탕', '5', 'g(1작은술)'], ['다진 마늘', '3', 'g'], ['참기름', '2.5', 'ml(1/2작은술)'], ['통깨', '1', 'g']]</x:v>
+      </x:c>
+      <x:c r="J120" s="5" t="str">
+        <x:v>1인분</x:v>
+      </x:c>
+      <x:c r="K120" s="5" t="str">
+        <x:v>초급</x:v>
+      </x:c>
+      <x:c r="L120" s="5" t="str">
+        <x:v>18분이내</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="121" ht="22" customHeight="1">
+      <x:c r="A121" s="4" t="n">
+        <x:v>8010</x:v>
+      </x:c>
+      <x:c r="B121" s="4" t="str">
+        <x:v>돼지고기 김치찜</x:v>
+      </x:c>
+      <x:c r="C121" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D121" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E121" s="5" t="str">
+        <x:v>찜·조림</x:v>
+      </x:c>
+      <x:c r="F121" s="5" t="str">
+        <x:v>냄비 하나|도시락 가능|냉동 가능|든든한 한 끼|밥반찬</x:v>
+      </x:c>
+      <x:c r="G121" s="5" t="str">
+        <x:v>돼지고기|김치|양파</x:v>
+      </x:c>
+      <x:c r="H121" s="5" t="str">
+        <x:v>메인요리</x:v>
+      </x:c>
+      <x:c r="I121" s="5" t="str">
+        <x:v>[['돼지고기 목살 또는 앞다리살', '220', 'g'], ['배추김치', '250', 'g'], ['양파', '1/2', '개(100g)'], ['대파', '20', 'g'], ['물', '300', 'ml'], ['김치국물', '50', 'ml'], ['고춧가루', '5', 'g(2작은술)'], ['진간장', '10', 'ml(2작은술)'], ['설탕', '5', 'g(1작은술)'], ['다진 마늘', '5', 'g(1작은술)'], ['맛술', '15', 'ml(1큰술)']]</x:v>
+      </x:c>
+      <x:c r="J121" s="5" t="str">
+        <x:v>1인분</x:v>
+      </x:c>
+      <x:c r="K121" s="5" t="str">
+        <x:v>중급</x:v>
+      </x:c>
+      <x:c r="L121" s="5" t="str">
+        <x:v>45분이내</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="122" ht="22" customHeight="1">
+      <x:c r="A122" s="4" t="n">
+        <x:v>8011</x:v>
+      </x:c>
+      <x:c r="B122" s="4" t="str">
+        <x:v>돼지불고기</x:v>
+      </x:c>
+      <x:c r="C122" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D122" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E122" s="5" t="str">
+        <x:v>볶음</x:v>
+      </x:c>
+      <x:c r="F122" s="5" t="str">
+        <x:v>원팬 요리|도시락 가능|든든한 한 끼|밥반찬</x:v>
+      </x:c>
+      <x:c r="G122" s="5" t="str">
+        <x:v>돼지고기|양파|당근</x:v>
+      </x:c>
+      <x:c r="H122" s="5" t="str">
+        <x:v>메인요리</x:v>
+      </x:c>
+      <x:c r="I122" s="5" t="str">
+        <x:v>[['돼지고기 앞다리살 불고기용', '180', 'g'], ['양파', '1/4', '개(50g)'], ['대파', '20', 'g'], ['당근', '25', 'g'], ['식용유', '5', 'ml(1작은술)'], ['진간장', '20', 'ml(1큰술+1작은술)'], ['설탕', '8', 'g(2작은술)'], ['맛술', '15', 'ml(1큰술)'], ['다진 마늘', '5', 'g(1작은술)'], ['참기름', '5', 'ml(1작은술)'], ['후추', '0.1', 'g'], ['통깨', '1', 'g']]</x:v>
+      </x:c>
+      <x:c r="J122" s="5" t="str">
+        <x:v>1인분</x:v>
+      </x:c>
+      <x:c r="K122" s="5" t="str">
+        <x:v>초급</x:v>
+      </x:c>
+      <x:c r="L122" s="5" t="str">
+        <x:v>20분이내</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="123" ht="22" customHeight="1">
+      <x:c r="A123" s="4" t="n">
+        <x:v>8012</x:v>
+      </x:c>
+      <x:c r="B123" s="4" t="str">
+        <x:v>두부강정</x:v>
+      </x:c>
+      <x:c r="C123" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D123" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E123" s="5" t="str">
+        <x:v>강정</x:v>
+      </x:c>
+      <x:c r="F123" s="5" t="str">
+        <x:v>원팬 요리|도시락 가능|든든한 한 끼|밥반찬</x:v>
+      </x:c>
+      <x:c r="G123" s="5" t="str">
+        <x:v>두부</x:v>
+      </x:c>
+      <x:c r="H123" s="5" t="str">
+        <x:v>메인요리</x:v>
+      </x:c>
+      <x:c r="I123" s="5" t="str">
+        <x:v>[['부침용 두부', '250', 'g'], ['전분', '25', 'g(2큰술)'], ['식용유', '15', 'ml(1큰술)'], ['고추장', '15', 'g(1큰술)'], ['케첩', '15', 'g(1큰술)'], ['올리고당', '15', 'g(1큰술)'], ['진간장', '5', 'ml(1작은술)'], ['물', '15', 'ml(1큰술)'], ['다진 마늘', '2', 'g'], ['통깨', '1', 'g']]</x:v>
+      </x:c>
+      <x:c r="J123" s="5" t="str">
+        <x:v>1인분</x:v>
+      </x:c>
+      <x:c r="K123" s="5" t="str">
+        <x:v>초급</x:v>
+      </x:c>
+      <x:c r="L123" s="5" t="str">
+        <x:v>22분이내</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="124" ht="22" customHeight="1">
+      <x:c r="A124" s="4" t="n">
+        <x:v>8013</x:v>
+      </x:c>
+      <x:c r="B124" s="4" t="str">
+        <x:v>두부김치</x:v>
+      </x:c>
+      <x:c r="C124" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D124" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E124" s="5" t="str">
+        <x:v>두부 요리</x:v>
+      </x:c>
+      <x:c r="F124" s="5" t="str">
+        <x:v>도시락 가능|든든한 한 끼|밥반찬</x:v>
+      </x:c>
+      <x:c r="G124" s="5" t="str">
+        <x:v>두부|김치|돼지고기</x:v>
+      </x:c>
+      <x:c r="H124" s="5" t="str">
+        <x:v>메인요리</x:v>
+      </x:c>
+      <x:c r="I124" s="5" t="str">
+        <x:v>[['부침용 두부', '250', 'g'], ['배추김치', '180', 'g'], ['돼지고기 앞다리살', '100', 'g(선택)'], ['양파', '1/4', '개(50g)'], ['대파', '15', 'g'], ['식용유', '5', 'ml(1작은술)'], ['고춧가루', '2', 'g(1작은술)'], ['설탕', '5', 'g(1작은술)'], ['진간장', '5', 'ml(1작은술)'], ['참기름', '5', 'ml(1작은술)'], ['통깨', '1', 'g']]</x:v>
+      </x:c>
+      <x:c r="J124" s="5" t="str">
+        <x:v>1인분</x:v>
+      </x:c>
+      <x:c r="K124" s="5" t="str">
+        <x:v>초급</x:v>
+      </x:c>
+      <x:c r="L124" s="5" t="str">
+        <x:v>22분이내</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="125" ht="22" customHeight="1">
+      <x:c r="A125" s="4" t="n">
+        <x:v>8014</x:v>
+      </x:c>
+      <x:c r="B125" s="4" t="str">
+        <x:v>목살 스테이크</x:v>
+      </x:c>
+      <x:c r="C125" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D125" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E125" s="5" t="str">
+        <x:v>스테이크</x:v>
+      </x:c>
+      <x:c r="F125" s="5" t="str">
+        <x:v>원팬 요리|든든한 한 끼|밥반찬</x:v>
+      </x:c>
+      <x:c r="G125" s="5" t="str">
+        <x:v>돼지고기|양파</x:v>
+      </x:c>
+      <x:c r="H125" s="5" t="str">
+        <x:v>메인요리</x:v>
+      </x:c>
+      <x:c r="I125" s="5" t="str">
+        <x:v>[['돼지 목살', '200', 'g(두께 1.5cm)'], ['소금', '1.5', 'g'], ['후추', '0.1', 'g'], ['식용유', '10', 'ml(2작은술)'], ['버터', '10', 'g'], ['다진 마늘', '3', 'g'], ['진간장', '10', 'ml(2작은술)'], ['설탕', '3', 'g'], ['물', '30', 'ml'], ['양파', '50', 'g']]</x:v>
+      </x:c>
+      <x:c r="J125" s="5" t="str">
+        <x:v>1인분</x:v>
+      </x:c>
+      <x:c r="K125" s="5" t="str">
+        <x:v>중급</x:v>
+      </x:c>
+      <x:c r="L125" s="5" t="str">
+        <x:v>22분이내</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="126" ht="22" customHeight="1">
+      <x:c r="A126" s="4" t="n">
+        <x:v>8015</x:v>
+      </x:c>
+      <x:c r="B126" s="4" t="str">
+        <x:v>삼겹살구이</x:v>
+      </x:c>
+      <x:c r="C126" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D126" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E126" s="5" t="str">
+        <x:v>구이</x:v>
+      </x:c>
+      <x:c r="F126" s="5" t="str">
+        <x:v>원팬 요리|칼 없이 가능|든든한 한 끼|밥반찬</x:v>
+      </x:c>
+      <x:c r="G126" s="5" t="str">
+        <x:v>삼겹살|상추|김치</x:v>
+      </x:c>
+      <x:c r="H126" s="5" t="str">
+        <x:v>메인요리</x:v>
+      </x:c>
+      <x:c r="I126" s="5" t="str">
+        <x:v>[['삼겹살', '200', 'g'], ['소금', '1', 'g'], ['후추', '0.1', 'g'], ['마늘', '4', '쪽(20g)'], ['상추', '8', '장(80g)'], ['쌈장', '20', 'g(1큰술+1작은술)'], ['김치', '80', 'g(선택)']]</x:v>
+      </x:c>
+      <x:c r="J126" s="5" t="str">
+        <x:v>1인분</x:v>
+      </x:c>
+      <x:c r="K126" s="5" t="str">
+        <x:v>초급</x:v>
+      </x:c>
+      <x:c r="L126" s="5" t="str">
+        <x:v>18분이내</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="127" ht="22" customHeight="1">
+      <x:c r="A127" s="4" t="n">
+        <x:v>8016</x:v>
+      </x:c>
+      <x:c r="B127" s="4" t="str">
+        <x:v>새우 감바스</x:v>
+      </x:c>
+      <x:c r="C127" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D127" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E127" s="5" t="str">
+        <x:v>해산물 요리</x:v>
+      </x:c>
+      <x:c r="F127" s="5" t="str">
+        <x:v>원팬 요리|든든한 한 끼|야식|밥반찬</x:v>
+      </x:c>
+      <x:c r="G127" s="5" t="str">
+        <x:v>새우|마늘|식빵</x:v>
+      </x:c>
+      <x:c r="H127" s="5" t="str">
+        <x:v>메인요리</x:v>
+      </x:c>
+      <x:c r="I127" s="5" t="str">
+        <x:v>[['손질 냉동새우', '150', 'g'], ['올리브유', '70', 'ml'], ['마늘', '6', '쪽(30g)'], ['페페론치노', '2', '개(0.5g, 선택)'], ['소금', '1', 'g'], ['후추', '0.1', 'g'], ['파슬리가루', '0.2', 'g'], ['식빵', '2', '장(70g, 선택)']]</x:v>
+      </x:c>
+      <x:c r="J127" s="5" t="str">
+        <x:v>1인분</x:v>
+      </x:c>
+      <x:c r="K127" s="5" t="str">
+        <x:v>초급</x:v>
+      </x:c>
+      <x:c r="L127" s="5" t="str">
+        <x:v>18분이내</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="128" ht="22" customHeight="1">
+      <x:c r="A128" s="4" t="n">
+        <x:v>8017</x:v>
+      </x:c>
+      <x:c r="B128" s="4" t="str">
+        <x:v>소고기 불고기</x:v>
+      </x:c>
+      <x:c r="C128" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D128" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E128" s="5" t="str">
+        <x:v>볶음</x:v>
+      </x:c>
+      <x:c r="F128" s="5" t="str">
+        <x:v>원팬 요리|도시락 가능|든든한 한 끼|밥반찬</x:v>
+      </x:c>
+      <x:c r="G128" s="5" t="str">
+        <x:v>소고기|양파|당근</x:v>
+      </x:c>
+      <x:c r="H128" s="5" t="str">
+        <x:v>메인요리</x:v>
+      </x:c>
+      <x:c r="I128" s="5" t="str">
+        <x:v>[['소고기 불고기용', '180', 'g'], ['양파', '1/4', '개(50g)'], ['당근', '20', 'g'], ['대파', '20', 'g'], ['버섯', '60', 'g'], ['식용유', '5', 'ml'], ['진간장', '22.5', 'ml(1큰술+1/2큰술)'], ['설탕', '8', 'g'], ['맛술', '15', 'ml'], ['다진 마늘', '5', 'g'], ['참기름', '5', 'ml'], ['후추', '0.1', 'g']]</x:v>
+      </x:c>
+      <x:c r="J128" s="5" t="str">
+        <x:v>1인분</x:v>
+      </x:c>
+      <x:c r="K128" s="5" t="str">
+        <x:v>초급</x:v>
+      </x:c>
+      <x:c r="L128" s="5" t="str">
+        <x:v>20분이내</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="129" ht="22" customHeight="1">
+      <x:c r="A129" s="4" t="n">
+        <x:v>8018</x:v>
+      </x:c>
+      <x:c r="B129" s="4" t="str">
+        <x:v>소고기 숙주볶음</x:v>
+      </x:c>
+      <x:c r="C129" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D129" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E129" s="5" t="str">
+        <x:v>볶음</x:v>
+      </x:c>
+      <x:c r="F129" s="5" t="str">
+        <x:v>15분 이하|원팬 요리|설거지 적음|도시락 가능|든든한 한 끼|밥반찬|남은 재료 활용</x:v>
+      </x:c>
+      <x:c r="G129" s="5" t="str">
+        <x:v>소고기|숙주|양파</x:v>
+      </x:c>
+      <x:c r="H129" s="5" t="str">
+        <x:v>메인요리</x:v>
+      </x:c>
+      <x:c r="I129" s="5" t="str">
+        <x:v>[['소고기 불고기용', '150', 'g'], ['숙주', '180', 'g'], ['양파', '1/4', '개(50g)'], ['대파', '20', 'g'], ['식용유', '10', 'ml(2작은술)'], ['굴소스', '10', 'ml(2작은술)'], ['진간장', '7.5', 'ml(1/2큰술)'], ['설탕', '2', 'g'], ['다진 마늘', '3', 'g'], ['후추', '0.1', 'g'], ['참기름', '2.5', 'ml']]</x:v>
+      </x:c>
+      <x:c r="J129" s="5" t="str">
+        <x:v>1인분</x:v>
+      </x:c>
+      <x:c r="K129" s="5" t="str">
+        <x:v>초급</x:v>
+      </x:c>
+      <x:c r="L129" s="5" t="str">
+        <x:v>15분이내</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="130" ht="22" customHeight="1">
+      <x:c r="A130" s="4" t="n">
+        <x:v>8019</x:v>
+      </x:c>
+      <x:c r="B130" s="4" t="str">
+        <x:v>소고기 찹스테이크</x:v>
+      </x:c>
+      <x:c r="C130" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D130" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E130" s="5" t="str">
+        <x:v>스테이크</x:v>
+      </x:c>
+      <x:c r="F130" s="5" t="str">
+        <x:v>원팬 요리|도시락 가능|든든한 한 끼|밥반찬</x:v>
+      </x:c>
+      <x:c r="G130" s="5" t="str">
+        <x:v>소고기|양파|파프리카</x:v>
+      </x:c>
+      <x:c r="H130" s="5" t="str">
+        <x:v>메인요리</x:v>
+      </x:c>
+      <x:c r="I130" s="5" t="str">
+        <x:v>[['소고기 등심 또는 부채살', '180', 'g'], ['양파', '1/4', '개(50g)'], ['파프리카', '80', 'g'], ['새송이버섯', '60', 'g'], ['식용유', '10', 'ml(2작은술)'], ['소금', '1', 'g'], ['후추', '0.1', 'g'], ['케첩', '20', 'g(1큰술+1작은술)'], ['돈까스소스', '15', 'g(1큰술)'], ['진간장', '5', 'ml(1작은술)'], ['설탕', '3', 'g'], ['다진 마늘', '3', 'g'], ['물', '30', 'ml']]</x:v>
+      </x:c>
+      <x:c r="J130" s="5" t="str">
+        <x:v>1인분</x:v>
+      </x:c>
+      <x:c r="K130" s="5" t="str">
+        <x:v>중급</x:v>
+      </x:c>
+      <x:c r="L130" s="5" t="str">
+        <x:v>22분이내</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="131" ht="22" customHeight="1">
+      <x:c r="A131" s="4" t="n">
+        <x:v>8020</x:v>
+      </x:c>
+      <x:c r="B131" s="4" t="str">
+        <x:v>소시지 채소볶음</x:v>
+      </x:c>
+      <x:c r="C131" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D131" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E131" s="5" t="str">
+        <x:v>볶음</x:v>
+      </x:c>
+      <x:c r="F131" s="5" t="str">
+        <x:v>15분 이하|원팬 요리|설거지 적음|도시락 가능|든든한 한 끼|밥반찬|남은 재료 활용</x:v>
+      </x:c>
+      <x:c r="G131" s="5" t="str">
+        <x:v>소시지|양파|파프리카</x:v>
+      </x:c>
+      <x:c r="H131" s="5" t="str">
+        <x:v>메인요리</x:v>
+      </x:c>
+      <x:c r="I131" s="5" t="str">
+        <x:v>[['비엔나소시지', '150', 'g'], ['양파', '1/4', '개(50g)'], ['파프리카', '70', 'g'], ['양배추', '60', 'g'], ['식용유', '5', 'ml(1작은술)'], ['케첩', '25', 'g(1큰술+2작은술)'], ['굴소스', '5', 'ml(1작은술)'], ['설탕', '3', 'g'], ['다진 마늘', '2', 'g'], ['물', '15', 'ml'], ['후추', '0.1', 'g']]</x:v>
+      </x:c>
+      <x:c r="J131" s="5" t="str">
+        <x:v>1인분</x:v>
+      </x:c>
+      <x:c r="K131" s="5" t="str">
+        <x:v>초급</x:v>
+      </x:c>
+      <x:c r="L131" s="5" t="str">
+        <x:v>15분이내</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="132" ht="22" customHeight="1">
+      <x:c r="A132" s="4" t="n">
+        <x:v>8021</x:v>
+      </x:c>
+      <x:c r="B132" s="4" t="str">
+        <x:v>스테이크</x:v>
+      </x:c>
+      <x:c r="C132" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D132" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E132" s="5" t="str">
+        <x:v>스테이크</x:v>
+      </x:c>
+      <x:c r="F132" s="5" t="str">
+        <x:v>원팬 요리|칼 없이 가능|든든한 한 끼|밥반찬</x:v>
+      </x:c>
+      <x:c r="G132" s="5" t="str">
+        <x:v>소고기</x:v>
+      </x:c>
+      <x:c r="H132" s="5" t="str">
+        <x:v>메인요리</x:v>
+      </x:c>
+      <x:c r="I132" s="5" t="str">
+        <x:v>[['소고기 등심 또는 채끝', '200', 'g(두께 2cm)'], ['소금', '2', 'g'], ['후추', '0.2', 'g'], ['식용유', '10', 'ml(2작은술)'], ['버터', '15', 'g'], ['마늘', '3', '쪽(15g)'], ['로즈마리', '1', '줄기(선택)']]</x:v>
+      </x:c>
+      <x:c r="J132" s="5" t="str">
+        <x:v>1인분</x:v>
+      </x:c>
+      <x:c r="K132" s="5" t="str">
+        <x:v>중급</x:v>
+      </x:c>
+      <x:c r="L132" s="5" t="str">
+        <x:v>20분이내</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="133" ht="22" customHeight="1">
+      <x:c r="A133" s="4" t="n">
+        <x:v>8022</x:v>
+      </x:c>
+      <x:c r="B133" s="4" t="str">
+        <x:v>연어스테이크</x:v>
+      </x:c>
+      <x:c r="C133" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D133" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E133" s="5" t="str">
+        <x:v>스테이크</x:v>
+      </x:c>
+      <x:c r="F133" s="5" t="str">
+        <x:v>원팬 요리|칼 없이 가능|설거지 적음|든든한 한 끼|밥반찬</x:v>
+      </x:c>
+      <x:c r="G133" s="5" t="str">
+        <x:v>연어</x:v>
+      </x:c>
+      <x:c r="H133" s="5" t="str">
+        <x:v>메인요리</x:v>
+      </x:c>
+      <x:c r="I133" s="5" t="str">
+        <x:v>[['연어 필렛', '180', 'g'], ['소금', '1.2', 'g'], ['후추', '0.1', 'g'], ['식용유 또는 올리브유', '10', 'ml(2작은술)'], ['버터', '10', 'g'], ['다진 마늘', '2', 'g'], ['레몬즙', '10', 'ml(2작은술)'], ['파슬리가루', '0.2', 'g(선택)']]</x:v>
+      </x:c>
+      <x:c r="J133" s="5" t="str">
+        <x:v>1인분</x:v>
+      </x:c>
+      <x:c r="K133" s="5" t="str">
+        <x:v>초급</x:v>
+      </x:c>
+      <x:c r="L133" s="5" t="str">
+        <x:v>18분이내</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="134" ht="22" customHeight="1">
+      <x:c r="A134" s="4" t="n">
+        <x:v>8023</x:v>
+      </x:c>
+      <x:c r="B134" s="4" t="str">
+        <x:v>오리불고기</x:v>
+      </x:c>
+      <x:c r="C134" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D134" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E134" s="5" t="str">
+        <x:v>볶음</x:v>
+      </x:c>
+      <x:c r="F134" s="5" t="str">
+        <x:v>원팬 요리|도시락 가능|든든한 한 끼|밥반찬</x:v>
+      </x:c>
+      <x:c r="G134" s="5" t="str">
+        <x:v>오리고기|양파|양배추</x:v>
+      </x:c>
+      <x:c r="H134" s="5" t="str">
+        <x:v>메인요리</x:v>
+      </x:c>
+      <x:c r="I134" s="5" t="str">
+        <x:v>[['오리 슬라이스', '180', 'g'], ['양파', '1/4', '개(50g)'], ['양배추', '80', 'g'], ['대파', '20', 'g'], ['고추장', '20', 'g(1큰술)'], ['고춧가루', '4', 'g(2작은술)'], ['진간장', '10', 'ml(2작은술)'], ['설탕', '8', 'g(2작은술)'], ['맛술', '15', 'ml(1큰술)'], ['다진 마늘', '5', 'g'], ['후추', '0.1', 'g'], ['식용유', '2.5', 'ml(1/2작은술)']]</x:v>
+      </x:c>
+      <x:c r="J134" s="5" t="str">
+        <x:v>1인분</x:v>
+      </x:c>
+      <x:c r="K134" s="5" t="str">
+        <x:v>초급</x:v>
+      </x:c>
+      <x:c r="L134" s="5" t="str">
+        <x:v>22분이내</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="135" ht="22" customHeight="1">
+      <x:c r="A135" s="4" t="n">
+        <x:v>8024</x:v>
+      </x:c>
+      <x:c r="B135" s="4" t="str">
+        <x:v>오징어볶음</x:v>
+      </x:c>
+      <x:c r="C135" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D135" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E135" s="5" t="str">
+        <x:v>볶음</x:v>
+      </x:c>
+      <x:c r="F135" s="5" t="str">
+        <x:v>원팬 요리|설거지 적음|도시락 가능|든든한 한 끼|밥반찬|남은 재료 활용</x:v>
+      </x:c>
+      <x:c r="G135" s="5" t="str">
+        <x:v>오징어|양파|양배추</x:v>
+      </x:c>
+      <x:c r="H135" s="5" t="str">
+        <x:v>메인요리</x:v>
+      </x:c>
+      <x:c r="I135" s="5" t="str">
+        <x:v>[['손질 오징어', '200', 'g'], ['양파', '1/4', '개(50g)'], ['양배추', '80', 'g'], ['당근', '25', 'g'], ['대파', '20', 'g'], ['식용유', '10', 'ml'], ['고추장', '20', 'g'], ['고춧가루', '5', 'g'], ['진간장', '10', 'ml'], ['설탕', '8', 'g'], ['맛술', '10', 'ml'], ['다진 마늘', '5', 'g'], ['참기름', '2.5', 'ml'], ['통깨', '1', 'g']]</x:v>
+      </x:c>
+      <x:c r="J135" s="5" t="str">
+        <x:v>1인분</x:v>
+      </x:c>
+      <x:c r="K135" s="5" t="str">
+        <x:v>초급</x:v>
+      </x:c>
+      <x:c r="L135" s="5" t="str">
+        <x:v>18분이내</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="136" ht="22" customHeight="1">
+      <x:c r="A136" s="4" t="n">
+        <x:v>8025</x:v>
+      </x:c>
+      <x:c r="B136" s="4" t="str">
+        <x:v>제육볶음</x:v>
+      </x:c>
+      <x:c r="C136" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D136" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E136" s="5" t="str">
+        <x:v>볶음</x:v>
+      </x:c>
+      <x:c r="F136" s="5" t="str">
+        <x:v>원팬 요리|도시락 가능|든든한 한 끼|밥반찬|남은 재료 활용</x:v>
+      </x:c>
+      <x:c r="G136" s="5" t="str">
+        <x:v>돼지고기|양파|양배추</x:v>
+      </x:c>
+      <x:c r="H136" s="5" t="str">
+        <x:v>메인요리</x:v>
+      </x:c>
+      <x:c r="I136" s="5" t="str">
+        <x:v>[['돼지고기 앞다리살', '180', 'g'], ['양파', '1/4', '개(50g)'], ['양배추', '100', 'g'], ['대파', '20', 'g'], ['식용유', '10', 'ml'], ['고추장', '20', 'g'], ['고춧가루', '5', 'g'], ['진간장', '12.5', 'ml'], ['설탕', '8', 'g'], ['맛술', '15', 'ml'], ['다진 마늘', '5', 'g'], ['참기름', '2.5', 'ml'], ['통깨', '1', 'g']]</x:v>
+      </x:c>
+      <x:c r="J136" s="5" t="str">
+        <x:v>1인분</x:v>
+      </x:c>
+      <x:c r="K136" s="5" t="str">
+        <x:v>초급</x:v>
+      </x:c>
+      <x:c r="L136" s="5" t="str">
+        <x:v>20분이내</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="137" ht="22" customHeight="1">
+      <x:c r="A137" s="4" t="n">
+        <x:v>8026</x:v>
+      </x:c>
+      <x:c r="B137" s="4" t="str">
+        <x:v>찜닭</x:v>
+      </x:c>
+      <x:c r="C137" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D137" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E137" s="5" t="str">
+        <x:v>찜·조림</x:v>
+      </x:c>
+      <x:c r="F137" s="5" t="str">
+        <x:v>냄비 하나|도시락 가능|든든한 한 끼|밥반찬</x:v>
+      </x:c>
+      <x:c r="G137" s="5" t="str">
+        <x:v>닭다리살|감자|당근</x:v>
+      </x:c>
+      <x:c r="H137" s="5" t="str">
+        <x:v>메인요리</x:v>
+      </x:c>
+      <x:c r="I137" s="5" t="str">
+        <x:v>[['닭다리살', '250', 'g'], ['감자', '1', '개(180g)'], ['당근', '50', 'g'], ['양파', '1/2', '개(100g)'], ['대파', '20', 'g'], ['당면', '50', 'g(선택)'], ['물', '400', 'ml'], ['진간장', '50', 'ml(3큰술+1작은술)'], ['설탕', '15', 'g(1큰술)'], ['맛술', '15', 'ml'], ['다진 마늘', '7', 'g'], ['후추', '0.1', 'g'], ['참기름', '5', 'ml']]</x:v>
+      </x:c>
+      <x:c r="J137" s="5" t="str">
+        <x:v>1인분</x:v>
+      </x:c>
+      <x:c r="K137" s="5" t="str">
+        <x:v>중급</x:v>
+      </x:c>
+      <x:c r="L137" s="5" t="str">
+        <x:v>40분이내</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="138" ht="22" customHeight="1">
+      <x:c r="A138" s="4" t="n">
+        <x:v>8027</x:v>
+      </x:c>
+      <x:c r="B138" s="4" t="str">
+        <x:v>콩나물불고기</x:v>
+      </x:c>
+      <x:c r="C138" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D138" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E138" s="5" t="str">
+        <x:v>볶음</x:v>
+      </x:c>
+      <x:c r="F138" s="5" t="str">
+        <x:v>원팬 요리|도시락 가능|든든한 한 끼|밥반찬</x:v>
+      </x:c>
+      <x:c r="G138" s="5" t="str">
+        <x:v>돼지고기|콩나물|양배추</x:v>
+      </x:c>
+      <x:c r="H138" s="5" t="str">
+        <x:v>메인요리</x:v>
+      </x:c>
+      <x:c r="I138" s="5" t="str">
+        <x:v>[['대패삼겹살 또는 얇은 앞다리살', '170', 'g'], ['콩나물', '200', 'g'], ['양배추', '80', 'g'], ['양파', '1/4', '개(50g)'], ['대파', '20', 'g'], ['고추장', '20', 'g'], ['고춧가루', '5', 'g'], ['진간장', '12.5', 'ml'], ['설탕', '8', 'g'], ['맛술', '15', 'ml'], ['다진 마늘', '5', 'g'], ['참기름', '2.5', 'ml'], ['통깨', '1', 'g']]</x:v>
+      </x:c>
+      <x:c r="J138" s="5" t="str">
+        <x:v>1인분</x:v>
+      </x:c>
+      <x:c r="K138" s="5" t="str">
+        <x:v>초급</x:v>
+      </x:c>
+      <x:c r="L138" s="5" t="str">
+        <x:v>22분이내</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="139" ht="22" customHeight="1">
+      <x:c r="A139" s="4" t="n">
+        <x:v>8028</x:v>
+      </x:c>
+      <x:c r="B139" s="4" t="str">
+        <x:v>훈제오리 채소볶음</x:v>
+      </x:c>
+      <x:c r="C139" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D139" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E139" s="5" t="str">
+        <x:v>볶음</x:v>
+      </x:c>
+      <x:c r="F139" s="5" t="str">
+        <x:v>15분 이하|원팬 요리|도시락 가능|든든한 한 끼|밥반찬|남은 재료 활용</x:v>
+      </x:c>
+      <x:c r="G139" s="5" t="str">
+        <x:v>훈제오리|양배추|양파</x:v>
+      </x:c>
+      <x:c r="H139" s="5" t="str">
+        <x:v>메인요리</x:v>
+      </x:c>
+      <x:c r="I139" s="5" t="str">
+        <x:v>[['훈제오리 슬라이스', '180', 'g'], ['양배추', '100', 'g'], ['양파', '1/4', '개(50g)'], ['부추', '50', 'g'], ['파프리카', '50', 'g'], ['다진 마늘', '2', 'g'], ['진간장', '5', 'ml(1작은술)'], ['굴소스', '5', 'ml(1작은술)'], ['후추', '0.1', 'g'], ['식초 또는 레몬즙', '5', 'ml(선택)']]</x:v>
+      </x:c>
+      <x:c r="J139" s="5" t="str">
+        <x:v>1인분</x:v>
+      </x:c>
+      <x:c r="K139" s="5" t="str">
+        <x:v>초급</x:v>
+      </x:c>
+      <x:c r="L139" s="5" t="str">
+        <x:v>15분이내</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="140" ht="22" customHeight="1">
+      <x:c r="A140" s="4" t="n">
+        <x:v>9001</x:v>
+      </x:c>
+      <x:c r="B140" s="4" t="str">
+        <x:v>감자샐러드</x:v>
+      </x:c>
+      <x:c r="C140" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D140" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E140" s="5" t="str">
+        <x:v>샐러드</x:v>
+      </x:c>
+      <x:c r="F140" s="5" t="str">
+        <x:v>냄비 하나|전자레인지</x:v>
+      </x:c>
+      <x:c r="G140" s="5" t="str">
+        <x:v>감자|오이|당근</x:v>
+      </x:c>
+      <x:c r="H140" s="5" t="str">
+        <x:v>샐러드</x:v>
+      </x:c>
+      <x:c r="I140" s="5" t="str">
+        <x:v>[['감자', '1', '개(200g)'], ['오이', '1/4', '개(50g)'], ['당근', '20', 'g'], ['마요네즈', '30', 'g(2큰술)'], ['설탕', '3', 'g(3/4작은술)'], ['소금', '1', 'g'], ['후추', '0.1', 'g']]</x:v>
+      </x:c>
+      <x:c r="J140" s="5" t="str">
+        <x:v>1인분</x:v>
+      </x:c>
+      <x:c r="K140" s="5" t="str">
+        <x:v>초급</x:v>
+      </x:c>
+      <x:c r="L140" s="5" t="str">
+        <x:v>25분이내</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="141" ht="22" customHeight="1">
+      <x:c r="A141" s="4" t="n">
+        <x:v>9002</x:v>
+      </x:c>
+      <x:c r="B141" s="4" t="str">
+        <x:v>계란샐러드</x:v>
+      </x:c>
+      <x:c r="C141" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D141" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E141" s="5" t="str">
+        <x:v>샐러드</x:v>
+      </x:c>
+      <x:c r="F141" s="5" t="str">
+        <x:v>냄비 하나</x:v>
+      </x:c>
+      <x:c r="G141" s="5" t="str">
+        <x:v>계란</x:v>
+      </x:c>
+      <x:c r="H141" s="5" t="str">
+        <x:v>샐러드</x:v>
+      </x:c>
+      <x:c r="I141" s="5" t="str">
+        <x:v>[['계란', '2', '개(100g)'], ['마요네즈', '20', 'g(1큰술+1작은술)'], ['머스터드', '5', 'g(1작은술)'], ['설탕', '2', 'g(1/2작은술)'], ['소금', '0.5', 'g'], ['후추', '0.1', 'g'], ['다진 오이피클', '15', 'g']]</x:v>
+      </x:c>
+      <x:c r="J141" s="5" t="str">
+        <x:v>1인분</x:v>
+      </x:c>
+      <x:c r="K141" s="5" t="str">
+        <x:v>초급</x:v>
+      </x:c>
+      <x:c r="L141" s="5" t="str">
+        <x:v>18분이내</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="142" ht="22" customHeight="1">
+      <x:c r="A142" s="4" t="n">
+        <x:v>9003</x:v>
+      </x:c>
+      <x:c r="B142" s="4" t="str">
+        <x:v>두부 샐러드</x:v>
+      </x:c>
+      <x:c r="C142" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D142" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E142" s="5" t="str">
+        <x:v>샐러드</x:v>
+      </x:c>
+      <x:c r="F142" s="5" t="str">
+        <x:v>15분 이하|원팬 요리</x:v>
+      </x:c>
+      <x:c r="G142" s="5" t="str">
+        <x:v>두부|샐러드 채소|방울토마토</x:v>
+      </x:c>
+      <x:c r="H142" s="5" t="str">
+        <x:v>샐러드</x:v>
+      </x:c>
+      <x:c r="I142" s="5" t="str">
+        <x:v>[['부침용 두부', '200', 'g'], ['양상추 또는 샐러드 채소', '80', 'g'], ['방울토마토', '5', '개(80g)'], ['오이', '50', 'g'], ['식용유', '5', 'ml(1작은술)'], ['진간장', '10', 'ml(2작은술)'], ['식초', '10', 'ml(2작은술)'], ['올리고당', '5', 'g(1작은술)'], ['참기름', '5', 'ml(1작은술)'], ['통깨', '1', 'g']]</x:v>
+      </x:c>
+      <x:c r="J142" s="5" t="str">
+        <x:v>1인분</x:v>
+      </x:c>
+      <x:c r="K142" s="5" t="str">
+        <x:v>초급</x:v>
+      </x:c>
+      <x:c r="L142" s="5" t="str">
+        <x:v>15분이내</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="143" ht="22" customHeight="1">
+      <x:c r="A143" s="4" t="n">
+        <x:v>9004</x:v>
+      </x:c>
+      <x:c r="B143" s="4" t="str">
+        <x:v>양배추샐러드</x:v>
+      </x:c>
+      <x:c r="C143" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D143" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E143" s="5" t="str">
+        <x:v>샐러드</x:v>
+      </x:c>
+      <x:c r="F143" s="5" t="str">
+        <x:v>10분 이하|불 없이 가능</x:v>
+      </x:c>
+      <x:c r="G143" s="5" t="str">
+        <x:v>양배추|당근|옥수수</x:v>
+      </x:c>
+      <x:c r="H143" s="5" t="str">
+        <x:v>샐러드</x:v>
+      </x:c>
+      <x:c r="I143" s="5" t="str">
+        <x:v>[['양배추', '180', 'g'], ['당근', '20', 'g'], ['옥수수 통조림', '30', 'g'], ['마요네즈', '25', 'g'], ['식초', '10', 'ml(2작은술)'], ['설탕', '5', 'g(1작은술)'], ['소금', '0.8', 'g'], ['후추', '0.1', 'g']]</x:v>
+      </x:c>
+      <x:c r="J143" s="5" t="str">
+        <x:v>1인분</x:v>
+      </x:c>
+      <x:c r="K143" s="5" t="str">
+        <x:v>초급</x:v>
+      </x:c>
+      <x:c r="L143" s="5" t="str">
+        <x:v>10분이내</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="144" ht="22" customHeight="1">
+      <x:c r="A144" s="4" t="n">
+        <x:v>9005</x:v>
+      </x:c>
+      <x:c r="B144" s="4" t="str">
+        <x:v>옥수수샐러드</x:v>
+      </x:c>
+      <x:c r="C144" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D144" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E144" s="5" t="str">
+        <x:v>샐러드</x:v>
+      </x:c>
+      <x:c r="F144" s="5" t="str">
+        <x:v>10분 이하|불 없이 가능|설거지 적음</x:v>
+      </x:c>
+      <x:c r="G144" s="5" t="str">
+        <x:v>옥수수|오이|당근</x:v>
+      </x:c>
+      <x:c r="H144" s="5" t="str">
+        <x:v>샐러드</x:v>
+      </x:c>
+      <x:c r="I144" s="5" t="str">
+        <x:v>[['옥수수 통조림', '150', 'g(물기 뺀 중량)'], ['오이', '50', 'g'], ['당근', '20', 'g'], ['양파', '20', 'g'], ['마요네즈', '25', 'g'], ['식초', '5', 'ml(1작은술)'], ['설탕', '3', 'g'], ['소금', '0.5', 'g'], ['후추', '0.1', 'g']]</x:v>
+      </x:c>
+      <x:c r="J144" s="5" t="str">
+        <x:v>1인분</x:v>
+      </x:c>
+      <x:c r="K144" s="5" t="str">
+        <x:v>초급</x:v>
+      </x:c>
+      <x:c r="L144" s="5" t="str">
+        <x:v>10분이내</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="145" ht="22" customHeight="1">
+      <x:c r="A145" s="4" t="n">
+        <x:v>9006</x:v>
+      </x:c>
+      <x:c r="B145" s="4" t="str">
+        <x:v>토마토 샐러드</x:v>
+      </x:c>
+      <x:c r="C145" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D145" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E145" s="5" t="str">
+        <x:v>샐러드</x:v>
+      </x:c>
+      <x:c r="F145" s="5" t="str">
+        <x:v>10분 이하|불 없이 가능|설거지 적음|아침 식사</x:v>
+      </x:c>
+      <x:c r="G145" s="5" t="str">
+        <x:v>토마토|양파</x:v>
+      </x:c>
+      <x:c r="H145" s="5" t="str">
+        <x:v>샐러드</x:v>
+      </x:c>
+      <x:c r="I145" s="5" t="str">
+        <x:v>[['완숙 토마토', '1', '개(200g)'], ['양파', '30', 'g'], ['올리브유', '10', 'ml(2작은술)'], ['식초 또는 레몬즙', '10', 'ml(2작은술)'], ['설탕', '3', 'g'], ['소금', '0.8', 'g'], ['후추', '0.1', 'g'], ['바질 또는 파슬리', '2', 'g(선택)']]</x:v>
+      </x:c>
+      <x:c r="J145" s="5" t="str">
+        <x:v>1인분</x:v>
+      </x:c>
+      <x:c r="K145" s="5" t="str">
+        <x:v>초급</x:v>
+      </x:c>
+      <x:c r="L145" s="5" t="str">
+        <x:v>8분이내</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="146" ht="22" customHeight="1">
+      <x:c r="A146" s="4" t="n">
+        <x:v>10001</x:v>
+      </x:c>
+      <x:c r="B146" s="4" t="str">
+        <x:v>감자샐러드 샌드위치</x:v>
+      </x:c>
+      <x:c r="C146" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D146" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E146" s="5" t="str">
+        <x:v>샌드위치</x:v>
+      </x:c>
+      <x:c r="F146" s="5" t="str">
+        <x:v>냄비 하나|전자레인지|도시락 가능|아침 식사|든든한 한 끼|남은 재료 활용</x:v>
+      </x:c>
+      <x:c r="G146" s="5" t="str">
+        <x:v>식빵|감자|오이</x:v>
+      </x:c>
+      <x:c r="H146" s="5" t="str">
+        <x:v>샌드위치·토스트</x:v>
+      </x:c>
+      <x:c r="I146" s="5" t="str">
+        <x:v>[['식빵', '2', '장(70g)'], ['감자', '1', '개(180g)'], ['오이', '30', 'g'], ['당근', '15', 'g'], ['마요네즈', '25', 'g'], ['설탕', '2', 'g(1/2작은술)'], ['소금', '0.8', 'g'], ['후추', '0.1', 'g'], ['버터', '5', 'g']]</x:v>
+      </x:c>
+      <x:c r="J146" s="5" t="str">
+        <x:v>1인분</x:v>
+      </x:c>
+      <x:c r="K146" s="5" t="str">
+        <x:v>초급</x:v>
+      </x:c>
+      <x:c r="L146" s="5" t="str">
+        <x:v>25분이내</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="147" ht="22" customHeight="1">
+      <x:c r="A147" s="4" t="n">
+        <x:v>10002</x:v>
+      </x:c>
+      <x:c r="B147" s="4" t="str">
+        <x:v>계란토스트</x:v>
+      </x:c>
+      <x:c r="C147" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D147" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E147" s="5" t="str">
+        <x:v>토스트</x:v>
+      </x:c>
+      <x:c r="F147" s="5" t="str">
+        <x:v>15분 이하|원팬 요리|도시락 가능|아침 식사|든든한 한 끼|남은 재료 활용</x:v>
+      </x:c>
+      <x:c r="G147" s="5" t="str">
+        <x:v>식빵|계란|양배추</x:v>
+      </x:c>
+      <x:c r="H147" s="5" t="str">
+        <x:v>샌드위치·토스트</x:v>
+      </x:c>
+      <x:c r="I147" s="5" t="str">
+        <x:v>[['식빵', '2', '장(70g)'], ['계란', '1', '개(50g)'], ['양배추', '50', 'g'], ['당근', '15', 'g'], ['소금', '0.5', 'g'], ['식용유', '5', 'ml(1작은술)'], ['버터', '5', 'g'], ['설탕', '4', 'g(1작은술)'], ['케첩', '15', 'g(1큰술)']]</x:v>
+      </x:c>
+      <x:c r="J147" s="5" t="str">
+        <x:v>1인분</x:v>
+      </x:c>
+      <x:c r="K147" s="5" t="str">
+        <x:v>초급</x:v>
+      </x:c>
+      <x:c r="L147" s="5" t="str">
+        <x:v>15분이내</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="148" ht="22" customHeight="1">
+      <x:c r="A148" s="4" t="n">
+        <x:v>10003</x:v>
+      </x:c>
+      <x:c r="B148" s="4" t="str">
+        <x:v>또띠아샌드위치</x:v>
+      </x:c>
+      <x:c r="C148" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D148" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E148" s="5" t="str">
+        <x:v>샌드위치</x:v>
+      </x:c>
+      <x:c r="F148" s="5" t="str">
+        <x:v>10분 이하|불 없이 가능|설거지 적음|도시락 가능|아침 식사|든든한 한 끼</x:v>
+      </x:c>
+      <x:c r="G148" s="5" t="str">
+        <x:v>또띠아|햄|치즈</x:v>
+      </x:c>
+      <x:c r="H148" s="5" t="str">
+        <x:v>샌드위치·토스트</x:v>
+      </x:c>
+      <x:c r="I148" s="5" t="str">
+        <x:v>[['또띠아', '1', '장(60g)'], ['슬라이스 햄', '2', '장(50g)'], ['슬라이스 치즈', '1', '장(20g)'], ['양상추', '40', 'g'], ['토마토', '60', 'g'], ['오이', '30', 'g'], ['마요네즈', '10', 'g(2작은술)'], ['머스터드', '5', 'g(1작은술)']]</x:v>
+      </x:c>
+      <x:c r="J148" s="5" t="str">
+        <x:v>1인분</x:v>
+      </x:c>
+      <x:c r="K148" s="5" t="str">
+        <x:v>초급</x:v>
+      </x:c>
+      <x:c r="L148" s="5" t="str">
+        <x:v>10분이내</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="149" ht="22" customHeight="1">
+      <x:c r="A149" s="4" t="n">
+        <x:v>10004</x:v>
+      </x:c>
+      <x:c r="B149" s="4" t="str">
+        <x:v>샐러드빵</x:v>
+      </x:c>
+      <x:c r="C149" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D149" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E149" s="5" t="str">
+        <x:v>샌드위치</x:v>
+      </x:c>
+      <x:c r="F149" s="5" t="str">
+        <x:v>15분 이하|불 없이 가능|설거지 적음|도시락 가능|아침 식사|든든한 한 끼</x:v>
+      </x:c>
+      <x:c r="G149" s="5" t="str">
+        <x:v>빵|양배추|오이</x:v>
+      </x:c>
+      <x:c r="H149" s="5" t="str">
+        <x:v>샌드위치·토스트</x:v>
+      </x:c>
+      <x:c r="I149" s="5" t="str">
+        <x:v>[['핫도그빵 또는 모닝빵', '2', '개(80g)'], ['양배추', '80', 'g'], ['오이', '30', 'g'], ['당근', '20', 'g'], ['마요네즈', '25', 'g'], ['케첩', '10', 'g'], ['설탕', '3', 'g'], ['소금', '0.8', 'g'], ['후추', '0.1', 'g'], ['슬라이스 햄', '1', '장(25g, 선택)']]</x:v>
+      </x:c>
+      <x:c r="J149" s="5" t="str">
+        <x:v>1인분</x:v>
+      </x:c>
+      <x:c r="K149" s="5" t="str">
+        <x:v>초급</x:v>
+      </x:c>
+      <x:c r="L149" s="5" t="str">
+        <x:v>15분이내</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="150" ht="22" customHeight="1">
+      <x:c r="A150" s="4" t="n">
+        <x:v>10005</x:v>
+      </x:c>
+      <x:c r="B150" s="4" t="str">
+        <x:v>에그마요 샌드위치</x:v>
+      </x:c>
+      <x:c r="C150" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D150" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E150" s="5" t="str">
+        <x:v>샌드위치</x:v>
+      </x:c>
+      <x:c r="F150" s="5" t="str">
+        <x:v>냄비 하나|도시락 가능|아침 식사|든든한 한 끼|남은 재료 활용</x:v>
+      </x:c>
+      <x:c r="G150" s="5" t="str">
+        <x:v>식빵|계란|양상추</x:v>
+      </x:c>
+      <x:c r="H150" s="5" t="str">
+        <x:v>샌드위치·토스트</x:v>
+      </x:c>
+      <x:c r="I150" s="5" t="str">
+        <x:v>[['식빵', '2', '장(70g)'], ['계란', '2', '개(100g)'], ['마요네즈', '20', 'g(1큰술+1작은술)'], ['머스터드', '5', 'g(1작은술)'], ['설탕', '2', 'g(1/2작은술)'], ['소금', '0.5', 'g'], ['후추', '0.1', 'g'], ['버터', '5', 'g'], ['양상추', '20', 'g(선택)']]</x:v>
+      </x:c>
+      <x:c r="J150" s="5" t="str">
+        <x:v>1인분</x:v>
+      </x:c>
+      <x:c r="K150" s="5" t="str">
+        <x:v>초급</x:v>
+      </x:c>
+      <x:c r="L150" s="5" t="str">
+        <x:v>18분이내</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="151" ht="22" customHeight="1">
+      <x:c r="A151" s="4" t="n">
+        <x:v>10006</x:v>
+      </x:c>
+      <x:c r="B151" s="4" t="str">
+        <x:v>참치 샌드위치</x:v>
+      </x:c>
+      <x:c r="C151" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D151" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E151" s="5" t="str">
+        <x:v>샌드위치</x:v>
+      </x:c>
+      <x:c r="F151" s="5" t="str">
+        <x:v>10분 이하|불 없이 가능|도시락 가능|아침 식사|든든한 한 끼|남은 재료 활용</x:v>
+      </x:c>
+      <x:c r="G151" s="5" t="str">
+        <x:v>식빵|참치|양파</x:v>
+      </x:c>
+      <x:c r="H151" s="5" t="str">
+        <x:v>샌드위치·토스트</x:v>
+      </x:c>
+      <x:c r="I151" s="5" t="str">
+        <x:v>[['식빵', '2', '장(70g)'], ['참치 통조림', '80', 'g'], ['마요네즈', '20', 'g(1큰술+1작은술)'], ['다진 양파', '20', 'g'], ['다진 오이피클', '15', 'g'], ['머스터드', '5', 'g(1작은술)'], ['후추', '0.1', 'g'], ['양상추', '20', 'g'], ['버터', '5', 'g']]</x:v>
+      </x:c>
+      <x:c r="J151" s="5" t="str">
+        <x:v>1인분</x:v>
+      </x:c>
+      <x:c r="K151" s="5" t="str">
+        <x:v>초급</x:v>
+      </x:c>
+      <x:c r="L151" s="5" t="str">
+        <x:v>10분이내</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="152" ht="22" customHeight="1">
+      <x:c r="A152" s="4" t="n">
+        <x:v>10007</x:v>
+      </x:c>
+      <x:c r="B152" s="4" t="str">
+        <x:v>프렌치토스트</x:v>
+      </x:c>
+      <x:c r="C152" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D152" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E152" s="5" t="str">
+        <x:v>토스트</x:v>
+      </x:c>
+      <x:c r="F152" s="5" t="str">
+        <x:v>15분 이하|원팬 요리|칼 없이 가능|설거지 적음|도시락 가능|아침 식사|든든한 한 끼|남은 재료 활용</x:v>
+      </x:c>
+      <x:c r="G152" s="5" t="str">
+        <x:v>식빵|계란|우유</x:v>
+      </x:c>
+      <x:c r="H152" s="5" t="str">
+        <x:v>샌드위치·토스트</x:v>
+      </x:c>
+      <x:c r="I152" s="5" t="str">
+        <x:v>[['식빵', '2', '장(70g)'], ['계란', '1', '개(50g)'], ['우유', '80', 'ml'], ['설탕', '8', 'g(2작은술)'], ['소금', '0.2', 'g'], ['버터', '10', 'g'], ['꿀 또는 메이플시럽', '10', 'g(선택)'], ['과일', '80', 'g(선택)']]</x:v>
+      </x:c>
+      <x:c r="J152" s="5" t="str">
+        <x:v>1인분</x:v>
+      </x:c>
+      <x:c r="K152" s="5" t="str">
+        <x:v>초급</x:v>
+      </x:c>
+      <x:c r="L152" s="5" t="str">
+        <x:v>12분이내</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="153" ht="22" customHeight="1">
+      <x:c r="A153" s="4" t="n">
+        <x:v>10008</x:v>
+      </x:c>
+      <x:c r="B153" s="4" t="str">
+        <x:v>핫도그 샌드위치</x:v>
+      </x:c>
+      <x:c r="C153" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D153" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E153" s="5" t="str">
+        <x:v>핫도그</x:v>
+      </x:c>
+      <x:c r="F153" s="5" t="str">
+        <x:v>15분 이하|원팬 요리|설거지 적음|도시락 가능|아침 식사|든든한 한 끼|남은 재료 활용</x:v>
+      </x:c>
+      <x:c r="G153" s="5" t="str">
+        <x:v>핫도그빵|소시지|양배추</x:v>
+      </x:c>
+      <x:c r="H153" s="5" t="str">
+        <x:v>샌드위치·토스트</x:v>
+      </x:c>
+      <x:c r="I153" s="5" t="str">
+        <x:v>[['핫도그빵', '2', '개(100g)'], ['비엔나 또는 프랑크소시지', '2', '개(120g)'], ['양배추', '60', 'g'], ['양파', '30', 'g'], ['식용유', '5', 'ml'], ['케첩', '20', 'g'], ['머스터드', '10', 'g'], ['마요네즈', '10', 'g'], ['피클', '20', 'g(선택)']]</x:v>
+      </x:c>
+      <x:c r="J153" s="5" t="str">
+        <x:v>1인분</x:v>
+      </x:c>
+      <x:c r="K153" s="5" t="str">
+        <x:v>초급</x:v>
+      </x:c>
+      <x:c r="L153" s="5" t="str">
+        <x:v>12분이내</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="154" ht="22" customHeight="1">
+      <x:c r="A154" s="4" t="n">
+        <x:v>10009</x:v>
+      </x:c>
+      <x:c r="B154" s="4" t="str">
+        <x:v>햄 치즈 샌드위치</x:v>
+      </x:c>
+      <x:c r="C154" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D154" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E154" s="5" t="str">
+        <x:v>샌드위치</x:v>
+      </x:c>
+      <x:c r="F154" s="5" t="str">
+        <x:v>10분 이하|불 없이 가능|설거지 적음|도시락 가능|아침 식사|든든한 한 끼|남은 재료 활용</x:v>
+      </x:c>
+      <x:c r="G154" s="5" t="str">
+        <x:v>식빵|햄|치즈</x:v>
+      </x:c>
+      <x:c r="H154" s="5" t="str">
+        <x:v>샌드위치·토스트</x:v>
+      </x:c>
+      <x:c r="I154" s="5" t="str">
+        <x:v>[['식빵', '2', '장(70g)'], ['슬라이스 햄', '2', '장(50g)'], ['슬라이스 치즈', '1', '장(20g)'], ['양상추', '30', 'g'], ['토마토', '50', 'g'], ['마요네즈', '10', 'g'], ['머스터드', '5', 'g'], ['버터', '5', 'g']]</x:v>
+      </x:c>
+      <x:c r="J154" s="5" t="str">
+        <x:v>1인분</x:v>
+      </x:c>
+      <x:c r="K154" s="5" t="str">
+        <x:v>초급</x:v>
+      </x:c>
+      <x:c r="L154" s="5" t="str">
+        <x:v>8분이내</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="155" ht="22" customHeight="1">
+      <x:c r="A155" s="4" t="n">
+        <x:v>11001</x:v>
+      </x:c>
+      <x:c r="B155" s="4" t="str">
+        <x:v>계란죽</x:v>
+      </x:c>
+      <x:c r="C155" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D155" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E155" s="5" t="str">
+        <x:v>죽</x:v>
+      </x:c>
+      <x:c r="F155" s="5" t="str">
+        <x:v>15분 이하|냄비 하나|칼 없이 가능|설거지 적음|아침 식사|든든한 한 끼|남은 재료 활용</x:v>
+      </x:c>
+      <x:c r="G155" s="5" t="str">
+        <x:v>밥|계란</x:v>
+      </x:c>
+      <x:c r="H155" s="5" t="str">
+        <x:v>죽</x:v>
+      </x:c>
+      <x:c r="I155" s="5" t="str">
+        <x:v>[['밥', '150', 'g'], ['계란', '1', '개(50g)'], ['물', '450', 'ml'], ['국간장', '5', 'ml(1작은술)'], ['소금', '0.8', 'g'], ['참기름', '5', 'ml(1작은술)'], ['대파', '8', 'g'], ['김가루', '2', 'g']]</x:v>
+      </x:c>
+      <x:c r="J155" s="5" t="str">
+        <x:v>1인분</x:v>
+      </x:c>
+      <x:c r="K155" s="5" t="str">
+        <x:v>초급</x:v>
+      </x:c>
+      <x:c r="L155" s="5" t="str">
+        <x:v>15분이내</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="156" ht="22" customHeight="1">
+      <x:c r="A156" s="4" t="n">
+        <x:v>11002</x:v>
+      </x:c>
+      <x:c r="B156" s="4" t="str">
+        <x:v>김치죽</x:v>
+      </x:c>
+      <x:c r="C156" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D156" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E156" s="5" t="str">
+        <x:v>죽</x:v>
+      </x:c>
+      <x:c r="F156" s="5" t="str">
+        <x:v>냄비 하나|설거지 적음|아침 식사|든든한 한 끼|남은 재료 활용</x:v>
+      </x:c>
+      <x:c r="G156" s="5" t="str">
+        <x:v>밥|김치|참치</x:v>
+      </x:c>
+      <x:c r="H156" s="5" t="str">
+        <x:v>죽</x:v>
+      </x:c>
+      <x:c r="I156" s="5" t="str">
+        <x:v>[['밥', '150', 'g'], ['배추김치', '80', 'g'], ['참치 통조림', '40', 'g(선택)'], ['물', '450', 'ml'], ['김치국물', '15', 'ml(1큰술)'], ['국간장', '5', 'ml(1작은술)'], ['참기름', '5', 'ml(1작은술)'], ['김가루', '2', 'g']]</x:v>
+      </x:c>
+      <x:c r="J156" s="5" t="str">
+        <x:v>1인분</x:v>
+      </x:c>
+      <x:c r="K156" s="5" t="str">
+        <x:v>초급</x:v>
+      </x:c>
+      <x:c r="L156" s="5" t="str">
+        <x:v>18분이내</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="157" ht="22" customHeight="1">
+      <x:c r="A157" s="4" t="n">
+        <x:v>11003</x:v>
+      </x:c>
+      <x:c r="B157" s="4" t="str">
+        <x:v>누룽지죽</x:v>
+      </x:c>
+      <x:c r="C157" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D157" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E157" s="5" t="str">
+        <x:v>죽</x:v>
+      </x:c>
+      <x:c r="F157" s="5" t="str">
+        <x:v>15분 이하|재료 5개 이하|냄비 하나|칼 없이 가능|설거지 적음|아침 식사|든든한 한 끼|남은 재료 활용</x:v>
+      </x:c>
+      <x:c r="G157" s="5" t="str">
+        <x:v>누룽지</x:v>
+      </x:c>
+      <x:c r="H157" s="5" t="str">
+        <x:v>죽</x:v>
+      </x:c>
+      <x:c r="I157" s="5" t="str">
+        <x:v>[['마른 누룽지', '80', 'g'], ['물', '550', 'ml'], ['소금', '0.8', 'g'], ['참기름', '2.5', 'ml(1/2작은술, 선택)'], ['김가루', '2', 'g(선택)']]</x:v>
+      </x:c>
+      <x:c r="J157" s="5" t="str">
+        <x:v>1인분</x:v>
+      </x:c>
+      <x:c r="K157" s="5" t="str">
+        <x:v>초급</x:v>
+      </x:c>
+      <x:c r="L157" s="5" t="str">
+        <x:v>15분이내</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="158" ht="22" customHeight="1">
+      <x:c r="A158" s="4" t="n">
+        <x:v>11004</x:v>
+      </x:c>
+      <x:c r="B158" s="4" t="str">
+        <x:v>닭죽</x:v>
+      </x:c>
+      <x:c r="C158" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D158" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E158" s="5" t="str">
+        <x:v>죽</x:v>
+      </x:c>
+      <x:c r="F158" s="5" t="str">
+        <x:v>냄비 하나|아침 식사|든든한 한 끼|남은 재료 활용</x:v>
+      </x:c>
+      <x:c r="G158" s="5" t="str">
+        <x:v>밥|닭가슴살|당근</x:v>
+      </x:c>
+      <x:c r="H158" s="5" t="str">
+        <x:v>죽</x:v>
+      </x:c>
+      <x:c r="I158" s="5" t="str">
+        <x:v>[['밥', '150', 'g'], ['닭가슴살', '100', 'g'], ['물', '550', 'ml'], ['당근', '20', 'g'], ['양파', '30', 'g'], ['대파', '8', 'g'], ['국간장', '5', 'ml(1작은술)'], ['소금', '0.8', 'g'], ['참기름', '5', 'ml(1작은술)']]</x:v>
+      </x:c>
+      <x:c r="J158" s="5" t="str">
+        <x:v>1인분</x:v>
+      </x:c>
+      <x:c r="K158" s="5" t="str">
+        <x:v>초급</x:v>
+      </x:c>
+      <x:c r="L158" s="5" t="str">
+        <x:v>25분이내</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="159" ht="22" customHeight="1">
+      <x:c r="A159" s="4" t="n">
+        <x:v>11005</x:v>
+      </x:c>
+      <x:c r="B159" s="4" t="str">
+        <x:v>오트밀죽</x:v>
+      </x:c>
+      <x:c r="C159" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D159" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E159" s="5" t="str">
+        <x:v>죽</x:v>
+      </x:c>
+      <x:c r="F159" s="5" t="str">
+        <x:v>10분 이하|전자레인지|불 없이 가능|설거지 적음|아침 식사|든든한 한 끼|남은 재료 활용</x:v>
+      </x:c>
+      <x:c r="G159" s="5" t="str">
+        <x:v>오트밀|계란</x:v>
+      </x:c>
+      <x:c r="H159" s="5" t="str">
+        <x:v>죽</x:v>
+      </x:c>
+      <x:c r="I159" s="5" t="str">
+        <x:v>[['압착 오트밀', '50', 'g'], ['물', '300', 'ml'], ['계란', '1', '개(50g)'], ['소금', '0.5', 'g'], ['대파', '8', 'g'], ['참기름', '2.5', 'ml(1/2작은술)'], ['김가루', '2', 'g(선택)']]</x:v>
+      </x:c>
+      <x:c r="J159" s="5" t="str">
+        <x:v>1인분</x:v>
+      </x:c>
+      <x:c r="K159" s="5" t="str">
+        <x:v>초급</x:v>
+      </x:c>
+      <x:c r="L159" s="5" t="str">
+        <x:v>8분이내</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="160" ht="22" customHeight="1">
+      <x:c r="A160" s="4" t="n">
+        <x:v>11006</x:v>
+      </x:c>
+      <x:c r="B160" s="4" t="str">
+        <x:v>참치 채소죽</x:v>
+      </x:c>
+      <x:c r="C160" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D160" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E160" s="5" t="str">
+        <x:v>죽</x:v>
+      </x:c>
+      <x:c r="F160" s="5" t="str">
+        <x:v>냄비 하나|아침 식사|든든한 한 끼|남은 재료 활용</x:v>
+      </x:c>
+      <x:c r="G160" s="5" t="str">
+        <x:v>밥|참치|당근</x:v>
+      </x:c>
+      <x:c r="H160" s="5" t="str">
+        <x:v>죽</x:v>
+      </x:c>
+      <x:c r="I160" s="5" t="str">
+        <x:v>[['밥', '150', 'g'], ['참치 통조림', '70', 'g'], ['당근', '20', 'g'], ['양파', '30', 'g'], ['애호박', '40', 'g'], ['물', '500', 'ml'], ['국간장', '5', 'ml(1작은술)'], ['소금', '0.5', 'g'], ['참기름', '5', 'ml(1작은술)'], ['대파', '8', 'g']]</x:v>
+      </x:c>
+      <x:c r="J160" s="5" t="str">
+        <x:v>1인분</x:v>
+      </x:c>
+      <x:c r="K160" s="5" t="str">
+        <x:v>초급</x:v>
+      </x:c>
+      <x:c r="L160" s="5" t="str">
+        <x:v>18분이내</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="161" ht="22" customHeight="1">
+      <x:c r="A161" s="4" t="n">
+        <x:v>11007</x:v>
+      </x:c>
+      <x:c r="B161" s="4" t="str">
+        <x:v>채소죽</x:v>
+      </x:c>
+      <x:c r="C161" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D161" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E161" s="5" t="str">
+        <x:v>죽</x:v>
+      </x:c>
+      <x:c r="F161" s="5" t="str">
+        <x:v>냄비 하나|설거지 적음|아침 식사|든든한 한 끼|남은 재료 활용</x:v>
+      </x:c>
+      <x:c r="G161" s="5" t="str">
+        <x:v>밥|당근|양파</x:v>
+      </x:c>
+      <x:c r="H161" s="5" t="str">
+        <x:v>죽</x:v>
+      </x:c>
+      <x:c r="I161" s="5" t="str">
+        <x:v>[['밥', '150', 'g'], ['당근', '25', 'g'], ['양파', '35', 'g'], ['애호박', '50', 'g'], ['표고버섯 또는 새송이버섯', '40', 'g'], ['물', '500', 'ml'], ['국간장', '5', 'ml(1작은술)'], ['소금', '0.6', 'g'], ['참기름', '5', 'ml(1작은술)'], ['대파', '8', 'g']]</x:v>
+      </x:c>
+      <x:c r="J161" s="5" t="str">
+        <x:v>1인분</x:v>
+      </x:c>
+      <x:c r="K161" s="5" t="str">
+        <x:v>초급</x:v>
+      </x:c>
+      <x:c r="L161" s="5" t="str">
+        <x:v>18분이내</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="162" ht="22" customHeight="1">
+      <x:c r="A162" s="4" t="n">
+        <x:v>12001</x:v>
+      </x:c>
+      <x:c r="B162" s="4" t="str">
+        <x:v>고구마맛탕</x:v>
+      </x:c>
+      <x:c r="C162" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D162" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E162" s="5" t="str">
+        <x:v>맛탕</x:v>
+      </x:c>
+      <x:c r="F162" s="5" t="str">
+        <x:v>재료 5개 이하|원팬 요리|전자레인지|야식</x:v>
+      </x:c>
+      <x:c r="G162" s="5" t="str">
+        <x:v>고구마</x:v>
+      </x:c>
+      <x:c r="H162" s="5" t="str">
+        <x:v>간식·야식</x:v>
+      </x:c>
+      <x:c r="I162" s="5" t="str">
+        <x:v>[['고구마', '1', '개(250g)'], ['식용유', '20', 'ml(1큰술+1작은술)'], ['설탕', '20', 'g(1큰술+2작은술)'], ['물', '15', 'ml(1큰술)'], ['검은깨', '1', 'g']]</x:v>
+      </x:c>
+      <x:c r="J162" s="5" t="str">
+        <x:v>1인분</x:v>
+      </x:c>
+      <x:c r="K162" s="5" t="str">
+        <x:v>초급</x:v>
+      </x:c>
+      <x:c r="L162" s="5" t="str">
+        <x:v>25분이내</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="163" ht="22" customHeight="1">
+      <x:c r="A163" s="4" t="n">
+        <x:v>12002</x:v>
+      </x:c>
+      <x:c r="B163" s="4" t="str">
+        <x:v>군고구마</x:v>
+      </x:c>
+      <x:c r="C163" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D163" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E163" s="5" t="str">
+        <x:v>구이</x:v>
+      </x:c>
+      <x:c r="F163" s="5" t="str">
+        <x:v>재료 5개 이하|전자레인지|에어프라이어|칼 없이 가능|불 없이 가능|설거지 적음|냉동 가능|아침 식사|야식</x:v>
+      </x:c>
+      <x:c r="G163" s="5" t="str">
+        <x:v>고구마</x:v>
+      </x:c>
+      <x:c r="H163" s="5" t="str">
+        <x:v>간식·야식</x:v>
+      </x:c>
+      <x:c r="I163" s="5" t="str">
+        <x:v>[['고구마', '1', '개(250g)'], ['물', '15', 'ml(1큰술, 전자레인지 조리 시)']]</x:v>
+      </x:c>
+      <x:c r="J163" s="5" t="str">
+        <x:v>1인분</x:v>
+      </x:c>
+      <x:c r="K163" s="5" t="str">
+        <x:v>초급</x:v>
+      </x:c>
+      <x:c r="L163" s="5" t="str">
+        <x:v>25분이내</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="164" ht="22" customHeight="1">
+      <x:c r="A164" s="4" t="n">
+        <x:v>12003</x:v>
+      </x:c>
+      <x:c r="B164" s="4" t="str">
+        <x:v>군만두</x:v>
+      </x:c>
+      <x:c r="C164" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D164" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E164" s="5" t="str">
+        <x:v>만두</x:v>
+      </x:c>
+      <x:c r="F164" s="5" t="str">
+        <x:v>15분 이하|재료 5개 이하|원팬 요리|칼 없이 가능|설거지 적음|야식</x:v>
+      </x:c>
+      <x:c r="G164" s="5" t="str">
+        <x:v>냉동만두</x:v>
+      </x:c>
+      <x:c r="H164" s="5" t="str">
+        <x:v>간식·야식</x:v>
+      </x:c>
+      <x:c r="I164" s="5" t="str">
+        <x:v>[['냉동만두', '6', '개(180g)'], ['식용유', '10', 'ml(2작은술)'], ['물', '45', 'ml(3큰술)']]</x:v>
+      </x:c>
+      <x:c r="J164" s="5" t="str">
+        <x:v>1인분</x:v>
+      </x:c>
+      <x:c r="K164" s="5" t="str">
+        <x:v>초급</x:v>
+      </x:c>
+      <x:c r="L164" s="5" t="str">
+        <x:v>12분이내</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="165" ht="22" customHeight="1">
+      <x:c r="A165" s="4" t="n">
+        <x:v>12004</x:v>
+      </x:c>
+      <x:c r="B165" s="4" t="str">
+        <x:v>떡볶이</x:v>
+      </x:c>
+      <x:c r="C165" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D165" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E165" s="5" t="str">
+        <x:v>떡볶이</x:v>
+      </x:c>
+      <x:c r="F165" s="5" t="str">
+        <x:v>야식</x:v>
+      </x:c>
+      <x:c r="G165" s="5" t="str">
+        <x:v>떡볶이떡|어묵|양배추</x:v>
+      </x:c>
+      <x:c r="H165" s="5" t="str">
+        <x:v>간식·야식</x:v>
+      </x:c>
+      <x:c r="I165" s="5" t="str">
+        <x:v>[['떡볶이떡', '200', 'g'], ['사각어묵', '1', '장(50g)'], ['양배추', '70', 'g'], ['대파', '20', 'g'], ['물', '350', 'ml'], ['고추장', '25', 'g(1큰술+1작은술)'], ['고춧가루', '4', 'g(2작은술)'], ['설탕', '15', 'g(1큰술)'], ['진간장', '10', 'ml(2작은술)'], ['다진 마늘', '2', 'g']]</x:v>
+      </x:c>
+      <x:c r="J165" s="5" t="str">
+        <x:v>1인분</x:v>
+      </x:c>
+      <x:c r="K165" s="5" t="str">
+        <x:v>초급</x:v>
+      </x:c>
+      <x:c r="L165" s="5" t="str">
+        <x:v>20분이내</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="166" ht="22" customHeight="1">
+      <x:c r="A166" s="4" t="n">
+        <x:v>12005</x:v>
+      </x:c>
+      <x:c r="B166" s="4" t="str">
+        <x:v>또띠아피자</x:v>
+      </x:c>
+      <x:c r="C166" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D166" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E166" s="5" t="str">
+        <x:v>간편 피자</x:v>
+      </x:c>
+      <x:c r="F166" s="5" t="str">
+        <x:v>15분 이하|원팬 요리|설거지 적음|야식</x:v>
+      </x:c>
+      <x:c r="G166" s="5" t="str">
+        <x:v>또띠아|모차렐라 치즈|양파</x:v>
+      </x:c>
+      <x:c r="H166" s="5" t="str">
+        <x:v>간식·야식</x:v>
+      </x:c>
+      <x:c r="I166" s="5" t="str">
+        <x:v>[['또띠아', '1', '장(60g)'], ['토마토소스', '35', 'g(2큰술)'], ['모차렐라 치즈', '70', 'g'], ['양파', '30', 'g'], ['파프리카', '30', 'g'], ['햄 또는 소시지', '40', 'g'], ['옥수수 통조림', '20', 'g'], ['식용유', '2.5', 'ml(1/2작은술)']]</x:v>
+      </x:c>
+      <x:c r="J166" s="5" t="str">
+        <x:v>1인분</x:v>
+      </x:c>
+      <x:c r="K166" s="5" t="str">
+        <x:v>초급</x:v>
+      </x:c>
+      <x:c r="L166" s="5" t="str">
+        <x:v>15분이내</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="167" ht="22" customHeight="1">
+      <x:c r="A167" s="4" t="n">
+        <x:v>12006</x:v>
+      </x:c>
+      <x:c r="B167" s="4" t="str">
+        <x:v>라볶이</x:v>
+      </x:c>
+      <x:c r="C167" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D167" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E167" s="5" t="str">
+        <x:v>떡볶이</x:v>
+      </x:c>
+      <x:c r="F167" s="5" t="str">
+        <x:v>설거지 적음|야식</x:v>
+      </x:c>
+      <x:c r="G167" s="5" t="str">
+        <x:v>라면사리|떡볶이떡|어묵</x:v>
+      </x:c>
+      <x:c r="H167" s="5" t="str">
+        <x:v>간식·야식</x:v>
+      </x:c>
+      <x:c r="I167" s="5" t="str">
+        <x:v>[['라면사리', '1', '개(110g)'], ['떡볶이떡', '120', 'g'], ['어묵', '50', 'g'], ['양배추', '60', 'g'], ['대파', '20', 'g'], ['물', '500', 'ml'], ['고추장', '25', 'g'], ['고춧가루', '3', 'g'], ['설탕', '15', 'g'], ['진간장', '10', 'ml'], ['다진 마늘', '2', 'g']]</x:v>
+      </x:c>
+      <x:c r="J167" s="5" t="str">
+        <x:v>1인분</x:v>
+      </x:c>
+      <x:c r="K167" s="5" t="str">
+        <x:v>초급</x:v>
+      </x:c>
+      <x:c r="L167" s="5" t="str">
+        <x:v>20분이내</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="168" ht="22" customHeight="1">
+      <x:c r="A168" s="4" t="n">
+        <x:v>12007</x:v>
+      </x:c>
+      <x:c r="B168" s="4" t="str">
+        <x:v>로제떡볶이</x:v>
+      </x:c>
+      <x:c r="C168" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D168" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E168" s="5" t="str">
+        <x:v>떡볶이</x:v>
+      </x:c>
+      <x:c r="F168" s="5" t="str">
+        <x:v>원팬 요리|설거지 적음|야식</x:v>
+      </x:c>
+      <x:c r="G168" s="5" t="str">
+        <x:v>떡볶이떡|소시지|양파</x:v>
+      </x:c>
+      <x:c r="H168" s="5" t="str">
+        <x:v>간식·야식</x:v>
+      </x:c>
+      <x:c r="I168" s="5" t="str">
+        <x:v>[['떡볶이떡', '180', 'g'], ['비엔나소시지', '80', 'g'], ['양파', '1/4', '개(50g)'], ['우유', '200', 'ml'], ['물', '100', 'ml'], ['고추장', '15', 'g(1큰술)'], ['고춧가루', '2', 'g(1작은술)'], ['설탕', '8', 'g(2작은술)'], ['진간장', '5', 'ml(1작은술)'], ['다진 마늘', '2', 'g'], ['슬라이스 치즈', '1', '장(20g, 선택)']]</x:v>
+      </x:c>
+      <x:c r="J168" s="5" t="str">
+        <x:v>1인분</x:v>
+      </x:c>
+      <x:c r="K168" s="5" t="str">
+        <x:v>초급</x:v>
+      </x:c>
+      <x:c r="L168" s="5" t="str">
+        <x:v>20분이내</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="169" ht="22" customHeight="1">
+      <x:c r="A169" s="4" t="n">
+        <x:v>12008</x:v>
+      </x:c>
+      <x:c r="B169" s="4" t="str">
+        <x:v>비빔만두</x:v>
+      </x:c>
+      <x:c r="C169" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D169" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E169" s="5" t="str">
+        <x:v>만두</x:v>
+      </x:c>
+      <x:c r="F169" s="5" t="str">
+        <x:v>원팬 요리|야식</x:v>
+      </x:c>
+      <x:c r="G169" s="5" t="str">
+        <x:v>냉동만두|양배추|오이</x:v>
+      </x:c>
+      <x:c r="H169" s="5" t="str">
+        <x:v>간식·야식</x:v>
+      </x:c>
+      <x:c r="I169" s="5" t="str">
+        <x:v>[['냉동만두', '6', '개(180g)'], ['양배추', '80', 'g'], ['오이', '40', 'g'], ['당근', '20', 'g'], ['상추', '30', 'g'], ['고추장', '15', 'g(1큰술)'], ['식초', '15', 'ml(1큰술)'], ['설탕', '8', 'g(2작은술)'], ['진간장', '5', 'ml(1작은술)'], ['고춧가루', '2', 'g'], ['참기름', '5', 'ml(1작은술)'], ['식용유', '5', 'ml'], ['물', '45', 'ml']]</x:v>
+      </x:c>
+      <x:c r="J169" s="5" t="str">
+        <x:v>1인분</x:v>
+      </x:c>
+      <x:c r="K169" s="5" t="str">
+        <x:v>초급</x:v>
+      </x:c>
+      <x:c r="L169" s="5" t="str">
+        <x:v>18분이내</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="170" ht="22" customHeight="1">
+      <x:c r="A170" s="4" t="n">
+        <x:v>12009</x:v>
+      </x:c>
+      <x:c r="B170" s="4" t="str">
+        <x:v>식빵피자</x:v>
+      </x:c>
+      <x:c r="C170" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D170" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E170" s="5" t="str">
+        <x:v>간편 피자</x:v>
+      </x:c>
+      <x:c r="F170" s="5" t="str">
+        <x:v>15분 이하|에어프라이어|불 없이 가능|설거지 적음|야식</x:v>
+      </x:c>
+      <x:c r="G170" s="5" t="str">
+        <x:v>식빵|모차렐라 치즈|양파</x:v>
+      </x:c>
+      <x:c r="H170" s="5" t="str">
+        <x:v>간식·야식</x:v>
+      </x:c>
+      <x:c r="I170" s="5" t="str">
+        <x:v>[['식빵', '2', '장(70g)'], ['토마토소스', '40', 'g 또는 케첩 30g'], ['모차렐라 치즈', '70', 'g'], ['양파', '30', 'g'], ['파프리카', '30', 'g'], ['햄 또는 소시지', '40', 'g'], ['옥수수 통조림', '20', 'g']]</x:v>
+      </x:c>
+      <x:c r="J170" s="5" t="str">
+        <x:v>1인분</x:v>
+      </x:c>
+      <x:c r="K170" s="5" t="str">
+        <x:v>초급</x:v>
+      </x:c>
+      <x:c r="L170" s="5" t="str">
+        <x:v>12분이내</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="171" ht="22" customHeight="1">
+      <x:c r="A171" s="4" t="n">
+        <x:v>12010</x:v>
+      </x:c>
+      <x:c r="B171" s="4" t="str">
+        <x:v>웨지감자</x:v>
+      </x:c>
+      <x:c r="C171" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D171" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E171" s="5" t="str">
+        <x:v>감자 구이</x:v>
+      </x:c>
+      <x:c r="F171" s="5" t="str">
+        <x:v>에어프라이어|불 없이 가능|냉동 가능|야식</x:v>
+      </x:c>
+      <x:c r="G171" s="5" t="str">
+        <x:v>감자</x:v>
+      </x:c>
+      <x:c r="H171" s="5" t="str">
+        <x:v>간식·야식</x:v>
+      </x:c>
+      <x:c r="I171" s="5" t="str">
+        <x:v>[['감자', '1', '개(250g)'], ['식용유 또는 올리브유', '15', 'ml(1큰술)'], ['소금', '1.2', 'g'], ['후추', '0.1', 'g'], ['파프리카가루', '1', 'g(선택)'], ['파슬리가루', '0.2', 'g(선택)']]</x:v>
+      </x:c>
+      <x:c r="J171" s="5" t="str">
+        <x:v>1인분</x:v>
+      </x:c>
+      <x:c r="K171" s="5" t="str">
+        <x:v>초급</x:v>
+      </x:c>
+      <x:c r="L171" s="5" t="str">
+        <x:v>30분이내</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="172" ht="22" customHeight="1">
+      <x:c r="A172" s="4" t="n">
+        <x:v>12011</x:v>
+      </x:c>
+      <x:c r="B172" s="4" t="str">
+        <x:v>콘치즈</x:v>
+      </x:c>
+      <x:c r="C172" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D172" s="4" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E172" s="5" t="str">
+        <x:v>치즈 간식</x:v>
+      </x:c>
+      <x:c r="F172" s="5" t="str">
+        <x:v>15분 이하|원팬 요리|칼 없이 가능|설거지 적음|야식</x:v>
+      </x:c>
+      <x:c r="G172" s="5" t="str">
+        <x:v>옥수수|모차렐라 치즈</x:v>
+      </x:c>
+      <x:c r="H172" s="5" t="str">
+        <x:v>간식·야식</x:v>
+      </x:c>
+      <x:c r="I172" s="5" t="str">
+        <x:v>[['옥수수 통조림', '180', 'g(물기 뺀 중량)'], ['모차렐라 치즈', '80', 'g'], ['마요네즈', '20', 'g(1큰술+1작은술)'], ['설탕', '5', 'g(1작은술)'], ['버터', '5', 'g'], ['소금', '0.3', 'g'], ['후추', '0.1', 'g'], ['파슬리가루', '0.2', 'g(선택)']]</x:v>
+      </x:c>
+      <x:c r="J172" s="5" t="str">
+        <x:v>1인분</x:v>
+      </x:c>
+      <x:c r="K172" s="5" t="str">
+        <x:v>초급</x:v>
+      </x:c>
+      <x:c r="L172" s="5" t="str">
+        <x:v>12분이내</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:tableParts count="1">
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ref851b6f575d4b16"/>
+  </x:tableParts>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:sheetData>
+    <x:row r="1" ht="26" customHeight="1">
+      <x:c r="A1" s="7" t="str">
+        <x:v>레시피ID</x:v>
+      </x:c>
+      <x:c r="B1" s="7" t="str">
+        <x:v>레시피명</x:v>
+      </x:c>
+      <x:c r="C1" s="7" t="str">
+        <x:v>메뉴 대분류</x:v>
+      </x:c>
+      <x:c r="D1" s="7" t="str">
+        <x:v>세부 카테고리</x:v>
+      </x:c>
+      <x:c r="E1" s="7" t="str">
+        <x:v>주재료</x:v>
+      </x:c>
+      <x:c r="F1" s="7" t="str">
+        <x:v>상황 태그</x:v>
+      </x:c>
+      <x:c r="G1" s="7" t="str">
+        <x:v>재료명</x:v>
+      </x:c>
+      <x:c r="H1" s="7" t="str">
+        <x:v>재료 분량</x:v>
+      </x:c>
+      <x:c r="I1" s="7" t="str">
+        <x:v>재료 수</x:v>
+      </x:c>
+      <x:c r="J1" s="7" t="str">
+        <x:v>총 소요 시간(분)</x:v>
+      </x:c>
+      <x:c r="K1" s="7" t="str">
+        <x:v>난이도</x:v>
+      </x:c>
+      <x:c r="L1" s="7" t="str">
+        <x:v>필요 도구</x:v>
+      </x:c>
+      <x:c r="M1" s="7" t="str">
+        <x:v>설거지 수준</x:v>
+      </x:c>
+      <x:c r="N1" s="7" t="str">
+        <x:v>조리 단계 수</x:v>
+      </x:c>
+      <x:c r="O1" s="7" t="str">
+        <x:v>조리 단계</x:v>
+      </x:c>
+      <x:c r="P1" s="7" t="str">
+        <x:v>단계별 시간</x:v>
+      </x:c>
+      <x:c r="Q1" s="7" t="str">
+        <x:v>보관 방법</x:v>
+      </x:c>
+      <x:c r="R1" s="7" t="str">
+        <x:v>대체 재료</x:v>
+      </x:c>
+      <x:c r="S1" s="7" t="str">
+        <x:v>생략 가능 재료</x:v>
+      </x:c>
+      <x:c r="T1" s="7" t="str">
+        <x:v>초보 팁</x:v>
+      </x:c>
+      <x:c r="U1" s="7" t="str">
+        <x:v>실패 방지 팁</x:v>
+      </x:c>
+      <x:c r="V1" s="7" t="str">
+        <x:v>초보 적합도(5점)</x:v>
+      </x:c>
+      <x:c r="W1" s="7" t="str">
+        <x:v>1인 가구 적합도(5점)</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" ht="22" customHeight="1">
       <x:c r="A2" t="n">
         <x:v>1001</x:v>
       </x:c>
@@ -471,7 +7028,7 @@
         <x:v>5</x:v>
       </x:c>
     </x:row>
-    <x:row r="3">
+    <x:row r="3" ht="22" customHeight="1">
       <x:c r="A3" t="n">
         <x:v>1002</x:v>
       </x:c>
@@ -542,7 +7099,7 @@
         <x:v>5</x:v>
       </x:c>
     </x:row>
-    <x:row r="4">
+    <x:row r="4" ht="22" customHeight="1">
       <x:c r="A4" t="n">
         <x:v>1003</x:v>
       </x:c>
@@ -613,7 +7170,7 @@
         <x:v>5</x:v>
       </x:c>
     </x:row>
-    <x:row r="5">
+    <x:row r="5" ht="22" customHeight="1">
       <x:c r="A5" t="n">
         <x:v>1004</x:v>
       </x:c>
@@ -684,7 +7241,7 @@
         <x:v>4</x:v>
       </x:c>
     </x:row>
-    <x:row r="6">
+    <x:row r="6" ht="22" customHeight="1">
       <x:c r="A6" t="n">
         <x:v>1005</x:v>
       </x:c>
@@ -755,7 +7312,7 @@
         <x:v>5</x:v>
       </x:c>
     </x:row>
-    <x:row r="7">
+    <x:row r="7" ht="22" customHeight="1">
       <x:c r="A7" t="n">
         <x:v>1006</x:v>
       </x:c>
@@ -826,7 +7383,7 @@
         <x:v>5</x:v>
       </x:c>
     </x:row>
-    <x:row r="8">
+    <x:row r="8" ht="22" customHeight="1">
       <x:c r="A8" t="n">
         <x:v>1007</x:v>
       </x:c>
@@ -897,14 +7454,14 @@
         <x:v>4</x:v>
       </x:c>
     </x:row>
-    <x:row r="9">
+    <x:row r="9" ht="22" customHeight="1">
       <x:c r="A9" t="n">
         <x:v>1008</x:v>
       </x:c>
       <x:c r="B9" t="str">
         <x:v>계란장</x:v>
       </x:c>
-      <x:c r="C9" s="1" t="str">
+      <x:c r="C9" t="str">
         <x:v>반찬</x:v>
       </x:c>
       <x:c r="D9" t="str">
@@ -968,7 +7525,7 @@
         <x:v>4</x:v>
       </x:c>
     </x:row>
-    <x:row r="10">
+    <x:row r="10" ht="22" customHeight="1">
       <x:c r="A10" t="n">
         <x:v>1009</x:v>
       </x:c>
@@ -1039,7 +7596,7 @@
         <x:v>5</x:v>
       </x:c>
     </x:row>
-    <x:row r="11">
+    <x:row r="11" ht="22" customHeight="1">
       <x:c r="A11" t="n">
         <x:v>1010</x:v>
       </x:c>
@@ -1110,7 +7667,7 @@
         <x:v>5</x:v>
       </x:c>
     </x:row>
-    <x:row r="12">
+    <x:row r="12" ht="22" customHeight="1">
       <x:c r="A12" t="n">
         <x:v>1011</x:v>
       </x:c>
@@ -1181,7 +7738,7 @@
         <x:v>5</x:v>
       </x:c>
     </x:row>
-    <x:row r="13">
+    <x:row r="13" ht="22" customHeight="1">
       <x:c r="A13" t="n">
         <x:v>1012</x:v>
       </x:c>
@@ -1252,7 +7809,7 @@
         <x:v>4</x:v>
       </x:c>
     </x:row>
-    <x:row r="14">
+    <x:row r="14" ht="22" customHeight="1">
       <x:c r="A14" t="n">
         <x:v>1013</x:v>
       </x:c>
@@ -1323,7 +7880,7 @@
         <x:v>5</x:v>
       </x:c>
     </x:row>
-    <x:row r="15">
+    <x:row r="15" ht="22" customHeight="1">
       <x:c r="A15" t="n">
         <x:v>1014</x:v>
       </x:c>
@@ -1394,7 +7951,7 @@
         <x:v>4</x:v>
       </x:c>
     </x:row>
-    <x:row r="16">
+    <x:row r="16" ht="22" customHeight="1">
       <x:c r="A16" t="n">
         <x:v>1015</x:v>
       </x:c>
@@ -1465,7 +8022,7 @@
         <x:v>5</x:v>
       </x:c>
     </x:row>
-    <x:row r="17">
+    <x:row r="17" ht="22" customHeight="1">
       <x:c r="A17" t="n">
         <x:v>1016</x:v>
       </x:c>
@@ -1536,7 +8093,7 @@
         <x:v>5</x:v>
       </x:c>
     </x:row>
-    <x:row r="18">
+    <x:row r="18" ht="22" customHeight="1">
       <x:c r="A18" t="n">
         <x:v>1017</x:v>
       </x:c>
@@ -1607,7 +8164,7 @@
         <x:v>5</x:v>
       </x:c>
     </x:row>
-    <x:row r="19">
+    <x:row r="19" ht="22" customHeight="1">
       <x:c r="A19" t="n">
         <x:v>1018</x:v>
       </x:c>
@@ -1678,7 +8235,7 @@
         <x:v>5</x:v>
       </x:c>
     </x:row>
-    <x:row r="20">
+    <x:row r="20" ht="22" customHeight="1">
       <x:c r="A20" t="n">
         <x:v>1019</x:v>
       </x:c>
@@ -1749,7 +8306,7 @@
         <x:v>5</x:v>
       </x:c>
     </x:row>
-    <x:row r="21">
+    <x:row r="21" ht="22" customHeight="1">
       <x:c r="A21" t="n">
         <x:v>1020</x:v>
       </x:c>
@@ -1820,7 +8377,7 @@
         <x:v>5</x:v>
       </x:c>
     </x:row>
-    <x:row r="22">
+    <x:row r="22" ht="22" customHeight="1">
       <x:c r="A22" t="n">
         <x:v>1021</x:v>
       </x:c>
@@ -1891,7 +8448,7 @@
         <x:v>5</x:v>
       </x:c>
     </x:row>
-    <x:row r="23">
+    <x:row r="23" ht="22" customHeight="1">
       <x:c r="A23" t="n">
         <x:v>1022</x:v>
       </x:c>
@@ -1962,7 +8519,7 @@
         <x:v>5</x:v>
       </x:c>
     </x:row>
-    <x:row r="24">
+    <x:row r="24" ht="22" customHeight="1">
       <x:c r="A24" t="n">
         <x:v>1023</x:v>
       </x:c>
@@ -2033,7 +8590,7 @@
         <x:v>5</x:v>
       </x:c>
     </x:row>
-    <x:row r="25">
+    <x:row r="25" ht="22" customHeight="1">
       <x:c r="A25" t="n">
         <x:v>1024</x:v>
       </x:c>
@@ -2104,7 +8661,7 @@
         <x:v>4</x:v>
       </x:c>
     </x:row>
-    <x:row r="26">
+    <x:row r="26" ht="22" customHeight="1">
       <x:c r="A26" t="n">
         <x:v>1025</x:v>
       </x:c>
@@ -2175,7 +8732,7 @@
         <x:v>5</x:v>
       </x:c>
     </x:row>
-    <x:row r="27">
+    <x:row r="27" ht="22" customHeight="1">
       <x:c r="A27" t="n">
         <x:v>1026</x:v>
       </x:c>
@@ -2246,7 +8803,7 @@
         <x:v>5</x:v>
       </x:c>
     </x:row>
-    <x:row r="28">
+    <x:row r="28" ht="22" customHeight="1">
       <x:c r="A28" t="n">
         <x:v>1027</x:v>
       </x:c>
@@ -2317,7 +8874,7 @@
         <x:v>4</x:v>
       </x:c>
     </x:row>
-    <x:row r="29">
+    <x:row r="29" ht="22" customHeight="1">
       <x:c r="A29" t="n">
         <x:v>1028</x:v>
       </x:c>
@@ -2388,7 +8945,7 @@
         <x:v>5</x:v>
       </x:c>
     </x:row>
-    <x:row r="30">
+    <x:row r="30" ht="22" customHeight="1">
       <x:c r="A30" t="n">
         <x:v>1029</x:v>
       </x:c>
@@ -2459,7 +9016,7 @@
         <x:v>5</x:v>
       </x:c>
     </x:row>
-    <x:row r="31">
+    <x:row r="31" ht="22" customHeight="1">
       <x:c r="A31" t="n">
         <x:v>1030</x:v>
       </x:c>
@@ -2530,7 +9087,7 @@
         <x:v>5</x:v>
       </x:c>
     </x:row>
-    <x:row r="32">
+    <x:row r="32" ht="22" customHeight="1">
       <x:c r="A32" t="n">
         <x:v>1031</x:v>
       </x:c>
@@ -2601,7 +9158,7 @@
         <x:v>5</x:v>
       </x:c>
     </x:row>
-    <x:row r="33">
+    <x:row r="33" ht="22" customHeight="1">
       <x:c r="A33" t="n">
         <x:v>1032</x:v>
       </x:c>
@@ -2672,7 +9229,7 @@
         <x:v>5</x:v>
       </x:c>
     </x:row>
-    <x:row r="34">
+    <x:row r="34" ht="22" customHeight="1">
       <x:c r="A34" t="n">
         <x:v>1033</x:v>
       </x:c>
@@ -2743,7 +9300,7 @@
         <x:v>5</x:v>
       </x:c>
     </x:row>
-    <x:row r="35">
+    <x:row r="35" ht="22" customHeight="1">
       <x:c r="A35" t="n">
         <x:v>1034</x:v>
       </x:c>
@@ -2814,7 +9371,7 @@
         <x:v>5</x:v>
       </x:c>
     </x:row>
-    <x:row r="36">
+    <x:row r="36" ht="22" customHeight="1">
       <x:c r="A36" t="n">
         <x:v>1035</x:v>
       </x:c>
@@ -2885,7 +9442,7 @@
         <x:v>5</x:v>
       </x:c>
     </x:row>
-    <x:row r="37">
+    <x:row r="37" ht="22" customHeight="1">
       <x:c r="A37" t="n">
         <x:v>1036</x:v>
       </x:c>
@@ -2956,7 +9513,7 @@
         <x:v>5</x:v>
       </x:c>
     </x:row>
-    <x:row r="38">
+    <x:row r="38" ht="22" customHeight="1">
       <x:c r="A38" t="n">
         <x:v>1037</x:v>
       </x:c>
@@ -3027,7 +9584,7 @@
         <x:v>5</x:v>
       </x:c>
     </x:row>
-    <x:row r="39">
+    <x:row r="39" ht="22" customHeight="1">
       <x:c r="A39" t="n">
         <x:v>1038</x:v>
       </x:c>
@@ -3098,7 +9655,7 @@
         <x:v>5</x:v>
       </x:c>
     </x:row>
-    <x:row r="40">
+    <x:row r="40" ht="22" customHeight="1">
       <x:c r="A40" t="n">
         <x:v>1039</x:v>
       </x:c>
@@ -3169,7 +9726,7 @@
         <x:v>5</x:v>
       </x:c>
     </x:row>
-    <x:row r="41">
+    <x:row r="41" ht="22" customHeight="1">
       <x:c r="A41" t="n">
         <x:v>1040</x:v>
       </x:c>
@@ -3240,7 +9797,7 @@
         <x:v>3</x:v>
       </x:c>
     </x:row>
-    <x:row r="42">
+    <x:row r="42" ht="22" customHeight="1">
       <x:c r="A42" t="n">
         <x:v>1041</x:v>
       </x:c>
@@ -3311,7 +9868,7 @@
         <x:v>5</x:v>
       </x:c>
     </x:row>
-    <x:row r="43">
+    <x:row r="43" ht="22" customHeight="1">
       <x:c r="A43" t="n">
         <x:v>2001</x:v>
       </x:c>
@@ -3382,7 +9939,7 @@
         <x:v>5</x:v>
       </x:c>
     </x:row>
-    <x:row r="44">
+    <x:row r="44" ht="22" customHeight="1">
       <x:c r="A44" t="n">
         <x:v>2002</x:v>
       </x:c>
@@ -3453,7 +10010,7 @@
         <x:v>5</x:v>
       </x:c>
     </x:row>
-    <x:row r="45">
+    <x:row r="45" ht="22" customHeight="1">
       <x:c r="A45" t="n">
         <x:v>2003</x:v>
       </x:c>
@@ -3524,7 +10081,7 @@
         <x:v>4</x:v>
       </x:c>
     </x:row>
-    <x:row r="46">
+    <x:row r="46" ht="22" customHeight="1">
       <x:c r="A46" t="n">
         <x:v>2004</x:v>
       </x:c>
@@ -3595,7 +10152,7 @@
         <x:v>5</x:v>
       </x:c>
     </x:row>
-    <x:row r="47">
+    <x:row r="47" ht="22" customHeight="1">
       <x:c r="A47" t="n">
         <x:v>2005</x:v>
       </x:c>
@@ -3666,7 +10223,7 @@
         <x:v>4</x:v>
       </x:c>
     </x:row>
-    <x:row r="48">
+    <x:row r="48" ht="22" customHeight="1">
       <x:c r="A48" t="n">
         <x:v>2006</x:v>
       </x:c>
@@ -3737,7 +10294,7 @@
         <x:v>5</x:v>
       </x:c>
     </x:row>
-    <x:row r="49">
+    <x:row r="49" ht="22" customHeight="1">
       <x:c r="A49" t="n">
         <x:v>2007</x:v>
       </x:c>
@@ -3808,7 +10365,7 @@
         <x:v>4</x:v>
       </x:c>
     </x:row>
-    <x:row r="50">
+    <x:row r="50" ht="22" customHeight="1">
       <x:c r="A50" t="n">
         <x:v>2008</x:v>
       </x:c>
@@ -3879,7 +10436,7 @@
         <x:v>5</x:v>
       </x:c>
     </x:row>
-    <x:row r="51">
+    <x:row r="51" ht="22" customHeight="1">
       <x:c r="A51" t="n">
         <x:v>2009</x:v>
       </x:c>
@@ -3950,7 +10507,7 @@
         <x:v>5</x:v>
       </x:c>
     </x:row>
-    <x:row r="52">
+    <x:row r="52" ht="22" customHeight="1">
       <x:c r="A52" t="n">
         <x:v>2010</x:v>
       </x:c>
@@ -4021,7 +10578,7 @@
         <x:v>5</x:v>
       </x:c>
     </x:row>
-    <x:row r="53">
+    <x:row r="53" ht="22" customHeight="1">
       <x:c r="A53" t="n">
         <x:v>2011</x:v>
       </x:c>
@@ -4092,7 +10649,7 @@
         <x:v>5</x:v>
       </x:c>
     </x:row>
-    <x:row r="54">
+    <x:row r="54" ht="22" customHeight="1">
       <x:c r="A54" t="n">
         <x:v>2012</x:v>
       </x:c>
@@ -4163,7 +10720,7 @@
         <x:v>5</x:v>
       </x:c>
     </x:row>
-    <x:row r="55">
+    <x:row r="55" ht="22" customHeight="1">
       <x:c r="A55" t="n">
         <x:v>3001</x:v>
       </x:c>
@@ -4234,7 +10791,7 @@
         <x:v>5</x:v>
       </x:c>
     </x:row>
-    <x:row r="56">
+    <x:row r="56" ht="22" customHeight="1">
       <x:c r="A56" t="n">
         <x:v>3002</x:v>
       </x:c>
@@ -4305,7 +10862,7 @@
         <x:v>4</x:v>
       </x:c>
     </x:row>
-    <x:row r="57">
+    <x:row r="57" ht="22" customHeight="1">
       <x:c r="A57" t="n">
         <x:v>3003</x:v>
       </x:c>
@@ -4376,7 +10933,7 @@
         <x:v>5</x:v>
       </x:c>
     </x:row>
-    <x:row r="58">
+    <x:row r="58" ht="22" customHeight="1">
       <x:c r="A58" t="n">
         <x:v>3004</x:v>
       </x:c>
@@ -4447,7 +11004,7 @@
         <x:v>5</x:v>
       </x:c>
     </x:row>
-    <x:row r="59">
+    <x:row r="59" ht="22" customHeight="1">
       <x:c r="A59" t="n">
         <x:v>3005</x:v>
       </x:c>
@@ -4518,7 +11075,7 @@
         <x:v>5</x:v>
       </x:c>
     </x:row>
-    <x:row r="60">
+    <x:row r="60" ht="22" customHeight="1">
       <x:c r="A60" t="n">
         <x:v>3006</x:v>
       </x:c>
@@ -4589,7 +11146,7 @@
         <x:v>5</x:v>
       </x:c>
     </x:row>
-    <x:row r="61">
+    <x:row r="61" ht="22" customHeight="1">
       <x:c r="A61" t="n">
         <x:v>3007</x:v>
       </x:c>
@@ -4660,7 +11217,7 @@
         <x:v>5</x:v>
       </x:c>
     </x:row>
-    <x:row r="62">
+    <x:row r="62" ht="22" customHeight="1">
       <x:c r="A62" t="n">
         <x:v>3008</x:v>
       </x:c>
@@ -4731,7 +11288,7 @@
         <x:v>4</x:v>
       </x:c>
     </x:row>
-    <x:row r="63">
+    <x:row r="63" ht="22" customHeight="1">
       <x:c r="A63" t="n">
         <x:v>3009</x:v>
       </x:c>
@@ -4802,7 +11359,7 @@
         <x:v>5</x:v>
       </x:c>
     </x:row>
-    <x:row r="64">
+    <x:row r="64" ht="22" customHeight="1">
       <x:c r="A64" t="n">
         <x:v>3010</x:v>
       </x:c>
@@ -4873,7 +11430,7 @@
         <x:v>5</x:v>
       </x:c>
     </x:row>
-    <x:row r="65">
+    <x:row r="65" ht="22" customHeight="1">
       <x:c r="A65" t="n">
         <x:v>3011</x:v>
       </x:c>
@@ -4944,7 +11501,7 @@
         <x:v>5</x:v>
       </x:c>
     </x:row>
-    <x:row r="66">
+    <x:row r="66" ht="22" customHeight="1">
       <x:c r="A66" t="n">
         <x:v>4001</x:v>
       </x:c>
@@ -5015,7 +11572,7 @@
         <x:v>5</x:v>
       </x:c>
     </x:row>
-    <x:row r="67">
+    <x:row r="67" ht="22" customHeight="1">
       <x:c r="A67" t="n">
         <x:v>4002</x:v>
       </x:c>
@@ -5086,7 +11643,7 @@
         <x:v>5</x:v>
       </x:c>
     </x:row>
-    <x:row r="68">
+    <x:row r="68" ht="22" customHeight="1">
       <x:c r="A68" t="n">
         <x:v>4003</x:v>
       </x:c>
@@ -5157,7 +11714,7 @@
         <x:v>5</x:v>
       </x:c>
     </x:row>
-    <x:row r="69">
+    <x:row r="69" ht="22" customHeight="1">
       <x:c r="A69" t="n">
         <x:v>4004</x:v>
       </x:c>
@@ -5228,7 +11785,7 @@
         <x:v>5</x:v>
       </x:c>
     </x:row>
-    <x:row r="70">
+    <x:row r="70" ht="22" customHeight="1">
       <x:c r="A70" t="n">
         <x:v>4005</x:v>
       </x:c>
@@ -5299,7 +11856,7 @@
         <x:v>5</x:v>
       </x:c>
     </x:row>
-    <x:row r="71">
+    <x:row r="71" ht="22" customHeight="1">
       <x:c r="A71" t="n">
         <x:v>4006</x:v>
       </x:c>
@@ -5370,7 +11927,7 @@
         <x:v>5</x:v>
       </x:c>
     </x:row>
-    <x:row r="72">
+    <x:row r="72" ht="22" customHeight="1">
       <x:c r="A72" t="n">
         <x:v>5001</x:v>
       </x:c>
@@ -5441,7 +11998,7 @@
         <x:v>5</x:v>
       </x:c>
     </x:row>
-    <x:row r="73">
+    <x:row r="73" ht="22" customHeight="1">
       <x:c r="A73" t="n">
         <x:v>5002</x:v>
       </x:c>
@@ -5512,7 +12069,7 @@
         <x:v>5</x:v>
       </x:c>
     </x:row>
-    <x:row r="74">
+    <x:row r="74" ht="22" customHeight="1">
       <x:c r="A74" t="n">
         <x:v>5003</x:v>
       </x:c>
@@ -5583,7 +12140,7 @@
         <x:v>5</x:v>
       </x:c>
     </x:row>
-    <x:row r="75">
+    <x:row r="75" ht="22" customHeight="1">
       <x:c r="A75" t="n">
         <x:v>5004</x:v>
       </x:c>
@@ -5654,7 +12211,7 @@
         <x:v>4</x:v>
       </x:c>
     </x:row>
-    <x:row r="76">
+    <x:row r="76" ht="22" customHeight="1">
       <x:c r="A76" t="n">
         <x:v>5005</x:v>
       </x:c>
@@ -5725,7 +12282,7 @@
         <x:v>4</x:v>
       </x:c>
     </x:row>
-    <x:row r="77">
+    <x:row r="77" ht="22" customHeight="1">
       <x:c r="A77" t="n">
         <x:v>5006</x:v>
       </x:c>
@@ -5796,7 +12353,7 @@
         <x:v>5</x:v>
       </x:c>
     </x:row>
-    <x:row r="78">
+    <x:row r="78" ht="22" customHeight="1">
       <x:c r="A78" t="n">
         <x:v>5007</x:v>
       </x:c>
@@ -5867,7 +12424,7 @@
         <x:v>5</x:v>
       </x:c>
     </x:row>
-    <x:row r="79">
+    <x:row r="79" ht="22" customHeight="1">
       <x:c r="A79" t="n">
         <x:v>5008</x:v>
       </x:c>
@@ -5938,7 +12495,7 @@
         <x:v>5</x:v>
       </x:c>
     </x:row>
-    <x:row r="80">
+    <x:row r="80" ht="22" customHeight="1">
       <x:c r="A80" t="n">
         <x:v>5009</x:v>
       </x:c>
@@ -6009,7 +12566,7 @@
         <x:v>5</x:v>
       </x:c>
     </x:row>
-    <x:row r="81">
+    <x:row r="81" ht="22" customHeight="1">
       <x:c r="A81" t="n">
         <x:v>5010</x:v>
       </x:c>
@@ -6080,7 +12637,7 @@
         <x:v>5</x:v>
       </x:c>
     </x:row>
-    <x:row r="82">
+    <x:row r="82" ht="22" customHeight="1">
       <x:c r="A82" t="n">
         <x:v>5011</x:v>
       </x:c>
@@ -6151,7 +12708,7 @@
         <x:v>5</x:v>
       </x:c>
     </x:row>
-    <x:row r="83">
+    <x:row r="83" ht="22" customHeight="1">
       <x:c r="A83" t="n">
         <x:v>5012</x:v>
       </x:c>
@@ -6222,7 +12779,7 @@
         <x:v>5</x:v>
       </x:c>
     </x:row>
-    <x:row r="84">
+    <x:row r="84" ht="22" customHeight="1">
       <x:c r="A84" t="n">
         <x:v>5013</x:v>
       </x:c>
@@ -6293,7 +12850,7 @@
         <x:v>5</x:v>
       </x:c>
     </x:row>
-    <x:row r="85">
+    <x:row r="85" ht="22" customHeight="1">
       <x:c r="A85" t="n">
         <x:v>5014</x:v>
       </x:c>
@@ -6364,7 +12921,7 @@
         <x:v>4</x:v>
       </x:c>
     </x:row>
-    <x:row r="86">
+    <x:row r="86" ht="22" customHeight="1">
       <x:c r="A86" t="n">
         <x:v>5015</x:v>
       </x:c>
@@ -6435,7 +12992,7 @@
         <x:v>5</x:v>
       </x:c>
     </x:row>
-    <x:row r="87">
+    <x:row r="87" ht="22" customHeight="1">
       <x:c r="A87" t="n">
         <x:v>6001</x:v>
       </x:c>
@@ -6506,7 +13063,7 @@
         <x:v>4</x:v>
       </x:c>
     </x:row>
-    <x:row r="88">
+    <x:row r="88" ht="22" customHeight="1">
       <x:c r="A88" t="n">
         <x:v>6002</x:v>
       </x:c>
@@ -6577,7 +13134,7 @@
         <x:v>5</x:v>
       </x:c>
     </x:row>
-    <x:row r="89">
+    <x:row r="89" ht="22" customHeight="1">
       <x:c r="A89" t="n">
         <x:v>6003</x:v>
       </x:c>
@@ -6648,7 +13205,7 @@
         <x:v>5</x:v>
       </x:c>
     </x:row>
-    <x:row r="90">
+    <x:row r="90" ht="22" customHeight="1">
       <x:c r="A90" t="n">
         <x:v>6004</x:v>
       </x:c>
@@ -6719,7 +13276,7 @@
         <x:v>5</x:v>
       </x:c>
     </x:row>
-    <x:row r="91">
+    <x:row r="91" ht="22" customHeight="1">
       <x:c r="A91" t="n">
         <x:v>6005</x:v>
       </x:c>
@@ -6790,7 +13347,7 @@
         <x:v>4</x:v>
       </x:c>
     </x:row>
-    <x:row r="92">
+    <x:row r="92" ht="22" customHeight="1">
       <x:c r="A92" t="n">
         <x:v>6006</x:v>
       </x:c>
@@ -6861,7 +13418,7 @@
         <x:v>5</x:v>
       </x:c>
     </x:row>
-    <x:row r="93">
+    <x:row r="93" ht="22" customHeight="1">
       <x:c r="A93" t="n">
         <x:v>6007</x:v>
       </x:c>
@@ -6932,7 +13489,7 @@
         <x:v>5</x:v>
       </x:c>
     </x:row>
-    <x:row r="94">
+    <x:row r="94" ht="22" customHeight="1">
       <x:c r="A94" t="n">
         <x:v>6008</x:v>
       </x:c>
@@ -7003,7 +13560,7 @@
         <x:v>5</x:v>
       </x:c>
     </x:row>
-    <x:row r="95">
+    <x:row r="95" ht="22" customHeight="1">
       <x:c r="A95" t="n">
         <x:v>6009</x:v>
       </x:c>
@@ -7074,7 +13631,7 @@
         <x:v>5</x:v>
       </x:c>
     </x:row>
-    <x:row r="96">
+    <x:row r="96" ht="22" customHeight="1">
       <x:c r="A96" t="n">
         <x:v>7001</x:v>
       </x:c>
@@ -7145,7 +13702,7 @@
         <x:v>5</x:v>
       </x:c>
     </x:row>
-    <x:row r="97">
+    <x:row r="97" ht="22" customHeight="1">
       <x:c r="A97" t="n">
         <x:v>7002</x:v>
       </x:c>
@@ -7216,7 +13773,7 @@
         <x:v>5</x:v>
       </x:c>
     </x:row>
-    <x:row r="98">
+    <x:row r="98" ht="22" customHeight="1">
       <x:c r="A98" t="n">
         <x:v>7003</x:v>
       </x:c>
@@ -7287,7 +13844,7 @@
         <x:v>4</x:v>
       </x:c>
     </x:row>
-    <x:row r="99">
+    <x:row r="99" ht="22" customHeight="1">
       <x:c r="A99" t="n">
         <x:v>7004</x:v>
       </x:c>
@@ -7358,7 +13915,7 @@
         <x:v>5</x:v>
       </x:c>
     </x:row>
-    <x:row r="100">
+    <x:row r="100" ht="22" customHeight="1">
       <x:c r="A100" t="n">
         <x:v>7005</x:v>
       </x:c>
@@ -7429,7 +13986,7 @@
         <x:v>5</x:v>
       </x:c>
     </x:row>
-    <x:row r="101">
+    <x:row r="101" ht="22" customHeight="1">
       <x:c r="A101" t="n">
         <x:v>7006</x:v>
       </x:c>
@@ -7500,7 +14057,7 @@
         <x:v>5</x:v>
       </x:c>
     </x:row>
-    <x:row r="102">
+    <x:row r="102" ht="22" customHeight="1">
       <x:c r="A102" t="n">
         <x:v>7007</x:v>
       </x:c>
@@ -7571,7 +14128,7 @@
         <x:v>5</x:v>
       </x:c>
     </x:row>
-    <x:row r="103">
+    <x:row r="103" ht="22" customHeight="1">
       <x:c r="A103" t="n">
         <x:v>7008</x:v>
       </x:c>
@@ -7642,7 +14199,7 @@
         <x:v>4</x:v>
       </x:c>
     </x:row>
-    <x:row r="104">
+    <x:row r="104" ht="22" customHeight="1">
       <x:c r="A104" t="n">
         <x:v>7009</x:v>
       </x:c>
@@ -7713,7 +14270,7 @@
         <x:v>4</x:v>
       </x:c>
     </x:row>
-    <x:row r="105">
+    <x:row r="105" ht="22" customHeight="1">
       <x:c r="A105" t="n">
         <x:v>7010</x:v>
       </x:c>
@@ -7784,7 +14341,7 @@
         <x:v>5</x:v>
       </x:c>
     </x:row>
-    <x:row r="106">
+    <x:row r="106" ht="22" customHeight="1">
       <x:c r="A106" t="n">
         <x:v>7011</x:v>
       </x:c>
@@ -7855,7 +14412,7 @@
         <x:v>5</x:v>
       </x:c>
     </x:row>
-    <x:row r="107">
+    <x:row r="107" ht="22" customHeight="1">
       <x:c r="A107" t="n">
         <x:v>7012</x:v>
       </x:c>
@@ -7926,7 +14483,7 @@
         <x:v>4</x:v>
       </x:c>
     </x:row>
-    <x:row r="108">
+    <x:row r="108" ht="22" customHeight="1">
       <x:c r="A108" t="n">
         <x:v>7013</x:v>
       </x:c>
@@ -7997,7 +14554,7 @@
         <x:v>4</x:v>
       </x:c>
     </x:row>
-    <x:row r="109">
+    <x:row r="109" ht="22" customHeight="1">
       <x:c r="A109" t="n">
         <x:v>7014</x:v>
       </x:c>
@@ -8068,7 +14625,7 @@
         <x:v>4</x:v>
       </x:c>
     </x:row>
-    <x:row r="110">
+    <x:row r="110" ht="22" customHeight="1">
       <x:c r="A110" t="n">
         <x:v>7015</x:v>
       </x:c>
@@ -8139,7 +14696,7 @@
         <x:v>5</x:v>
       </x:c>
     </x:row>
-    <x:row r="111">
+    <x:row r="111" ht="22" customHeight="1">
       <x:c r="A111" t="n">
         <x:v>7016</x:v>
       </x:c>
@@ -8210,7 +14767,7 @@
         <x:v>5</x:v>
       </x:c>
     </x:row>
-    <x:row r="112">
+    <x:row r="112" ht="22" customHeight="1">
       <x:c r="A112" t="n">
         <x:v>8001</x:v>
       </x:c>
@@ -8281,7 +14838,7 @@
         <x:v>4</x:v>
       </x:c>
     </x:row>
-    <x:row r="113">
+    <x:row r="113" ht="22" customHeight="1">
       <x:c r="A113" t="n">
         <x:v>8002</x:v>
       </x:c>
@@ -8352,7 +14909,7 @@
         <x:v>3</x:v>
       </x:c>
     </x:row>
-    <x:row r="114">
+    <x:row r="114" ht="22" customHeight="1">
       <x:c r="A114" t="n">
         <x:v>8003</x:v>
       </x:c>
@@ -8423,7 +14980,7 @@
         <x:v>4</x:v>
       </x:c>
     </x:row>
-    <x:row r="115">
+    <x:row r="115" ht="22" customHeight="1">
       <x:c r="A115" t="n">
         <x:v>8004</x:v>
       </x:c>
@@ -8494,7 +15051,7 @@
         <x:v>5</x:v>
       </x:c>
     </x:row>
-    <x:row r="116">
+    <x:row r="116" ht="22" customHeight="1">
       <x:c r="A116" t="n">
         <x:v>8005</x:v>
       </x:c>
@@ -8565,7 +15122,7 @@
         <x:v>4</x:v>
       </x:c>
     </x:row>
-    <x:row r="117">
+    <x:row r="117" ht="22" customHeight="1">
       <x:c r="A117" t="n">
         <x:v>8006</x:v>
       </x:c>
@@ -8636,7 +15193,7 @@
         <x:v>4</x:v>
       </x:c>
     </x:row>
-    <x:row r="118">
+    <x:row r="118" ht="22" customHeight="1">
       <x:c r="A118" t="n">
         <x:v>8007</x:v>
       </x:c>
@@ -8707,7 +15264,7 @@
         <x:v>3</x:v>
       </x:c>
     </x:row>
-    <x:row r="119">
+    <x:row r="119" ht="22" customHeight="1">
       <x:c r="A119" t="n">
         <x:v>8008</x:v>
       </x:c>
@@ -8778,7 +15335,7 @@
         <x:v>4</x:v>
       </x:c>
     </x:row>
-    <x:row r="120">
+    <x:row r="120" ht="22" customHeight="1">
       <x:c r="A120" t="n">
         <x:v>8009</x:v>
       </x:c>
@@ -8849,7 +15406,7 @@
         <x:v>5</x:v>
       </x:c>
     </x:row>
-    <x:row r="121">
+    <x:row r="121" ht="22" customHeight="1">
       <x:c r="A121" t="n">
         <x:v>8010</x:v>
       </x:c>
@@ -8920,7 +15477,7 @@
         <x:v>3</x:v>
       </x:c>
     </x:row>
-    <x:row r="122">
+    <x:row r="122" ht="22" customHeight="1">
       <x:c r="A122" t="n">
         <x:v>8011</x:v>
       </x:c>
@@ -8991,7 +15548,7 @@
         <x:v>5</x:v>
       </x:c>
     </x:row>
-    <x:row r="123">
+    <x:row r="123" ht="22" customHeight="1">
       <x:c r="A123" t="n">
         <x:v>8012</x:v>
       </x:c>
@@ -9062,7 +15619,7 @@
         <x:v>4</x:v>
       </x:c>
     </x:row>
-    <x:row r="124">
+    <x:row r="124" ht="22" customHeight="1">
       <x:c r="A124" t="n">
         <x:v>8013</x:v>
       </x:c>
@@ -9133,7 +15690,7 @@
         <x:v>5</x:v>
       </x:c>
     </x:row>
-    <x:row r="125">
+    <x:row r="125" ht="22" customHeight="1">
       <x:c r="A125" t="n">
         <x:v>8014</x:v>
       </x:c>
@@ -9204,7 +15761,7 @@
         <x:v>3</x:v>
       </x:c>
     </x:row>
-    <x:row r="126">
+    <x:row r="126" ht="22" customHeight="1">
       <x:c r="A126" t="n">
         <x:v>8015</x:v>
       </x:c>
@@ -9275,7 +15832,7 @@
         <x:v>3</x:v>
       </x:c>
     </x:row>
-    <x:row r="127">
+    <x:row r="127" ht="22" customHeight="1">
       <x:c r="A127" t="n">
         <x:v>8016</x:v>
       </x:c>
@@ -9346,7 +15903,7 @@
         <x:v>3</x:v>
       </x:c>
     </x:row>
-    <x:row r="128">
+    <x:row r="128" ht="22" customHeight="1">
       <x:c r="A128" t="n">
         <x:v>8017</x:v>
       </x:c>
@@ -9417,7 +15974,7 @@
         <x:v>4</x:v>
       </x:c>
     </x:row>
-    <x:row r="129">
+    <x:row r="129" ht="22" customHeight="1">
       <x:c r="A129" t="n">
         <x:v>8018</x:v>
       </x:c>
@@ -9488,7 +16045,7 @@
         <x:v>4</x:v>
       </x:c>
     </x:row>
-    <x:row r="130">
+    <x:row r="130" ht="22" customHeight="1">
       <x:c r="A130" t="n">
         <x:v>8019</x:v>
       </x:c>
@@ -9559,7 +16116,7 @@
         <x:v>3</x:v>
       </x:c>
     </x:row>
-    <x:row r="131">
+    <x:row r="131" ht="22" customHeight="1">
       <x:c r="A131" t="n">
         <x:v>8020</x:v>
       </x:c>
@@ -9630,7 +16187,7 @@
         <x:v>5</x:v>
       </x:c>
     </x:row>
-    <x:row r="132">
+    <x:row r="132" ht="22" customHeight="1">
       <x:c r="A132" t="n">
         <x:v>8021</x:v>
       </x:c>
@@ -9701,7 +16258,7 @@
         <x:v>2</x:v>
       </x:c>
     </x:row>
-    <x:row r="133">
+    <x:row r="133" ht="22" customHeight="1">
       <x:c r="A133" t="n">
         <x:v>8022</x:v>
       </x:c>
@@ -9772,7 +16329,7 @@
         <x:v>3</x:v>
       </x:c>
     </x:row>
-    <x:row r="134">
+    <x:row r="134" ht="22" customHeight="1">
       <x:c r="A134" t="n">
         <x:v>8023</x:v>
       </x:c>
@@ -9843,7 +16400,7 @@
         <x:v>3</x:v>
       </x:c>
     </x:row>
-    <x:row r="135">
+    <x:row r="135" ht="22" customHeight="1">
       <x:c r="A135" t="n">
         <x:v>8024</x:v>
       </x:c>
@@ -9914,7 +16471,7 @@
         <x:v>4</x:v>
       </x:c>
     </x:row>
-    <x:row r="136">
+    <x:row r="136" ht="22" customHeight="1">
       <x:c r="A136" t="n">
         <x:v>8025</x:v>
       </x:c>
@@ -9985,7 +16542,7 @@
         <x:v>5</x:v>
       </x:c>
     </x:row>
-    <x:row r="137">
+    <x:row r="137" ht="22" customHeight="1">
       <x:c r="A137" t="n">
         <x:v>8026</x:v>
       </x:c>
@@ -10056,7 +16613,7 @@
         <x:v>3</x:v>
       </x:c>
     </x:row>
-    <x:row r="138">
+    <x:row r="138" ht="22" customHeight="1">
       <x:c r="A138" t="n">
         <x:v>8027</x:v>
       </x:c>
@@ -10127,7 +16684,7 @@
         <x:v>4</x:v>
       </x:c>
     </x:row>
-    <x:row r="139">
+    <x:row r="139" ht="22" customHeight="1">
       <x:c r="A139" t="n">
         <x:v>8028</x:v>
       </x:c>
@@ -10198,7 +16755,7 @@
         <x:v>4</x:v>
       </x:c>
     </x:row>
-    <x:row r="140">
+    <x:row r="140" ht="22" customHeight="1">
       <x:c r="A140" t="n">
         <x:v>9001</x:v>
       </x:c>
@@ -10269,7 +16826,7 @@
         <x:v>4</x:v>
       </x:c>
     </x:row>
-    <x:row r="141">
+    <x:row r="141" ht="22" customHeight="1">
       <x:c r="A141" t="n">
         <x:v>9002</x:v>
       </x:c>
@@ -10340,7 +16897,7 @@
         <x:v>5</x:v>
       </x:c>
     </x:row>
-    <x:row r="142">
+    <x:row r="142" ht="22" customHeight="1">
       <x:c r="A142" t="n">
         <x:v>9003</x:v>
       </x:c>
@@ -10411,7 +16968,7 @@
         <x:v>5</x:v>
       </x:c>
     </x:row>
-    <x:row r="143">
+    <x:row r="143" ht="22" customHeight="1">
       <x:c r="A143" t="n">
         <x:v>9004</x:v>
       </x:c>
@@ -10482,7 +17039,7 @@
         <x:v>5</x:v>
       </x:c>
     </x:row>
-    <x:row r="144">
+    <x:row r="144" ht="22" customHeight="1">
       <x:c r="A144" t="n">
         <x:v>9005</x:v>
       </x:c>
@@ -10553,7 +17110,7 @@
         <x:v>5</x:v>
       </x:c>
     </x:row>
-    <x:row r="145">
+    <x:row r="145" ht="22" customHeight="1">
       <x:c r="A145" t="n">
         <x:v>9006</x:v>
       </x:c>
@@ -10624,7 +17181,7 @@
         <x:v>5</x:v>
       </x:c>
     </x:row>
-    <x:row r="146">
+    <x:row r="146" ht="22" customHeight="1">
       <x:c r="A146" t="n">
         <x:v>10001</x:v>
       </x:c>
@@ -10695,7 +17252,7 @@
         <x:v>4</x:v>
       </x:c>
     </x:row>
-    <x:row r="147">
+    <x:row r="147" ht="22" customHeight="1">
       <x:c r="A147" t="n">
         <x:v>10002</x:v>
       </x:c>
@@ -10766,7 +17323,7 @@
         <x:v>5</x:v>
       </x:c>
     </x:row>
-    <x:row r="148">
+    <x:row r="148" ht="22" customHeight="1">
       <x:c r="A148" t="n">
         <x:v>10003</x:v>
       </x:c>
@@ -10837,7 +17394,7 @@
         <x:v>5</x:v>
       </x:c>
     </x:row>
-    <x:row r="149">
+    <x:row r="149" ht="22" customHeight="1">
       <x:c r="A149" t="n">
         <x:v>10004</x:v>
       </x:c>
@@ -10908,7 +17465,7 @@
         <x:v>4</x:v>
       </x:c>
     </x:row>
-    <x:row r="150">
+    <x:row r="150" ht="22" customHeight="1">
       <x:c r="A150" t="n">
         <x:v>10005</x:v>
       </x:c>
@@ -10979,7 +17536,7 @@
         <x:v>5</x:v>
       </x:c>
     </x:row>
-    <x:row r="151">
+    <x:row r="151" ht="22" customHeight="1">
       <x:c r="A151" t="n">
         <x:v>10006</x:v>
       </x:c>
@@ -11050,7 +17607,7 @@
         <x:v>5</x:v>
       </x:c>
     </x:row>
-    <x:row r="152">
+    <x:row r="152" ht="22" customHeight="1">
       <x:c r="A152" t="n">
         <x:v>10007</x:v>
       </x:c>
@@ -11121,7 +17678,7 @@
         <x:v>5</x:v>
       </x:c>
     </x:row>
-    <x:row r="153">
+    <x:row r="153" ht="22" customHeight="1">
       <x:c r="A153" t="n">
         <x:v>10008</x:v>
       </x:c>
@@ -11192,7 +17749,7 @@
         <x:v>5</x:v>
       </x:c>
     </x:row>
-    <x:row r="154">
+    <x:row r="154" ht="22" customHeight="1">
       <x:c r="A154" t="n">
         <x:v>10009</x:v>
       </x:c>
@@ -11263,7 +17820,7 @@
         <x:v>5</x:v>
       </x:c>
     </x:row>
-    <x:row r="155">
+    <x:row r="155" ht="22" customHeight="1">
       <x:c r="A155" t="n">
         <x:v>11001</x:v>
       </x:c>
@@ -11334,7 +17891,7 @@
         <x:v>5</x:v>
       </x:c>
     </x:row>
-    <x:row r="156">
+    <x:row r="156" ht="22" customHeight="1">
       <x:c r="A156" t="n">
         <x:v>11002</x:v>
       </x:c>
@@ -11405,7 +17962,7 @@
         <x:v>5</x:v>
       </x:c>
     </x:row>
-    <x:row r="157">
+    <x:row r="157" ht="22" customHeight="1">
       <x:c r="A157" t="n">
         <x:v>11003</x:v>
       </x:c>
@@ -11476,7 +18033,7 @@
         <x:v>5</x:v>
       </x:c>
     </x:row>
-    <x:row r="158">
+    <x:row r="158" ht="22" customHeight="1">
       <x:c r="A158" t="n">
         <x:v>11004</x:v>
       </x:c>
@@ -11547,7 +18104,7 @@
         <x:v>5</x:v>
       </x:c>
     </x:row>
-    <x:row r="159">
+    <x:row r="159" ht="22" customHeight="1">
       <x:c r="A159" t="n">
         <x:v>11005</x:v>
       </x:c>
@@ -11618,7 +18175,7 @@
         <x:v>5</x:v>
       </x:c>
     </x:row>
-    <x:row r="160">
+    <x:row r="160" ht="22" customHeight="1">
       <x:c r="A160" t="n">
         <x:v>11006</x:v>
       </x:c>
@@ -11689,7 +18246,7 @@
         <x:v>5</x:v>
       </x:c>
     </x:row>
-    <x:row r="161">
+    <x:row r="161" ht="22" customHeight="1">
       <x:c r="A161" t="n">
         <x:v>11007</x:v>
       </x:c>
@@ -11760,7 +18317,7 @@
         <x:v>5</x:v>
       </x:c>
     </x:row>
-    <x:row r="162">
+    <x:row r="162" ht="22" customHeight="1">
       <x:c r="A162" t="n">
         <x:v>12001</x:v>
       </x:c>
@@ -11831,7 +18388,7 @@
         <x:v>3</x:v>
       </x:c>
     </x:row>
-    <x:row r="163">
+    <x:row r="163" ht="22" customHeight="1">
       <x:c r="A163" t="n">
         <x:v>12002</x:v>
       </x:c>
@@ -11902,7 +18459,7 @@
         <x:v>5</x:v>
       </x:c>
     </x:row>
-    <x:row r="164">
+    <x:row r="164" ht="22" customHeight="1">
       <x:c r="A164" t="n">
         <x:v>12003</x:v>
       </x:c>
@@ -11973,7 +18530,7 @@
         <x:v>5</x:v>
       </x:c>
     </x:row>
-    <x:row r="165">
+    <x:row r="165" ht="22" customHeight="1">
       <x:c r="A165" t="n">
         <x:v>12004</x:v>
       </x:c>
@@ -12044,7 +18601,7 @@
         <x:v>4</x:v>
       </x:c>
     </x:row>
-    <x:row r="166">
+    <x:row r="166" ht="22" customHeight="1">
       <x:c r="A166" t="n">
         <x:v>12005</x:v>
       </x:c>
@@ -12115,7 +18672,7 @@
         <x:v>5</x:v>
       </x:c>
     </x:row>
-    <x:row r="167">
+    <x:row r="167" ht="22" customHeight="1">
       <x:c r="A167" t="n">
         <x:v>12006</x:v>
       </x:c>
@@ -12186,7 +18743,7 @@
         <x:v>4</x:v>
       </x:c>
     </x:row>
-    <x:row r="168">
+    <x:row r="168" ht="22" customHeight="1">
       <x:c r="A168" t="n">
         <x:v>12007</x:v>
       </x:c>
@@ -12257,7 +18814,7 @@
         <x:v>4</x:v>
       </x:c>
     </x:row>
-    <x:row r="169">
+    <x:row r="169" ht="22" customHeight="1">
       <x:c r="A169" t="n">
         <x:v>12008</x:v>
       </x:c>
@@ -12328,7 +18885,7 @@
         <x:v>4</x:v>
       </x:c>
     </x:row>
-    <x:row r="170">
+    <x:row r="170" ht="22" customHeight="1">
       <x:c r="A170" t="n">
         <x:v>12009</x:v>
       </x:c>
@@ -12399,7 +18956,7 @@
         <x:v>5</x:v>
       </x:c>
     </x:row>
-    <x:row r="171">
+    <x:row r="171" ht="22" customHeight="1">
       <x:c r="A171" t="n">
         <x:v>12010</x:v>
       </x:c>
@@ -12470,7 +19027,7 @@
         <x:v>4</x:v>
       </x:c>
     </x:row>
-    <x:row r="172">
+    <x:row r="172" ht="22" customHeight="1">
       <x:c r="A172" t="n">
         <x:v>12011</x:v>
       </x:c>
@@ -12543,5 +19100,8 @@
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:tableParts count="1">
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R959262c07b2d44a9"/>
+  </x:tableParts>
 </x:worksheet>
 </file>